--- a/2026 수능 LLM 풀이 hard.xlsx
+++ b/2026 수능 LLM 풀이 hard.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1000"/>
+  <dimension ref="A1:AH1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -640,6 +640,36 @@
           <t>Gemini 3.1 Flash-Lite (minimal)</t>
         </is>
       </c>
+      <c r="AC2" s="23" t="inlineStr">
+        <is>
+          <t>Kanana-o 9.8B</t>
+        </is>
+      </c>
+      <c r="AD2" s="23" t="inlineStr">
+        <is>
+          <t>o1 (high)</t>
+        </is>
+      </c>
+      <c r="AE2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-4.1</t>
+        </is>
+      </c>
+      <c r="AF2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-4o</t>
+        </is>
+      </c>
+      <c r="AG2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash (minimal)</t>
+        </is>
+      </c>
+      <c r="AH2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -726,6 +756,24 @@
       <c r="AB3" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AC3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -812,6 +860,24 @@
       <c r="AB4" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC4" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH4" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -898,6 +964,24 @@
       <c r="AB5" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AC5" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD5" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE5" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF5" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG5" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH5" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -984,6 +1068,24 @@
       <c r="AB6" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AC6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -1068,6 +1170,24 @@
         <v>4</v>
       </c>
       <c r="AB7" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH7" s="24" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1156,6 +1276,24 @@
       <c r="AB8" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AC8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH8" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -1242,6 +1380,24 @@
       <c r="AB9" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC9" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD9" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE9" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF9" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG9" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH9" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -1328,6 +1484,24 @@
       <c r="AB10" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AC10" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD10" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE10" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF10" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG10" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH10" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -1414,6 +1588,24 @@
       <c r="AB11" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC11" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD11" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE11" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF11" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG11" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH11" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -1500,6 +1692,24 @@
       <c r="AB12" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC12" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD12" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE12" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF12" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG12" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH12" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -1586,6 +1796,24 @@
       <c r="AB13" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AC13" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH13" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -1672,6 +1900,24 @@
       <c r="AB14" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AC14" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH14" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -1758,6 +2004,24 @@
       <c r="AB15" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AC15" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD15" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE15" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF15" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG15" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH15" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -1844,6 +2108,24 @@
       <c r="AB16" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC16" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD16" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE16" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF16" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG16" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH16" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -1930,6 +2212,24 @@
       <c r="AB17" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AC17" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD17" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE17" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF17" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG17" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH17" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -2016,6 +2316,24 @@
       <c r="AB18" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AC18" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD18" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE18" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF18" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG18" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH18" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -2102,6 +2420,24 @@
       <c r="AB19" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AC19" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD19" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE19" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF19" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG19" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH19" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -2188,6 +2524,24 @@
       <c r="AB20" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AC20" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH20" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -2274,6 +2628,24 @@
       <c r="AB21" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AC21" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD21" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE21" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF21" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG21" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH21" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -2360,6 +2732,24 @@
       <c r="AB22" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AC22" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD22" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE22" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF22" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG22" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH22" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -2446,6 +2836,24 @@
       <c r="AB23" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AC23" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD23" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE23" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF23" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG23" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH23" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -2532,6 +2940,24 @@
       <c r="AB24" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC24" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD24" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE24" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF24" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG24" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH24" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -2618,6 +3044,24 @@
       <c r="AB25" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AC25" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD25" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE25" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF25" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG25" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH25" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -2704,6 +3148,24 @@
       <c r="AB26" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AC26" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD26" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE26" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF26" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG26" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH26" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -2790,6 +3252,24 @@
       <c r="AB27" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AC27" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD27" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE27" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF27" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG27" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH27" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -2876,6 +3356,24 @@
       <c r="AB28" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AC28" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD28" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE28" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF28" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG28" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH28" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -2962,6 +3460,24 @@
       <c r="AB29" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC29" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD29" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE29" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF29" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG29" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH29" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -3048,6 +3564,24 @@
       <c r="AB30" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC30" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD30" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE30" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF30" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG30" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH30" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -3134,6 +3668,24 @@
       <c r="AB31" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AC31" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD31" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE31" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF31" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG31" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH31" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -3220,6 +3772,24 @@
       <c r="AB32" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AC32" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD32" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE32" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF32" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG32" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH32" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -3306,6 +3876,24 @@
       <c r="AB33" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AC33" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD33" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE33" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF33" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG33" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH33" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -3392,6 +3980,24 @@
       <c r="AB34" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AC34" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD34" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE34" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF34" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG34" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH34" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -3478,6 +4084,24 @@
       <c r="AB35" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AC35" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD35" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE35" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF35" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG35" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH35" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -3564,6 +4188,24 @@
       <c r="AB36" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="AC36" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD36" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE36" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF36" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG36" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH36" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n"/>
@@ -3655,6 +4297,24 @@
       </c>
       <c r="AB38" s="24" t="n">
         <v>49</v>
+      </c>
+      <c r="AC38" s="24" t="n">
+        <v>35</v>
+      </c>
+      <c r="AD38" s="24" t="n">
+        <v>70</v>
+      </c>
+      <c r="AE38" s="24" t="n">
+        <v>68</v>
+      </c>
+      <c r="AF38" s="24" t="n">
+        <v>54</v>
+      </c>
+      <c r="AG38" s="24" t="n">
+        <v>73</v>
+      </c>
+      <c r="AH38" s="24" t="n">
+        <v>73</v>
       </c>
     </row>
     <row r="39">
@@ -7519,7 +8179,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1000"/>
+  <dimension ref="A1:AH1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -7676,6 +8336,36 @@
           <t>Gemini 3.1 Flash-Lite (minimal)</t>
         </is>
       </c>
+      <c r="AC2" s="23" t="inlineStr">
+        <is>
+          <t>Kanana-o 9.8B</t>
+        </is>
+      </c>
+      <c r="AD2" s="23" t="inlineStr">
+        <is>
+          <t>o1 (high)</t>
+        </is>
+      </c>
+      <c r="AE2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-4.1</t>
+        </is>
+      </c>
+      <c r="AF2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-4o</t>
+        </is>
+      </c>
+      <c r="AG2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash (high)</t>
+        </is>
+      </c>
+      <c r="AH2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash (minimal)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
@@ -7768,6 +8458,24 @@
       <c r="AB3" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AC3" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="n">
@@ -7862,6 +8570,24 @@
       <c r="AB4" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="AC4" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE4" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH4" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="n">
@@ -7954,6 +8680,24 @@
       <c r="AB5" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AC5" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH5" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="n">
@@ -8052,6 +8796,24 @@
       <c r="AB6" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AC6" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD6" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE6" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG6" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH6" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="n">
@@ -8153,6 +8915,24 @@
       </c>
       <c r="AB7" s="25" t="n">
         <v>5</v>
+      </c>
+      <c r="AC7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH7" s="24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -8254,6 +9034,26 @@
       <c r="AB8" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AC8" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AD8" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE8" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF8" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG8" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH8" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="n">
@@ -8352,6 +9152,26 @@
       <c r="AB9" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AC9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AD9" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE9" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF9" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG9" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH9" s="25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="n">
@@ -8450,6 +9270,26 @@
       <c r="AB10" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AD10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE10" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="n">
@@ -8548,6 +9388,24 @@
       <c r="AB11" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AC11" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF11" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH11" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="n">
@@ -8646,6 +9504,24 @@
       <c r="AB12" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AC12" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD12" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE12" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF12" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG12" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH12" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
@@ -8744,6 +9620,24 @@
       <c r="AB13" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AC13" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD13" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE13" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF13" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG13" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH13" s="25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="n">
@@ -8844,6 +9738,24 @@
       <c r="AB14" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AC14" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE14" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF14" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH14" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="n">
@@ -8948,6 +9860,24 @@
       <c r="AB15" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC15" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD15" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE15" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF15" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG15" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH15" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="n">
@@ -9050,6 +9980,24 @@
       <c r="AB16" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AC16" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD16" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE16" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG16" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH16" s="25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="n">
@@ -9152,6 +10100,24 @@
       <c r="AB17" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AC17" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD17" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE17" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF17" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG17" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH17" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n">
@@ -9252,6 +10218,26 @@
       <c r="AB18" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC18" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AD18" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE18" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH18" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="n">
@@ -9354,6 +10340,24 @@
       <c r="AB19" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC19" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD19" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE19" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF19" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG19" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH19" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="n">
@@ -9456,6 +10460,24 @@
       <c r="AB20" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AC20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD20" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE20" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF20" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG20" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH20" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="n">
@@ -9558,6 +10580,24 @@
       <c r="AB21" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AC21" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD21" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE21" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF21" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG21" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH21" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="n">
@@ -9660,6 +10700,24 @@
       <c r="AB22" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AC22" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD22" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE22" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF22" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG22" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH22" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="n"/>
@@ -9751,6 +10809,24 @@
       </c>
       <c r="AB24" s="24" t="n">
         <v>14</v>
+      </c>
+      <c r="AC24" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD24" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE24" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF24" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG24" s="24" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH24" s="24" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="25">
@@ -13671,7 +14747,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1000"/>
+  <dimension ref="A1:AH1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -13828,6 +14904,36 @@
           <t>Gemini 3.1 Flash-Lite (minimal)</t>
         </is>
       </c>
+      <c r="AC2" s="23" t="inlineStr">
+        <is>
+          <t>Kanana-o 9.8B</t>
+        </is>
+      </c>
+      <c r="AD2" s="23" t="inlineStr">
+        <is>
+          <t>o1 (high)</t>
+        </is>
+      </c>
+      <c r="AE2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-4.1</t>
+        </is>
+      </c>
+      <c r="AF2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-4o</t>
+        </is>
+      </c>
+      <c r="AG2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash (minimal)</t>
+        </is>
+      </c>
+      <c r="AH2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
@@ -13924,6 +15030,24 @@
       <c r="AB3" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC3" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD3" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE3" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF3" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG3" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH3" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="n">
@@ -14020,6 +15144,24 @@
       <c r="AB4" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AC4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH4" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="n">
@@ -14118,6 +15260,24 @@
       <c r="AB5" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="AC5" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE5" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG5" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="n">
@@ -14216,6 +15376,24 @@
       <c r="AB6" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AC6" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF6" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="n">
@@ -14313,6 +15491,24 @@
       </c>
       <c r="AB7" s="25" t="n">
         <v>5</v>
+      </c>
+      <c r="AC7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF7" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH7" s="24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -14414,6 +15610,24 @@
       <c r="AB8" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AC8" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD8" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE8" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF8" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG8" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH8" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="n">
@@ -14512,6 +15726,24 @@
       <c r="AB9" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AC9" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD9" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE9" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF9" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG9" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH9" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="n">
@@ -14612,6 +15844,24 @@
       <c r="AB10" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AC10" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD10" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE10" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG10" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="n">
@@ -14714,6 +15964,24 @@
       <c r="AB11" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AC11" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD11" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE11" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF11" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG11" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH11" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="n">
@@ -14814,6 +16082,24 @@
       <c r="AB12" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AC12" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD12" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE12" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF12" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG12" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH12" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
@@ -14918,6 +16204,24 @@
       <c r="AB13" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AC13" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD13" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE13" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF13" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG13" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH13" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="n">
@@ -15020,6 +16324,24 @@
       <c r="AB14" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="AC14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD14" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE14" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF14" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG14" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH14" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="n">
@@ -15122,6 +16444,24 @@
       <c r="AB15" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AC15" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD15" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE15" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF15" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG15" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH15" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="n">
@@ -15224,6 +16564,24 @@
       <c r="AB16" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="AC16" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD16" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE16" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF16" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG16" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH16" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="n">
@@ -15326,6 +16684,24 @@
       <c r="AB17" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AC17" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD17" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE17" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF17" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG17" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH17" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n">
@@ -15430,6 +16806,26 @@
       <c r="AB18" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AC18" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD18" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE18" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF18" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AG18" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH18" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="n">
@@ -15532,6 +16928,26 @@
       <c r="AB19" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC19" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD19" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE19" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF19" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AG19" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH19" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="n">
@@ -15636,6 +17052,26 @@
       <c r="AB20" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AC20" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD20" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE20" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF20" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AG20" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH20" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="n">
@@ -15740,6 +17176,28 @@
       <c r="AB21" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="AC21" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AD21" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE21" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF21" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AG21" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH21" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="n">
@@ -15844,6 +17302,28 @@
       <c r="AB22" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AC22" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AD22" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE22" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF22" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AG22" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH22" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="n"/>
@@ -15935,6 +17415,24 @@
       </c>
       <c r="AB24" s="24" t="n">
         <v>7</v>
+      </c>
+      <c r="AC24" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD24" s="24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE24" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF24" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG24" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH24" s="24" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="25">
@@ -19855,7 +21353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1000"/>
+  <dimension ref="A1:AH1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -20012,6 +21510,36 @@
           <t>Gemini 3.1 Flash-Lite (minimal)</t>
         </is>
       </c>
+      <c r="AC2" s="23" t="inlineStr">
+        <is>
+          <t>Kanana-o 9.8B</t>
+        </is>
+      </c>
+      <c r="AD2" s="23" t="inlineStr">
+        <is>
+          <t>o1 (high)</t>
+        </is>
+      </c>
+      <c r="AE2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-4.1</t>
+        </is>
+      </c>
+      <c r="AF2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-4o</t>
+        </is>
+      </c>
+      <c r="AG2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash (minimal)</t>
+        </is>
+      </c>
+      <c r="AH2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
@@ -20106,6 +21634,24 @@
       <c r="AB3" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC3" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD3" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE3" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF3" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG3" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH3" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="n">
@@ -20200,6 +21746,24 @@
       <c r="AB4" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AC4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH4" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="n">
@@ -20294,6 +21858,24 @@
       <c r="AB5" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AC5" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD5" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE5" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF5" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="n">
@@ -20388,6 +21970,24 @@
       <c r="AB6" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AC6" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH6" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="n">
@@ -20480,6 +22080,24 @@
         <v>4</v>
       </c>
       <c r="AB7" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH7" s="24" t="n">
         <v>4</v>
       </c>
     </row>
@@ -20576,6 +22194,24 @@
       <c r="AB8" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AC8" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG8" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH8" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="n">
@@ -20670,6 +22306,24 @@
       <c r="AB9" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AC9" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD9" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE9" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF9" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG9" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH9" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="n">
@@ -20764,6 +22418,24 @@
       <c r="AB10" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE10" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="n">
@@ -20860,6 +22532,24 @@
       <c r="AB11" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC11" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD11" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE11" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF11" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG11" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH11" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="n">
@@ -20954,6 +22644,24 @@
       <c r="AB12" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AC12" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH12" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
@@ -21050,6 +22758,24 @@
       <c r="AB13" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AC13" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD13" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE13" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG13" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH13" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="n">
@@ -21144,6 +22870,24 @@
       <c r="AB14" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AC14" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE14" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF14" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH14" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="n">
@@ -21240,6 +22984,24 @@
       <c r="AB15" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AC15" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD15" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE15" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF15" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG15" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH15" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="n">
@@ -21338,6 +23100,24 @@
       <c r="AB16" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AC16" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD16" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE16" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF16" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG16" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH16" s="25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="n">
@@ -21436,6 +23216,24 @@
       <c r="AB17" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC17" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD17" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE17" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF17" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG17" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH17" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n">
@@ -21534,6 +23332,24 @@
       <c r="AB18" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AC18" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD18" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE18" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF18" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG18" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH18" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="n">
@@ -21632,6 +23448,24 @@
       <c r="AB19" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AC19" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD19" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE19" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF19" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG19" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH19" s="25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="n">
@@ -21730,6 +23564,24 @@
       <c r="AB20" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AC20" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD20" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE20" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF20" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG20" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH20" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="n">
@@ -21830,6 +23682,24 @@
       <c r="AB21" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AC21" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD21" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE21" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF21" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG21" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH21" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="n">
@@ -21928,6 +23798,24 @@
       <c r="AB22" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AC22" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD22" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE22" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF22" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG22" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH22" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="n"/>
@@ -22019,6 +23907,24 @@
       </c>
       <c r="AB24" s="24" t="n">
         <v>18</v>
+      </c>
+      <c r="AC24" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD24" s="24" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE24" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF24" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG24" s="24" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH24" s="24" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="25">
@@ -25939,7 +27845,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1000"/>
+  <dimension ref="A1:AH1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -26096,6 +28002,36 @@
           <t>Gemini 3.1 Flash-Lite (minimal)</t>
         </is>
       </c>
+      <c r="AC2" s="23" t="inlineStr">
+        <is>
+          <t>Kanana-o 9.8B</t>
+        </is>
+      </c>
+      <c r="AD2" s="23" t="inlineStr">
+        <is>
+          <t>o1 (high)</t>
+        </is>
+      </c>
+      <c r="AE2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-4o</t>
+        </is>
+      </c>
+      <c r="AF2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-4.1</t>
+        </is>
+      </c>
+      <c r="AG2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash (high)</t>
+        </is>
+      </c>
+      <c r="AH2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash (minimal)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
@@ -26184,6 +28120,24 @@
       <c r="AB3" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AC3" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD3" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE3" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF3" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG3" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH3" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="n">
@@ -26272,6 +28226,24 @@
       <c r="AB4" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AC4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH4" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="n">
@@ -26360,6 +28332,24 @@
       <c r="AB5" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AC5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="n">
@@ -26448,6 +28438,24 @@
       <c r="AB6" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="AC6" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD6" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE6" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF6" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG6" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH6" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="n">
@@ -26535,6 +28543,24 @@
       </c>
       <c r="AB7" s="25" t="n">
         <v>3</v>
+      </c>
+      <c r="AC7" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH7" s="25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -26626,6 +28652,24 @@
       <c r="AB8" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AC8" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG8" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH8" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="n">
@@ -26716,6 +28760,24 @@
       <c r="AB9" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AC9" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD9" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE9" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG9" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH9" s="25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="n">
@@ -26806,6 +28868,24 @@
       <c r="AB10" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC10" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD10" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE10" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF10" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG10" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="n">
@@ -26896,6 +28976,24 @@
       <c r="AB11" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AC11" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD11" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE11" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF11" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG11" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH11" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="n">
@@ -26988,6 +29086,24 @@
       <c r="AB12" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AC12" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD12" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE12" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG12" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH12" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
@@ -27078,6 +29194,24 @@
       <c r="AB13" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AC13" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD13" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE13" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF13" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG13" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH13" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="n">
@@ -27168,6 +29302,24 @@
       <c r="AB14" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AC14" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE14" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF14" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG14" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH14" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="n">
@@ -27258,6 +29410,26 @@
       <c r="AB15" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AC15" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD15" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE15" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF15" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AG15" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH15" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="n">
@@ -27348,6 +29520,24 @@
       <c r="AB16" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AC16" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD16" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE16" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF16" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG16" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH16" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="n">
@@ -27438,6 +29628,24 @@
       <c r="AB17" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC17" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD17" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE17" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF17" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG17" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH17" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n">
@@ -27528,6 +29736,24 @@
       <c r="AB18" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF18" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH18" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="n">
@@ -27618,6 +29844,24 @@
       <c r="AB19" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AC19" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD19" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE19" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF19" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG19" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH19" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="n">
@@ -27708,6 +29952,24 @@
       <c r="AB20" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AC20" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH20" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="n">
@@ -27798,6 +30060,24 @@
       <c r="AB21" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AC21" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD21" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE21" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF21" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG21" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH21" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="n">
@@ -27890,6 +30170,24 @@
       <c r="AB22" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AC22" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD22" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE22" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF22" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG22" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH22" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="n"/>
@@ -27981,6 +30279,24 @@
       </c>
       <c r="AB24" s="24" t="n">
         <v>23</v>
+      </c>
+      <c r="AC24" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD24" s="24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE24" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF24" s="24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG24" s="24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AH24" s="24" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="25">
@@ -31901,7 +34217,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1000"/>
+  <dimension ref="A1:AH1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -32060,6 +34376,36 @@
           <t>Gemini 3.1 Flash-Lite (minimal)</t>
         </is>
       </c>
+      <c r="AC2" s="23" t="inlineStr">
+        <is>
+          <t>Kanana-o 9.8B</t>
+        </is>
+      </c>
+      <c r="AD2" s="23" t="inlineStr">
+        <is>
+          <t>o1 (high)</t>
+        </is>
+      </c>
+      <c r="AE2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-4.1</t>
+        </is>
+      </c>
+      <c r="AF2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-4o</t>
+        </is>
+      </c>
+      <c r="AG2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash (high)</t>
+        </is>
+      </c>
+      <c r="AH2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash (minimal)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -32146,6 +34492,24 @@
       <c r="AB3" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AC3" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD3" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE3" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF3" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG3" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH3" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -32232,6 +34596,24 @@
       <c r="AB4" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH4" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -32318,6 +34700,24 @@
       <c r="AB5" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AC5" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH5" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -32404,6 +34804,24 @@
       <c r="AB6" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AC6" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF6" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -32490,6 +34908,24 @@
       <c r="AB7" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AC7" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE7" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH7" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -32576,6 +35012,24 @@
       <c r="AB8" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC8" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF8" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH8" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -32662,6 +35116,24 @@
       <c r="AB9" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AC9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH9" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -32748,6 +35220,24 @@
       <c r="AB10" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AC10" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD10" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE10" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF10" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG10" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH10" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -32834,6 +35324,24 @@
       <c r="AB11" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AC11" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH11" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -32920,6 +35428,24 @@
       <c r="AB12" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AC12" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD12" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE12" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF12" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG12" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH12" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -33006,6 +35532,24 @@
       <c r="AB13" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AC13" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD13" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE13" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG13" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH13" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
@@ -33097,6 +35641,24 @@
       </c>
       <c r="AB15" s="24" t="n">
         <v>15</v>
+      </c>
+      <c r="AC15" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD15" s="24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE15" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF15" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG15" s="24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH15" s="24" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -37053,7 +39615,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1000"/>
+  <dimension ref="A1:AH1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -37214,6 +39776,36 @@
           <t>Gemini 3.1 Flash-Lite (minimal)</t>
         </is>
       </c>
+      <c r="AC2" s="23" t="inlineStr">
+        <is>
+          <t>Kanana-o 9.8B</t>
+        </is>
+      </c>
+      <c r="AD2" s="23" t="inlineStr">
+        <is>
+          <t>o1 (high)</t>
+        </is>
+      </c>
+      <c r="AE2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-4.1</t>
+        </is>
+      </c>
+      <c r="AF2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-4o</t>
+        </is>
+      </c>
+      <c r="AG2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash (high)</t>
+        </is>
+      </c>
+      <c r="AH2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash (minimal)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -37300,6 +39892,24 @@
       <c r="AB3" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AC3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE3" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH3" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -37388,6 +39998,24 @@
       <c r="AB4" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AC4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE4" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG4" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH4" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -37476,6 +40104,24 @@
       <c r="AB5" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="AC5" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE5" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH5" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -37562,6 +40208,24 @@
       <c r="AB6" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AC6" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD6" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE6" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF6" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG6" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH6" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -37648,6 +40312,24 @@
       <c r="AB7" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AC7" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD7" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE7" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF7" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH7" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -37734,6 +40416,24 @@
       <c r="AB8" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="AC8" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH8" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -37820,6 +40520,26 @@
       <c r="AB9" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AC9" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AF9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH9" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -37906,6 +40626,24 @@
       <c r="AB10" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE10" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -37992,6 +40730,24 @@
       <c r="AB11" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AC11" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD11" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE11" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF11" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG11" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH11" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -38078,6 +40834,24 @@
       <c r="AB12" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AC12" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD12" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE12" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF12" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG12" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH12" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -38164,6 +40938,24 @@
       <c r="AB13" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AC13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH13" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
@@ -38255,6 +41047,24 @@
       </c>
       <c r="AB15" s="24" t="n">
         <v>11</v>
+      </c>
+      <c r="AC15" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD15" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE15" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF15" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG15" s="24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH15" s="24" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -42211,7 +45021,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB37"/>
+  <dimension ref="A1:AH37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -42368,6 +45178,36 @@
           <t>Gemini 3.1 Flash-Lite (minimal)</t>
         </is>
       </c>
+      <c r="AC2" s="23" t="inlineStr">
+        <is>
+          <t>Kanana-o 9.8B</t>
+        </is>
+      </c>
+      <c r="AD2" s="23" t="inlineStr">
+        <is>
+          <t>o1 (high)</t>
+        </is>
+      </c>
+      <c r="AE2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-4o</t>
+        </is>
+      </c>
+      <c r="AF2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-4.1</t>
+        </is>
+      </c>
+      <c r="AG2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash (high)</t>
+        </is>
+      </c>
+      <c r="AH2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash (minimal)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -42458,6 +45298,24 @@
       <c r="AB3" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AC3" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG3" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH3" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -42548,6 +45406,24 @@
       <c r="AB4" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AC4" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH4" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -42638,6 +45514,24 @@
       <c r="AB5" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC5" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD5" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE5" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF5" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG5" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH5" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -42728,6 +45622,24 @@
       <c r="AB6" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AC6" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH6" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -42817,6 +45729,24 @@
       </c>
       <c r="AB7" s="26" t="n">
         <v>3</v>
+      </c>
+      <c r="AC7" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE7" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF7" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG7" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH7" s="25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -42908,6 +45838,24 @@
       <c r="AB8" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AC8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH8" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -42998,6 +45946,24 @@
       <c r="AB9" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC9" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD9" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE9" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF9" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG9" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH9" s="25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -43088,6 +46054,24 @@
       <c r="AB10" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AC10" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD10" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE10" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF10" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG10" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH10" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -43178,6 +46162,26 @@
       <c r="AB11" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AC11" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD11" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE11" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AF11" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG11" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH11" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -43272,6 +46276,28 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AC12" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AD12" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE12" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AF12" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG12" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH12" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -43364,6 +46390,26 @@
       <c r="AB13" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="AC13" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE13" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AF13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH13" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -43456,6 +46502,26 @@
       <c r="AB14" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AC14" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE14" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AF14" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH14" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -43548,6 +46614,26 @@
       <c r="AB15" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC15" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD15" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE15" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AF15" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG15" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH15" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -43644,6 +46730,26 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AC16" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD16" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE16" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AF16" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG16" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH16" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -43742,6 +46848,26 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AC17" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD17" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE17" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AF17" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG17" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH17" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -43834,6 +46960,26 @@
       <c r="AB18" s="26" t="n">
         <v>9</v>
       </c>
+      <c r="AC18" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD18" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE18" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AF18" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG18" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH18" s="25" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -43926,6 +47072,26 @@
       <c r="AB19" s="26" t="n">
         <v>16</v>
       </c>
+      <c r="AC19" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD19" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE19" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AF19" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG19" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH19" s="24" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -44022,6 +47188,26 @@
       <c r="AB20" s="26" t="n">
         <v>12</v>
       </c>
+      <c r="AC20" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD20" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE20" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AF20" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG20" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH20" s="24" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -44116,6 +47302,26 @@
       <c r="AB21" s="26" t="n">
         <v>15</v>
       </c>
+      <c r="AC21" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD21" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE21" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AF21" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG21" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH21" s="25" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -44216,6 +47422,28 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AC22" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AD22" s="24" t="n">
+        <v>130</v>
+      </c>
+      <c r="AE22" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AF22" s="25" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG22" s="24" t="n">
+        <v>130</v>
+      </c>
+      <c r="AH22" s="25" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -44316,6 +47544,30 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AC23" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AD23" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AE23" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AF23" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG23" s="25" t="n">
+        <v>50</v>
+      </c>
+      <c r="AH23" s="25" t="n">
+        <v>-12</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -44418,6 +47670,30 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AC24" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AD24" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AE24" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AF24" s="25" t="n">
+        <v>141</v>
+      </c>
+      <c r="AG24" s="24" t="n">
+        <v>457</v>
+      </c>
+      <c r="AH24" s="25" t="n">
+        <v>231</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n"/>
@@ -44509,6 +47785,24 @@
       </c>
       <c r="AB26" s="24" t="n">
         <v>46</v>
+      </c>
+      <c r="AC26" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD26" s="24" t="n">
+        <v>62</v>
+      </c>
+      <c r="AE26" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF26" s="24" t="n">
+        <v>39</v>
+      </c>
+      <c r="AG26" s="24" t="n">
+        <v>70</v>
+      </c>
+      <c r="AH26" s="24" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="27">
@@ -44569,7 +47863,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB37"/>
+  <dimension ref="A1:AH37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -44726,6 +48020,36 @@
           <t>Gemini 3.1 Flash-Lite (minimal)</t>
         </is>
       </c>
+      <c r="AC2" s="23" t="inlineStr">
+        <is>
+          <t>Kanana-o 9.8B</t>
+        </is>
+      </c>
+      <c r="AD2" s="23" t="inlineStr">
+        <is>
+          <t>o1 (high)</t>
+        </is>
+      </c>
+      <c r="AE2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-4.1</t>
+        </is>
+      </c>
+      <c r="AF2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-4o</t>
+        </is>
+      </c>
+      <c r="AG2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash (high)</t>
+        </is>
+      </c>
+      <c r="AH2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash (minimal)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -44812,6 +48136,24 @@
       <c r="AB3" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AC3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -44898,6 +48240,24 @@
       <c r="AB4" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AC4" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH4" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -44984,6 +48344,26 @@
       <c r="AB5" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AC5" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AD5" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE5" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF5" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG5" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH5" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -45070,6 +48450,24 @@
       <c r="AB6" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF6" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH6" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -45158,6 +48556,24 @@
       <c r="AB7" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AC7" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE7" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF7" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH7" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -45248,6 +48664,26 @@
       <c r="AB8" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AC8" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF8" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AG8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH8" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -45338,6 +48774,26 @@
       <c r="AB9" s="26" t="n">
         <v>977</v>
       </c>
+      <c r="AC9" s="25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD9" s="24" t="n">
+        <v>977</v>
+      </c>
+      <c r="AE9" s="24" t="n">
+        <v>977</v>
+      </c>
+      <c r="AF9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AG9" s="24" t="n">
+        <v>977</v>
+      </c>
+      <c r="AH9" s="24" t="n">
+        <v>977</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -45430,6 +48886,28 @@
       <c r="AB10" s="25" t="n">
         <v>30</v>
       </c>
+      <c r="AC10" s="25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD10" s="24" t="n">
+        <v>262</v>
+      </c>
+      <c r="AE10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AF10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AG10" s="24" t="n">
+        <v>262</v>
+      </c>
+      <c r="AH10" s="25" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -45521,6 +48999,24 @@
       </c>
       <c r="AB12" s="24" t="n">
         <v>22</v>
+      </c>
+      <c r="AC12" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD12" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE12" s="24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF12" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG12" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH12" s="24" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -45633,7 +49129,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1000"/>
+  <dimension ref="A1:AH1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -45792,6 +49288,36 @@
           <t>Gemini 3.1 Flash-Lite (minimal)</t>
         </is>
       </c>
+      <c r="AC2" s="23" t="inlineStr">
+        <is>
+          <t>Kanana-o 9.8B</t>
+        </is>
+      </c>
+      <c r="AD2" s="23" t="inlineStr">
+        <is>
+          <t>o1 (high)</t>
+        </is>
+      </c>
+      <c r="AE2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-4o</t>
+        </is>
+      </c>
+      <c r="AF2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-4.1</t>
+        </is>
+      </c>
+      <c r="AG2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash (minimal)</t>
+        </is>
+      </c>
+      <c r="AH2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -45880,6 +49406,24 @@
       <c r="AB3" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AC3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -45968,6 +49512,24 @@
       <c r="AB4" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AC4" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE4" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH4" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -46056,6 +49618,24 @@
       <c r="AB5" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AC5" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH5" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -46144,6 +49724,24 @@
       <c r="AB6" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AC6" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -46232,6 +49830,24 @@
       <c r="AB7" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AC7" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE7" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH7" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -46320,6 +49936,24 @@
       <c r="AB8" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE8" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF8" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH8" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -46408,6 +50042,24 @@
       <c r="AB9" s="25" t="n">
         <v>7</v>
       </c>
+      <c r="AC9" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD9" s="24" t="n">
+        <v>97</v>
+      </c>
+      <c r="AE9" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF9" s="25" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG9" s="25" t="n">
+        <v>751</v>
+      </c>
+      <c r="AH9" s="24" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -46500,6 +50152,26 @@
       <c r="AB10" s="25" t="n">
         <v>0</v>
       </c>
+      <c r="AC10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AF10" s="25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG10" s="25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH10" s="25" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -46591,6 +50263,24 @@
       </c>
       <c r="AB12" s="24" t="n">
         <v>12</v>
+      </c>
+      <c r="AC12" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD12" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE12" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF12" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG12" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH12" s="24" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -50559,7 +54249,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB37"/>
+  <dimension ref="A1:AH37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -50716,6 +54406,36 @@
           <t>Gemini 3.1 Flash-Lite (minimal)</t>
         </is>
       </c>
+      <c r="AC2" s="23" t="inlineStr">
+        <is>
+          <t>Kanana-o 9.8B</t>
+        </is>
+      </c>
+      <c r="AD2" s="23" t="inlineStr">
+        <is>
+          <t>o1 (high)</t>
+        </is>
+      </c>
+      <c r="AE2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-4.1</t>
+        </is>
+      </c>
+      <c r="AF2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-4o</t>
+        </is>
+      </c>
+      <c r="AG2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash (minimal)</t>
+        </is>
+      </c>
+      <c r="AH2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -50802,6 +54522,24 @@
       <c r="AB3" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AC3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -50888,6 +54626,24 @@
       <c r="AB4" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AC4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH4" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -50974,6 +54730,26 @@
       <c r="AB5" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="AC5" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AD5" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE5" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF5" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG5" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH5" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -51060,6 +54836,24 @@
       <c r="AB6" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AC6" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD6" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE6" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF6" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG6" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH6" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -51146,6 +54940,26 @@
       <c r="AB7" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AC7" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AD7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG7" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH7" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -51232,6 +55046,24 @@
       <c r="AB8" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AC8" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD8" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE8" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF8" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG8" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH8" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -51318,6 +55150,26 @@
       <c r="AB9" s="25" t="n">
         <v>256</v>
       </c>
+      <c r="AC9" s="25" t="n">
+        <v>78</v>
+      </c>
+      <c r="AD9" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="AE9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AF9" s="25" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG9" s="25" t="n">
+        <v>169</v>
+      </c>
+      <c r="AH9" s="24" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -51404,6 +55256,24 @@
       <c r="AB10" s="25" t="n">
         <v>197</v>
       </c>
+      <c r="AC10" s="25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD10" s="24" t="n">
+        <v>221</v>
+      </c>
+      <c r="AE10" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF10" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG10" s="25" t="n">
+        <v>207</v>
+      </c>
+      <c r="AH10" s="24" t="n">
+        <v>221</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -51495,6 +55365,24 @@
       </c>
       <c r="AB12" s="24" t="n">
         <v>10</v>
+      </c>
+      <c r="AC12" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD12" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE12" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF12" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG12" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH12" s="24" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="13">
@@ -51607,7 +55495,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1000"/>
+  <dimension ref="A1:AH1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -51767,6 +55655,36 @@
           <t>Gemini 3.1 Flash-Lite (minimal)</t>
         </is>
       </c>
+      <c r="AC2" s="23" t="inlineStr">
+        <is>
+          <t>Kanana-o 9.8B</t>
+        </is>
+      </c>
+      <c r="AD2" s="23" t="inlineStr">
+        <is>
+          <t>o1 (high)</t>
+        </is>
+      </c>
+      <c r="AE2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-4o</t>
+        </is>
+      </c>
+      <c r="AF2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-4.1</t>
+        </is>
+      </c>
+      <c r="AG2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash (minimal)</t>
+        </is>
+      </c>
+      <c r="AH2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -51853,6 +55771,24 @@
       <c r="AB3" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AC3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -51939,6 +55875,24 @@
       <c r="AB4" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AC4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH4" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -52025,6 +55979,24 @@
       <c r="AB5" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AC5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -52113,6 +56085,24 @@
       <c r="AB6" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH6" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -52197,6 +56187,24 @@
         <v>1</v>
       </c>
       <c r="AB7" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH7" s="24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -52285,6 +56293,24 @@
       <c r="AB8" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AC8" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE8" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF8" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG8" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH8" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -52371,6 +56397,24 @@
       <c r="AB9" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AC9" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD9" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE9" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG9" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH9" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -52457,6 +56501,24 @@
       <c r="AB10" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -52543,6 +56605,24 @@
       <c r="AB11" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AC11" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD11" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE11" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF11" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG11" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH11" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -52629,6 +56709,24 @@
       <c r="AB12" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AC12" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD12" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE12" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF12" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG12" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH12" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -52715,6 +56813,24 @@
       <c r="AB13" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AC13" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD13" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE13" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG13" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH13" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -52801,6 +56917,24 @@
       <c r="AB14" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AC14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH14" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -52887,6 +57021,24 @@
       <c r="AB15" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AC15" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD15" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE15" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF15" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG15" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH15" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -52973,6 +57125,24 @@
       <c r="AB16" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AC16" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD16" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE16" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF16" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG16" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH16" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -53059,6 +57229,24 @@
       <c r="AB17" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AC17" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD17" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE17" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF17" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG17" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH17" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -53145,6 +57333,24 @@
       <c r="AB18" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AC18" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD18" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE18" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF18" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG18" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH18" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -53231,6 +57437,24 @@
       <c r="AB19" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC19" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD19" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE19" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF19" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG19" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH19" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -53317,6 +57541,24 @@
       <c r="AB20" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AC20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH20" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -53403,6 +57645,24 @@
       <c r="AB21" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AC21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH21" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -53489,6 +57749,24 @@
       <c r="AB22" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AC22" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD22" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE22" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF22" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG22" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH22" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -53575,6 +57853,24 @@
       <c r="AB23" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AC23" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD23" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE23" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF23" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG23" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH23" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -53661,6 +57957,24 @@
       <c r="AB24" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AC24" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD24" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE24" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF24" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG24" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH24" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -53747,6 +58061,24 @@
       <c r="AB25" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AC25" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD25" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE25" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF25" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG25" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH25" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -53833,6 +58165,24 @@
       <c r="AB26" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AC26" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD26" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE26" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF26" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG26" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH26" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -53921,6 +58271,24 @@
       <c r="AB27" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AC27" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD27" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE27" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF27" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG27" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH27" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -54007,6 +58375,24 @@
       <c r="AB28" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AC28" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD28" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE28" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF28" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG28" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH28" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -54093,6 +58479,24 @@
       <c r="AB29" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AC29" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD29" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE29" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF29" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG29" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH29" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -54179,6 +58583,24 @@
       <c r="AB30" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AC30" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD30" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE30" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF30" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG30" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH30" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -54265,6 +58687,24 @@
       <c r="AB31" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AC31" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD31" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE31" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF31" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG31" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH31" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -54351,6 +58791,24 @@
       <c r="AB32" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC32" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD32" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE32" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF32" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG32" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH32" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -54439,6 +58897,24 @@
       <c r="AB33" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AC33" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD33" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE33" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF33" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG33" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH33" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -54527,6 +59003,24 @@
       <c r="AB34" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC34" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD34" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE34" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF34" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG34" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH34" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -54615,6 +59109,24 @@
       <c r="AB35" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AC35" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD35" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE35" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF35" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG35" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH35" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -54703,6 +59215,24 @@
       <c r="AB36" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AC36" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD36" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE36" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF36" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG36" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH36" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -54791,6 +59321,24 @@
       <c r="AB37" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AC37" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD37" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE37" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF37" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG37" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH37" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -54879,6 +59427,24 @@
       <c r="AB38" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AC38" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD38" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE38" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF38" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG38" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH38" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -54967,6 +59533,24 @@
       <c r="AB39" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC39" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD39" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE39" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF39" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG39" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH39" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -55055,6 +59639,24 @@
       <c r="AB40" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AC40" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD40" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE40" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF40" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG40" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH40" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -55143,6 +59745,24 @@
       <c r="AB41" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="AC41" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD41" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE41" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF41" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG41" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH41" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -55233,6 +59853,24 @@
       <c r="AB42" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AC42" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD42" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE42" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF42" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG42" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH42" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -55321,6 +59959,24 @@
       <c r="AB43" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AC43" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD43" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE43" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF43" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG43" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH43" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -55409,6 +60065,24 @@
       <c r="AB44" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC44" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD44" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE44" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF44" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG44" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH44" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -55497,6 +60171,24 @@
       <c r="AB45" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC45" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD45" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE45" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF45" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG45" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH45" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -55585,6 +60277,24 @@
       <c r="AB46" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AC46" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD46" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE46" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF46" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG46" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH46" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -55673,6 +60383,24 @@
       <c r="AB47" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC47" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD47" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE47" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF47" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG47" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH47" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n"/>
@@ -55764,6 +60492,24 @@
       </c>
       <c r="AB49" s="24" t="n">
         <v>91</v>
+      </c>
+      <c r="AC49" s="24" t="n">
+        <v>80</v>
+      </c>
+      <c r="AD49" s="24" t="n">
+        <v>92</v>
+      </c>
+      <c r="AE49" s="24" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF49" s="24" t="n">
+        <v>93</v>
+      </c>
+      <c r="AG49" s="24" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH49" s="24" t="n">
+        <v>97</v>
       </c>
     </row>
     <row r="50">
@@ -59584,7 +64330,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1000"/>
+  <dimension ref="A1:AH1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -59745,6 +64491,36 @@
           <t>Gemini 3.1 Flash-Lite (minimal)</t>
         </is>
       </c>
+      <c r="AC2" s="23" t="inlineStr">
+        <is>
+          <t>Kanana-o 9.8B</t>
+        </is>
+      </c>
+      <c r="AD2" s="23" t="inlineStr">
+        <is>
+          <t>o1 (high)</t>
+        </is>
+      </c>
+      <c r="AE2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-4o</t>
+        </is>
+      </c>
+      <c r="AF2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-4.1</t>
+        </is>
+      </c>
+      <c r="AG2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash (high)</t>
+        </is>
+      </c>
+      <c r="AH2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 3 Flash (minimal)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -59831,6 +64607,24 @@
       <c r="AB3" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AC3" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -59917,6 +64711,24 @@
       <c r="AB4" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AC4" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD4" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE4" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF4" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG4" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH4" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -60003,6 +64815,24 @@
       <c r="AB5" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AC5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -60089,6 +64919,24 @@
       <c r="AB6" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH6" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -60173,6 +65021,24 @@
         <v>2</v>
       </c>
       <c r="AB7" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC7" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH7" s="24" t="n">
         <v>2</v>
       </c>
     </row>
@@ -60261,6 +65127,24 @@
       <c r="AB8" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH8" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -60347,6 +65231,24 @@
       <c r="AB9" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AC9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH9" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -60433,6 +65335,24 @@
       <c r="AB10" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -60519,6 +65439,24 @@
       <c r="AB11" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AC11" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH11" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -60605,6 +65543,24 @@
       <c r="AB12" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AC12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH12" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -60691,6 +65647,24 @@
       <c r="AB13" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AC13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH13" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -60777,6 +65751,24 @@
       <c r="AB14" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AC14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH14" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -60863,6 +65855,24 @@
       <c r="AB15" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AC15" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD15" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE15" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF15" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG15" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH15" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -60949,6 +65959,24 @@
       <c r="AB16" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC16" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD16" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE16" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF16" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG16" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH16" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -61035,6 +66063,24 @@
       <c r="AB17" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AC17" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD17" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE17" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF17" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG17" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH17" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -61121,6 +66167,24 @@
       <c r="AB18" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AC18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH18" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -61207,6 +66271,24 @@
       <c r="AB19" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AC19" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD19" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE19" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF19" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG19" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH19" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -61293,6 +66375,24 @@
       <c r="AB20" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AC20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH20" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -61379,6 +66479,24 @@
       <c r="AB21" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AC21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH21" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -61465,6 +66583,24 @@
       <c r="AB22" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AC22" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD22" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE22" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF22" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG22" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH22" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n"/>
@@ -61556,6 +66692,24 @@
       </c>
       <c r="AB24" s="24" t="n">
         <v>47</v>
+      </c>
+      <c r="AC24" s="24" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD24" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AE24" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF24" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG24" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AH24" s="24" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="25">

--- a/2026 수능 LLM 풀이 hard.xlsx
+++ b/2026 수능 LLM 풀이 hard.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1000"/>
+  <dimension ref="A1:AP1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -670,6 +670,46 @@
           <t>Gemini 3 Flash (high)</t>
         </is>
       </c>
+      <c r="AI2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.3 (high)</t>
+        </is>
+      </c>
+      <c r="AJ2" s="23" t="inlineStr">
+        <is>
+          <t>GLM-5.2 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AK2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.3 (none)</t>
+        </is>
+      </c>
+      <c r="AL2" s="23" t="inlineStr">
+        <is>
+          <t>MiniMax M3 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AM2" s="23" t="inlineStr">
+        <is>
+          <t>MiniMax M3 (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AN2" s="23" t="inlineStr">
+        <is>
+          <t>GLM-5.2 (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AO2" s="23" t="inlineStr">
+        <is>
+          <t>Solar Pro 3 (high)</t>
+        </is>
+      </c>
+      <c r="AP2" s="23" t="inlineStr">
+        <is>
+          <t>Solar Pro 3 (low)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -774,6 +814,30 @@
       <c r="AH3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP3" s="26" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -878,6 +942,30 @@
       <c r="AH4" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI4" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ4" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK4" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL4" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM4" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN4" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO4" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP4" s="26" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -982,6 +1070,30 @@
       <c r="AH5" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI5" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ5" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK5" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL5" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM5" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN5" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO5" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP5" s="26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1086,6 +1198,32 @@
       <c r="AH6" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AI6" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ6" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK6" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL6" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM6" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN6" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP6" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -1189,6 +1327,32 @@
       </c>
       <c r="AH7" s="24" t="n">
         <v>4</v>
+      </c>
+      <c r="AI7" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ7" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK7" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL7" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM7" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN7" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO7" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP7" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1294,6 +1458,32 @@
       <c r="AH8" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI8" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ8" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK8" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL8" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM8" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN8" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO8" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP8" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -1398,6 +1588,32 @@
       <c r="AH9" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI9" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ9" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK9" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL9" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM9" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN9" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO9" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -1502,6 +1718,32 @@
       <c r="AH10" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI10" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ10" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK10" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL10" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM10" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN10" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO10" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -1606,6 +1848,32 @@
       <c r="AH11" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI11" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ11" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK11" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL11" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM11" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN11" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO11" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP11" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -1710,6 +1978,30 @@
       <c r="AH12" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI12" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ12" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK12" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL12" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM12" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN12" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO12" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP12" s="26" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -1814,6 +2106,32 @@
       <c r="AH13" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO13" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP13" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -1918,6 +2236,30 @@
       <c r="AH14" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AI14" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ14" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK14" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL14" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM14" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN14" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO14" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP14" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -2022,6 +2364,30 @@
       <c r="AH15" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AI15" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ15" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK15" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL15" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM15" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN15" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO15" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP15" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -2126,6 +2492,30 @@
       <c r="AH16" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI16" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ16" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK16" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL16" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM16" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN16" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO16" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP16" s="26" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -2230,6 +2620,30 @@
       <c r="AH17" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AI17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP17" s="26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -2334,6 +2748,30 @@
       <c r="AH18" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI18" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ18" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK18" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL18" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM18" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN18" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO18" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP18" s="26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -2438,6 +2876,30 @@
       <c r="AH19" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI19" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ19" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK19" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL19" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM19" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN19" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO19" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP19" s="26" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -2542,6 +3004,30 @@
       <c r="AH20" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI20" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ20" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK20" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL20" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM20" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN20" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO20" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP20" s="26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -2646,6 +3132,30 @@
       <c r="AH21" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI21" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ21" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK21" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL21" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM21" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN21" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO21" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP21" s="26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -2750,6 +3260,30 @@
       <c r="AH22" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI22" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ22" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK22" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL22" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM22" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN22" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO22" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP22" s="26" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -2854,6 +3388,30 @@
       <c r="AH23" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI23" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ23" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK23" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL23" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM23" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN23" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO23" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP23" s="26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -2958,6 +3516,30 @@
       <c r="AH24" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI24" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ24" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK24" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL24" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM24" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN24" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO24" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP24" s="26" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -3062,6 +3644,30 @@
       <c r="AH25" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AI25" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ25" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK25" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL25" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM25" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN25" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO25" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP25" s="26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -3166,6 +3772,30 @@
       <c r="AH26" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI26" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ26" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK26" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL26" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM26" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN26" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO26" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP26" s="26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -3270,6 +3900,30 @@
       <c r="AH27" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI27" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ27" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK27" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL27" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM27" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN27" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO27" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP27" s="26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -3374,6 +4028,30 @@
       <c r="AH28" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI28" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ28" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK28" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL28" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM28" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN28" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO28" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP28" s="26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -3478,6 +4156,32 @@
       <c r="AH29" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI29" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ29" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK29" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL29" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM29" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN29" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO29" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AP29" s="26" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -3582,6 +4286,32 @@
       <c r="AH30" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI30" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ30" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK30" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL30" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM30" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN30" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO30" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AP30" s="26" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -3686,6 +4416,32 @@
       <c r="AH31" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AI31" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ31" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK31" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL31" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM31" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN31" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO31" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AP31" s="26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -3790,6 +4546,32 @@
       <c r="AH32" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI32" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ32" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK32" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL32" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM32" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN32" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO32" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AP32" s="26" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -3894,6 +4676,32 @@
       <c r="AH33" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI33" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ33" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK33" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL33" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM33" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN33" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO33" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AP33" s="26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -3998,6 +4806,32 @@
       <c r="AH34" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI34" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ34" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK34" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL34" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM34" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN34" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO34" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AP34" s="26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -4102,6 +4936,32 @@
       <c r="AH35" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AI35" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ35" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK35" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL35" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM35" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN35" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO35" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AP35" s="26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -4206,6 +5066,32 @@
       <c r="AH36" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AI36" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ36" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK36" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL36" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM36" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN36" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO36" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AP36" s="26" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n"/>
@@ -4315,6 +5201,30 @@
       </c>
       <c r="AH38" s="24" t="n">
         <v>73</v>
+      </c>
+      <c r="AI38" s="24" t="n">
+        <v>59</v>
+      </c>
+      <c r="AJ38" s="24" t="n">
+        <v>73</v>
+      </c>
+      <c r="AK38" s="24" t="n">
+        <v>58</v>
+      </c>
+      <c r="AL38" s="24" t="n">
+        <v>68</v>
+      </c>
+      <c r="AM38" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN38" s="24" t="n">
+        <v>73</v>
+      </c>
+      <c r="AO38" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP38" s="24" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="39">
@@ -8179,7 +9089,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1000"/>
+  <dimension ref="A1:AP1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -8366,6 +9276,46 @@
           <t>Gemini 3 Flash (minimal)</t>
         </is>
       </c>
+      <c r="AI2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.3 (high)</t>
+        </is>
+      </c>
+      <c r="AJ2" s="23" t="inlineStr">
+        <is>
+          <t>MiniMax M3 (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AK2" s="23" t="inlineStr">
+        <is>
+          <t>MiniMax M3 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AL2" s="23" t="inlineStr">
+        <is>
+          <t>GLM-5.2 (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AM2" s="23" t="inlineStr">
+        <is>
+          <t>Solar Pro 3 (high)</t>
+        </is>
+      </c>
+      <c r="AN2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.3 (none)</t>
+        </is>
+      </c>
+      <c r="AO2" s="23" t="inlineStr">
+        <is>
+          <t>GLM-5.2 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AP2" s="23" t="inlineStr">
+        <is>
+          <t>Solar Pro 3 (low)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
@@ -8476,6 +9426,30 @@
       <c r="AH3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ3" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL3" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN3" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO3" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP3" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="n">
@@ -8588,6 +9562,32 @@
       <c r="AH4" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AI4" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ4" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK4" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL4" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM4" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AN4" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP4" s="26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="n">
@@ -8698,6 +9698,30 @@
       <c r="AH5" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI5" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ5" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK5" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL5" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM5" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN5" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO5" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP5" s="25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="n">
@@ -8814,6 +9838,30 @@
       <c r="AH6" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AI6" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ6" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK6" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL6" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM6" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN6" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO6" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP6" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="n">
@@ -8932,6 +9980,30 @@
         <v>1</v>
       </c>
       <c r="AH7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI7" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ7" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK7" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL7" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM7" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN7" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP7" s="26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9054,6 +10126,32 @@
       <c r="AH8" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI8" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ8" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK8" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL8" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM8" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AN8" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO8" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP8" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="n">
@@ -9172,6 +10270,32 @@
       <c r="AH9" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="AI9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ9" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AN9" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP9" s="26" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="n">
@@ -9290,6 +10414,32 @@
       <c r="AH10" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI10" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ10" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK10" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL10" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AN10" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO10" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP10" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="n">
@@ -9406,6 +10556,32 @@
       <c r="AH11" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AI11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ11" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL11" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM11" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AN11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO11" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP11" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="n">
@@ -9522,6 +10698,32 @@
       <c r="AH12" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AI12" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ12" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK12" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL12" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM12" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AN12" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO12" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP12" s="26" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
@@ -9638,6 +10840,34 @@
       <c r="AH13" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="AI13" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ13" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK13" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL13" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM13" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AN13" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO13" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AP13" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="n">
@@ -9756,6 +10986,34 @@
       <c r="AH14" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AI14" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ14" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK14" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL14" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM14" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AN14" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO14" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AP14" s="26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="n">
@@ -9878,6 +11136,34 @@
       <c r="AH15" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AI15" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ15" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK15" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL15" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM15" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AN15" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO15" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AP15" s="26" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="n">
@@ -9998,6 +11284,34 @@
       <c r="AH16" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="AI16" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ16" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK16" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL16" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM16" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AN16" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO16" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AP16" s="26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="n">
@@ -10118,6 +11432,34 @@
       <c r="AH17" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AI17" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ17" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK17" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL17" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM17" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AN17" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO17" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AP17" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n">
@@ -10238,6 +11580,34 @@
       <c r="AH18" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI18" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ18" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK18" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL18" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM18" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AN18" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO18" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AP18" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="n">
@@ -10358,6 +11728,34 @@
       <c r="AH19" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AI19" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ19" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK19" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL19" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM19" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AN19" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO19" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AP19" s="26" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="n">
@@ -10478,6 +11876,34 @@
       <c r="AH20" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AI20" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ20" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK20" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL20" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM20" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AN20" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO20" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AP20" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="n">
@@ -10598,6 +12024,34 @@
       <c r="AH21" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AI21" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ21" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK21" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL21" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM21" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AN21" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO21" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AP21" s="25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="n">
@@ -10718,6 +12172,34 @@
       <c r="AH22" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AI22" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ22" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK22" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL22" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM22" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AN22" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO22" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AP22" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="n"/>
@@ -10827,6 +12309,30 @@
       </c>
       <c r="AH24" s="24" t="n">
         <v>17</v>
+      </c>
+      <c r="AI24" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ24" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK24" s="24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL24" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AM24" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN24" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO24" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP24" s="24" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="25">
@@ -14747,7 +16253,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1000"/>
+  <dimension ref="A1:AP1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -14934,6 +16440,46 @@
           <t>Gemini 3 Flash (high)</t>
         </is>
       </c>
+      <c r="AI2" s="23" t="inlineStr">
+        <is>
+          <t>MiniMax M3 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AJ2" s="23" t="inlineStr">
+        <is>
+          <t>Solar Pro 3 (low)</t>
+        </is>
+      </c>
+      <c r="AK2" s="23" t="inlineStr">
+        <is>
+          <t>MiniMax M3 (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AL2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.3 (none)</t>
+        </is>
+      </c>
+      <c r="AM2" s="23" t="inlineStr">
+        <is>
+          <t>GLM-5.2 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AN2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.3 (high)</t>
+        </is>
+      </c>
+      <c r="AO2" s="23" t="inlineStr">
+        <is>
+          <t>GLM-5.2 (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AP2" s="23" t="inlineStr">
+        <is>
+          <t>Solar Pro 3 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
@@ -15048,6 +16594,34 @@
       <c r="AH3" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI3" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ3" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AK3" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL3" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM3" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN3" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO3" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP3" s="26" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="n">
@@ -15162,6 +16736,34 @@
       <c r="AH4" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI4" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ4" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AK4" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL4" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM4" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN4" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO4" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP4" s="26" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="n">
@@ -15278,6 +16880,34 @@
       <c r="AH5" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI5" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ5" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AK5" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL5" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM5" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN5" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP5" s="26" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="n">
@@ -15394,6 +17024,34 @@
       <c r="AH6" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AI6" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ6" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AK6" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL6" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM6" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN6" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP6" s="26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="n">
@@ -15509,6 +17167,34 @@
       </c>
       <c r="AH7" s="24" t="n">
         <v>2</v>
+      </c>
+      <c r="AI7" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ7" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AK7" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL7" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM7" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN7" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO7" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP7" s="25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -15628,6 +17314,34 @@
       <c r="AH8" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI8" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ8" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AK8" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL8" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM8" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN8" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO8" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP8" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="n">
@@ -15744,6 +17458,36 @@
       <c r="AH9" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AK9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL9" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN9" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO9" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="n">
@@ -15862,6 +17606,36 @@
       <c r="AH10" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AK10" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL10" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM10" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN10" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO10" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="n">
@@ -15982,6 +17756,36 @@
       <c r="AH11" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AI11" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ11" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AK11" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL11" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM11" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN11" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO11" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP11" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="n">
@@ -16100,6 +17904,36 @@
       <c r="AH12" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AI12" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ12" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AK12" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL12" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM12" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN12" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO12" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP12" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
@@ -16222,6 +18056,36 @@
       <c r="AH13" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI13" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ13" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AK13" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL13" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM13" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN13" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO13" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP13" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="n">
@@ -16342,6 +18206,36 @@
       <c r="AH14" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI14" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ14" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AK14" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL14" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM14" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN14" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO14" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP14" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="n">
@@ -16462,6 +18356,36 @@
       <c r="AH15" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI15" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ15" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AK15" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL15" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM15" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN15" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO15" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP15" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="n">
@@ -16582,6 +18506,36 @@
       <c r="AH16" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI16" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ16" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AK16" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL16" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM16" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN16" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO16" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP16" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="n">
@@ -16702,6 +18656,36 @@
       <c r="AH17" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AI17" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ17" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AK17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN17" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP17" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n">
@@ -16826,6 +18810,36 @@
       <c r="AH18" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI18" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ18" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AK18" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL18" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM18" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN18" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO18" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP18" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="n">
@@ -16948,6 +18962,36 @@
       <c r="AH19" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI19" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ19" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AK19" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL19" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM19" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN19" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO19" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP19" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="n">
@@ -17072,6 +19116,36 @@
       <c r="AH20" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI20" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ20" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AK20" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL20" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM20" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN20" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO20" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP20" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="n">
@@ -17198,6 +19272,36 @@
       <c r="AH21" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI21" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ21" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AK21" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL21" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM21" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN21" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO21" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP21" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="n">
@@ -17324,6 +19428,34 @@
       <c r="AH22" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AI22" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ22" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK22" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL22" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM22" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN22" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO22" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP22" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="n"/>
@@ -17433,6 +19565,30 @@
       </c>
       <c r="AH24" s="24" t="n">
         <v>48</v>
+      </c>
+      <c r="AI24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL24" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AM24" s="24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AN24" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO24" s="24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP24" s="24" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="25">
@@ -21353,7 +23509,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1000"/>
+  <dimension ref="A1:AP1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -21540,6 +23696,46 @@
           <t>Gemini 3 Flash (high)</t>
         </is>
       </c>
+      <c r="AI2" s="23" t="inlineStr">
+        <is>
+          <t>MiniMax M3 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AJ2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.3 (high)</t>
+        </is>
+      </c>
+      <c r="AK2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.3 (none)</t>
+        </is>
+      </c>
+      <c r="AL2" s="23" t="inlineStr">
+        <is>
+          <t>GLM-5.2 (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AM2" s="23" t="inlineStr">
+        <is>
+          <t>GLM-5.2 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AN2" s="23" t="inlineStr">
+        <is>
+          <t>MiniMax M3 (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AO2" s="23" t="inlineStr">
+        <is>
+          <t>Solar Pro 3 (high)</t>
+        </is>
+      </c>
+      <c r="AP2" s="23" t="inlineStr">
+        <is>
+          <t>Solar Pro 3 (low)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
@@ -21652,6 +23848,32 @@
       <c r="AH3" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI3" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ3" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK3" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL3" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM3" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN3" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO3" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP3" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="n">
@@ -21764,6 +23986,32 @@
       <c r="AH4" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI4" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ4" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK4" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL4" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM4" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN4" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO4" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP4" s="26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="n">
@@ -21876,6 +24124,32 @@
       <c r="AH5" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AI5" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ5" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK5" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL5" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM5" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN5" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO5" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP5" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="n">
@@ -21988,6 +24262,32 @@
       <c r="AH6" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI6" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ6" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK6" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL6" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM6" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN6" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP6" s="26" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="n">
@@ -22099,6 +24399,34 @@
       </c>
       <c r="AH7" s="24" t="n">
         <v>4</v>
+      </c>
+      <c r="AI7" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ7" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK7" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL7" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM7" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN7" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO7" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP7" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -22212,6 +24540,34 @@
       <c r="AH8" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI8" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ8" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK8" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL8" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM8" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN8" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP8" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="n">
@@ -22324,6 +24680,32 @@
       <c r="AH9" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP9" s="26" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="n">
@@ -22436,6 +24818,32 @@
       <c r="AH10" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ10" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK10" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL10" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM10" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN10" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO10" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP10" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="n">
@@ -22550,6 +24958,34 @@
       <c r="AH11" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI11" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ11" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK11" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL11" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM11" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN11" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO11" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP11" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="n">
@@ -22662,6 +25098,34 @@
       <c r="AH12" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AI12" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ12" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK12" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL12" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM12" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN12" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO12" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP12" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
@@ -22776,6 +25240,34 @@
       <c r="AH13" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AI13" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ13" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK13" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL13" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM13" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN13" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO13" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP13" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="n">
@@ -22888,6 +25380,34 @@
       <c r="AH14" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI14" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ14" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK14" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL14" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM14" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN14" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO14" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP14" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="n">
@@ -23002,6 +25522,34 @@
       <c r="AH15" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AI15" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ15" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK15" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL15" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM15" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN15" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO15" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP15" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="n">
@@ -23118,6 +25666,34 @@
       <c r="AH16" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="AI16" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ16" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK16" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL16" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM16" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN16" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO16" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP16" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="n">
@@ -23234,6 +25810,34 @@
       <c r="AH17" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI17" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ17" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK17" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL17" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM17" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN17" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO17" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP17" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n">
@@ -23350,6 +25954,34 @@
       <c r="AH18" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AI18" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ18" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK18" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN18" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP18" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="n">
@@ -23466,6 +26098,34 @@
       <c r="AH19" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="AI19" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ19" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK19" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL19" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM19" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN19" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO19" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP19" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="n">
@@ -23582,6 +26242,34 @@
       <c r="AH20" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AI20" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ20" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK20" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL20" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM20" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN20" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO20" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP20" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="n">
@@ -23700,6 +26388,34 @@
       <c r="AH21" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI21" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ21" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK21" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL21" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM21" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN21" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO21" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP21" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="n">
@@ -23816,6 +26532,34 @@
       <c r="AH22" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI22" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ22" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK22" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL22" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM22" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN22" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO22" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP22" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="n"/>
@@ -23925,6 +26669,30 @@
       </c>
       <c r="AH24" s="24" t="n">
         <v>38</v>
+      </c>
+      <c r="AI24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK24" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL24" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AM24" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AN24" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO24" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP24" s="24" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="25">
@@ -27845,7 +30613,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1000"/>
+  <dimension ref="A1:AP1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -28032,6 +30800,46 @@
           <t>Gemini 3 Flash (minimal)</t>
         </is>
       </c>
+      <c r="AI2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.3 (high)</t>
+        </is>
+      </c>
+      <c r="AJ2" s="23" t="inlineStr">
+        <is>
+          <t>GLM-5.2 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AK2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.3 (none)</t>
+        </is>
+      </c>
+      <c r="AL2" s="23" t="inlineStr">
+        <is>
+          <t>GLM-5.2 (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AM2" s="23" t="inlineStr">
+        <is>
+          <t>MiniMax M3 (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AN2" s="23" t="inlineStr">
+        <is>
+          <t>Solar Pro 3 (low)</t>
+        </is>
+      </c>
+      <c r="AO2" s="23" t="inlineStr">
+        <is>
+          <t>Solar Pro 3 (high)</t>
+        </is>
+      </c>
+      <c r="AP2" s="23" t="inlineStr">
+        <is>
+          <t>MiniMax M3 (Thinking)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
@@ -28138,6 +30946,30 @@
       <c r="AH3" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI3" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ3" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK3" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL3" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM3" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN3" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO3" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP3" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="n">
@@ -28244,6 +31076,32 @@
       <c r="AH4" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI4" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ4" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK4" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL4" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM4" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN4" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AO4" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP4" s="26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="n">
@@ -28350,6 +31208,32 @@
       <c r="AH5" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AI5" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ5" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK5" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL5" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM5" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN5" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AO5" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP5" s="26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="n">
@@ -28456,6 +31340,32 @@
       <c r="AH6" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI6" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ6" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK6" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL6" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM6" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN6" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AO6" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP6" s="26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="n">
@@ -28561,6 +31471,32 @@
       </c>
       <c r="AH7" s="25" t="n">
         <v>2</v>
+      </c>
+      <c r="AI7" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ7" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK7" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL7" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM7" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN7" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AO7" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP7" s="26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -28670,6 +31606,32 @@
       <c r="AH8" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AI8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN8" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AO8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP8" s="26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="n">
@@ -28778,6 +31740,32 @@
       <c r="AH9" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="AI9" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ9" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK9" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL9" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM9" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AO9" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP9" s="25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="n">
@@ -28886,6 +31874,32 @@
       <c r="AH10" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI10" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ10" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK10" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL10" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM10" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AO10" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP10" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="n">
@@ -28994,6 +32008,32 @@
       <c r="AH11" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AI11" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ11" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK11" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL11" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM11" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN11" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AO11" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP11" s="26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="n">
@@ -29104,6 +32144,32 @@
       <c r="AH12" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI12" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ12" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK12" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL12" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM12" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN12" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AO12" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP12" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
@@ -29212,6 +32278,32 @@
       <c r="AH13" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI13" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ13" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK13" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL13" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM13" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN13" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AO13" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP13" s="25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="n">
@@ -29320,6 +32412,32 @@
       <c r="AH14" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AI14" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ14" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK14" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL14" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM14" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN14" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AO14" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP14" s="26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="n">
@@ -29430,6 +32548,32 @@
       <c r="AH15" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI15" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ15" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK15" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL15" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM15" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN15" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AO15" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP15" s="26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="n">
@@ -29538,6 +32682,32 @@
       <c r="AH16" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AI16" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ16" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK16" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL16" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM16" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN16" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AO16" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP16" s="26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="n">
@@ -29646,6 +32816,32 @@
       <c r="AH17" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AI17" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ17" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK17" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL17" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM17" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN17" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AO17" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP17" s="26" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n">
@@ -29754,6 +32950,32 @@
       <c r="AH18" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI18" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ18" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK18" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL18" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM18" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN18" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AO18" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP18" s="26" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="n">
@@ -29862,6 +33084,32 @@
       <c r="AH19" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AI19" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ19" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK19" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL19" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM19" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN19" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AO19" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP19" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="n">
@@ -29970,6 +33218,32 @@
       <c r="AH20" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI20" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ20" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK20" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL20" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM20" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN20" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AO20" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP20" s="26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="n">
@@ -30078,6 +33352,32 @@
       <c r="AH21" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI21" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ21" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK21" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL21" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM21" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN21" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AO21" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP21" s="26" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="n">
@@ -30188,6 +33488,32 @@
       <c r="AH22" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AI22" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ22" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK22" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL22" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM22" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN22" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AO22" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP22" s="26" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="n"/>
@@ -30297,6 +33623,30 @@
       </c>
       <c r="AH24" s="24" t="n">
         <v>31</v>
+      </c>
+      <c r="AI24" s="24" t="n">
+        <v>37</v>
+      </c>
+      <c r="AJ24" s="24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK24" s="24" t="n">
+        <v>31</v>
+      </c>
+      <c r="AL24" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AM24" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP24" s="24" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="25">
@@ -34217,7 +37567,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1000"/>
+  <dimension ref="A1:AP1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -34406,6 +37756,46 @@
           <t>Gemini 3 Flash (minimal)</t>
         </is>
       </c>
+      <c r="AI2" s="23" t="inlineStr">
+        <is>
+          <t>GLM-5.2 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AJ2" s="23" t="inlineStr">
+        <is>
+          <t>MiniMax M3 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AK2" s="23" t="inlineStr">
+        <is>
+          <t>MiniMax M3 (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AL2" s="23" t="inlineStr">
+        <is>
+          <t>GLM-5.2 (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AM2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.3 (high)</t>
+        </is>
+      </c>
+      <c r="AN2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.3 (none)</t>
+        </is>
+      </c>
+      <c r="AO2" s="23" t="inlineStr">
+        <is>
+          <t>Solar Pro 3 (high)</t>
+        </is>
+      </c>
+      <c r="AP2" s="23" t="inlineStr">
+        <is>
+          <t>Solar Pro 3 (low)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -34510,6 +37900,30 @@
       <c r="AH3" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI3" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ3" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK3" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL3" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM3" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN3" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO3" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP3" s="26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -34614,6 +38028,30 @@
       <c r="AH4" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI4" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ4" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK4" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL4" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM4" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN4" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO4" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP4" s="25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -34718,6 +38156,32 @@
       <c r="AH5" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AI5" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ5" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK5" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL5" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM5" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN5" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO5" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AP5" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -34822,6 +38286,32 @@
       <c r="AH6" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AI6" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ6" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK6" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL6" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM6" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN6" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO6" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AP6" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -34926,6 +38416,32 @@
       <c r="AH7" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI7" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ7" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK7" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL7" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM7" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN7" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO7" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AP7" s="26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -35030,6 +38546,32 @@
       <c r="AH8" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI8" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ8" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK8" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL8" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM8" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN8" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO8" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AP8" s="26" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -35134,6 +38676,32 @@
       <c r="AH9" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI9" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ9" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK9" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL9" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM9" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN9" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AP9" s="26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -35238,6 +38806,32 @@
       <c r="AH10" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI10" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ10" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK10" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL10" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM10" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN10" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AP10" s="26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -35342,6 +38936,32 @@
       <c r="AH11" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO11" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AP11" s="26" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -35446,6 +39066,32 @@
       <c r="AH12" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI12" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ12" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK12" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL12" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM12" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN12" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO12" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AP12" s="26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -35550,6 +39196,34 @@
       <c r="AH13" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI13" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ13" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK13" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL13" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM13" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN13" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO13" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AP13" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
@@ -35659,6 +39333,30 @@
       </c>
       <c r="AH15" s="24" t="n">
         <v>20</v>
+      </c>
+      <c r="AI15" s="24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ15" s="24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK15" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL15" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AM15" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AN15" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO15" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP15" s="24" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -39615,7 +43313,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1000"/>
+  <dimension ref="A1:AP1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -39806,6 +43504,46 @@
           <t>Gemini 3 Flash (minimal)</t>
         </is>
       </c>
+      <c r="AI2" s="23" t="inlineStr">
+        <is>
+          <t>Solar Pro 3 (low)</t>
+        </is>
+      </c>
+      <c r="AJ2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.3 (none)</t>
+        </is>
+      </c>
+      <c r="AK2" s="23" t="inlineStr">
+        <is>
+          <t>MiniMax M3 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AL2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.3 (high)</t>
+        </is>
+      </c>
+      <c r="AM2" s="23" t="inlineStr">
+        <is>
+          <t>GLM-5.2 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AN2" s="23" t="inlineStr">
+        <is>
+          <t>MiniMax M3 (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AO2" s="23" t="inlineStr">
+        <is>
+          <t>GLM-5.2 (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AP2" s="23" t="inlineStr">
+        <is>
+          <t>Solar Pro 3 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -39910,6 +43648,32 @@
       <c r="AH3" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AI3" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ3" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AK3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN3" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP3" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -40016,6 +43780,32 @@
       <c r="AH4" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AI4" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ4" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AK4" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL4" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM4" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN4" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO4" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP4" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -40122,6 +43912,34 @@
       <c r="AH5" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI5" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ5" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AK5" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL5" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM5" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN5" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO5" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP5" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -40226,6 +44044,34 @@
       <c r="AH6" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI6" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ6" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AK6" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL6" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM6" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN6" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO6" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP6" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -40330,6 +44176,34 @@
       <c r="AH7" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AI7" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ7" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AK7" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL7" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM7" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN7" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO7" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP7" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -40434,6 +44308,34 @@
       <c r="AH8" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI8" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ8" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AK8" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL8" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM8" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN8" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP8" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -40540,6 +44442,34 @@
       <c r="AH9" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI9" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AK9" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL9" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM9" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN9" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO9" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -40644,6 +44574,34 @@
       <c r="AH10" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI10" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AK10" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL10" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM10" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN10" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO10" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -40748,6 +44706,34 @@
       <c r="AH11" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI11" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ11" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AK11" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL11" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM11" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN11" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO11" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP11" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -40852,6 +44838,34 @@
       <c r="AH12" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI12" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ12" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AK12" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL12" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM12" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN12" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO12" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP12" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -40956,6 +44970,34 @@
       <c r="AH13" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ13" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AK13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP13" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
@@ -41065,6 +45107,30 @@
       </c>
       <c r="AH15" s="24" t="n">
         <v>19</v>
+      </c>
+      <c r="AI15" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ15" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL15" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AM15" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AN15" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO15" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP15" s="24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -45021,7 +49087,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH37"/>
+  <dimension ref="A1:AP37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -45208,6 +49274,46 @@
           <t>Gemini 3 Flash (minimal)</t>
         </is>
       </c>
+      <c r="AI2" s="23" t="inlineStr">
+        <is>
+          <t>MiniMax M3 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AJ2" s="23" t="inlineStr">
+        <is>
+          <t>GLM-5.2 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AK2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.3 (high)</t>
+        </is>
+      </c>
+      <c r="AL2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.3 (none)</t>
+        </is>
+      </c>
+      <c r="AM2" s="23" t="inlineStr">
+        <is>
+          <t>Solar Pro 3 (high)</t>
+        </is>
+      </c>
+      <c r="AN2" s="23" t="inlineStr">
+        <is>
+          <t>MiniMax M3 (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AO2" s="23" t="inlineStr">
+        <is>
+          <t>Solar Pro 3 (low)</t>
+        </is>
+      </c>
+      <c r="AP2" s="23" t="inlineStr">
+        <is>
+          <t>GLM-5.2 (Non-Thinking)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -45316,6 +49422,30 @@
       <c r="AH3" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AI3" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ3" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK3" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL3" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN3" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP3" s="26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -45424,6 +49554,30 @@
       <c r="AH4" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI4" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ4" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK4" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL4" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM4" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN4" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO4" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP4" s="26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -45532,6 +49686,30 @@
       <c r="AH5" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI5" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ5" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK5" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL5" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM5" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN5" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO5" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP5" s="26" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -45640,6 +49818,30 @@
       <c r="AH6" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AI6" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ6" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK6" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL6" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM6" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN6" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO6" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP6" s="26" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -45747,6 +49949,30 @@
       </c>
       <c r="AH7" s="25" t="n">
         <v>5</v>
+      </c>
+      <c r="AI7" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ7" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK7" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL7" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM7" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN7" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO7" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP7" s="26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -45856,6 +50082,30 @@
       <c r="AH8" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AI8" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ8" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK8" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL8" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM8" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN8" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO8" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP8" s="26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -45964,6 +50214,30 @@
       <c r="AH9" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="AI9" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ9" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK9" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL9" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM9" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN9" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO9" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP9" s="26" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -46072,6 +50346,32 @@
       <c r="AH10" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AI10" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ10" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK10" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL10" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM10" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN10" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AP10" s="26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -46182,6 +50482,30 @@
       <c r="AH11" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AI11" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ11" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK11" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL11" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM11" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN11" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO11" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP11" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -46298,6 +50622,30 @@
       <c r="AH12" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AI12" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ12" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK12" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL12" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM12" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN12" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO12" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP12" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -46410,6 +50758,30 @@
       <c r="AH13" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AI13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ13" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL13" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN13" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP13" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -46522,6 +50894,30 @@
       <c r="AH14" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI14" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ14" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK14" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL14" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM14" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN14" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO14" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP14" s="26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -46634,6 +51030,30 @@
       <c r="AH15" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AI15" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ15" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK15" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL15" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM15" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN15" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO15" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP15" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -46750,6 +51170,30 @@
       <c r="AH16" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI16" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ16" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK16" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL16" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM16" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN16" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO16" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP16" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -46868,6 +51312,30 @@
       <c r="AH17" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AI17" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ17" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK17" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL17" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM17" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN17" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO17" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP17" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -46980,6 +51448,30 @@
       <c r="AH18" s="25" t="n">
         <v>6</v>
       </c>
+      <c r="AI18" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ18" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK18" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL18" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM18" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN18" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO18" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP18" s="26" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -47092,6 +51584,30 @@
       <c r="AH19" s="24" t="n">
         <v>16</v>
       </c>
+      <c r="AI19" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ19" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK19" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL19" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AM19" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AN19" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO19" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP19" s="26" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -47208,6 +51724,30 @@
       <c r="AH20" s="24" t="n">
         <v>12</v>
       </c>
+      <c r="AI20" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ20" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK20" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AL20" s="25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM20" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AN20" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO20" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP20" s="26" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -47322,6 +51862,32 @@
       <c r="AH21" s="25" t="n">
         <v>9</v>
       </c>
+      <c r="AI21" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ21" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK21" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL21" s="25" t="n">
+        <v>24</v>
+      </c>
+      <c r="AM21" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN21" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO21" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP21" s="26" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -47444,6 +52010,32 @@
       <c r="AH22" s="25" t="n">
         <v>160</v>
       </c>
+      <c r="AI22" s="26" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ22" s="26" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK22" s="26" t="n">
+        <v>130</v>
+      </c>
+      <c r="AL22" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AM22" s="26" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN22" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AO22" s="25" t="n">
+        <v>1405</v>
+      </c>
+      <c r="AP22" s="25" t="n">
+        <v>-18</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -47568,6 +52160,36 @@
       <c r="AH23" s="25" t="n">
         <v>-12</v>
       </c>
+      <c r="AI23" s="25" t="n">
+        <v>35</v>
+      </c>
+      <c r="AJ23" s="25" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK23" s="25" t="n">
+        <v>-35</v>
+      </c>
+      <c r="AL23" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM23" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AN23" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AO23" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AP23" s="25" t="n">
+        <v>-10</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -47694,6 +52316,36 @@
       <c r="AH24" s="25" t="n">
         <v>231</v>
       </c>
+      <c r="AI24" s="26" t="n">
+        <v>457</v>
+      </c>
+      <c r="AJ24" s="26" t="n">
+        <v>457</v>
+      </c>
+      <c r="AK24" s="26" t="n">
+        <v>457</v>
+      </c>
+      <c r="AL24" s="25" t="n">
+        <v>141</v>
+      </c>
+      <c r="AM24" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AN24" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AO24" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AP24" s="25" t="n">
+        <v>1474</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n"/>
@@ -47803,6 +52455,30 @@
       </c>
       <c r="AH26" s="24" t="n">
         <v>24</v>
+      </c>
+      <c r="AI26" s="24" t="n">
+        <v>67</v>
+      </c>
+      <c r="AJ26" s="24" t="n">
+        <v>66</v>
+      </c>
+      <c r="AK26" s="24" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL26" s="24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AM26" s="24" t="n">
+        <v>66</v>
+      </c>
+      <c r="AN26" s="24" t="n">
+        <v>47</v>
+      </c>
+      <c r="AO26" s="24" t="n">
+        <v>59</v>
+      </c>
+      <c r="AP26" s="24" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="27">
@@ -47863,7 +52539,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH37"/>
+  <dimension ref="A1:AP37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -48050,6 +52726,46 @@
           <t>Gemini 3 Flash (minimal)</t>
         </is>
       </c>
+      <c r="AI2" s="23" t="inlineStr">
+        <is>
+          <t>MiniMax M3 (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AJ2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.3 (high)</t>
+        </is>
+      </c>
+      <c r="AK2" s="23" t="inlineStr">
+        <is>
+          <t>GLM-5.2 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AL2" s="23" t="inlineStr">
+        <is>
+          <t>MiniMax M3 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AM2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.3 (none)</t>
+        </is>
+      </c>
+      <c r="AN2" s="23" t="inlineStr">
+        <is>
+          <t>Solar Pro 3 (high)</t>
+        </is>
+      </c>
+      <c r="AO2" s="23" t="inlineStr">
+        <is>
+          <t>Solar Pro 3 (low)</t>
+        </is>
+      </c>
+      <c r="AP2" s="23" t="inlineStr">
+        <is>
+          <t>GLM-5.2 (Non-Thinking)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -48154,6 +52870,30 @@
       <c r="AH3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM3" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP3" s="26" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -48258,6 +52998,30 @@
       <c r="AH4" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AI4" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ4" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK4" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL4" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM4" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN4" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP4" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -48364,6 +53128,30 @@
       <c r="AH5" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI5" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ5" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK5" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL5" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM5" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN5" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO5" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP5" s="26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -48468,6 +53256,30 @@
       <c r="AH6" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI6" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ6" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK6" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL6" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM6" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN6" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO6" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP6" s="26" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -48574,6 +53386,30 @@
       <c r="AH7" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI7" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ7" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK7" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL7" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM7" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN7" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO7" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP7" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -48684,6 +53520,34 @@
       <c r="AH8" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AI8" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ8" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK8" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL8" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM8" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN8" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AO8" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AP8" s="26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -48794,6 +53658,32 @@
       <c r="AH9" s="24" t="n">
         <v>977</v>
       </c>
+      <c r="AI9" s="25" t="n">
+        <v>308</v>
+      </c>
+      <c r="AJ9" s="26" t="n">
+        <v>977</v>
+      </c>
+      <c r="AK9" s="26" t="n">
+        <v>977</v>
+      </c>
+      <c r="AL9" s="26" t="n">
+        <v>977</v>
+      </c>
+      <c r="AM9" s="25" t="n">
+        <v>694</v>
+      </c>
+      <c r="AN9" s="25" t="n">
+        <v>97</v>
+      </c>
+      <c r="AO9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AP9" s="25" t="n">
+        <v>457</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -48908,6 +53798,32 @@
       <c r="AH10" s="25" t="n">
         <v>105</v>
       </c>
+      <c r="AI10" s="25" t="n">
+        <v>135</v>
+      </c>
+      <c r="AJ10" s="26" t="n">
+        <v>262</v>
+      </c>
+      <c r="AK10" s="26" t="n">
+        <v>262</v>
+      </c>
+      <c r="AL10" s="25" t="n">
+        <v>202</v>
+      </c>
+      <c r="AM10" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AN10" s="26" t="n">
+        <v>262</v>
+      </c>
+      <c r="AO10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AP10" s="25" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -49017,6 +53933,30 @@
       </c>
       <c r="AH12" s="24" t="n">
         <v>18</v>
+      </c>
+      <c r="AI12" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ12" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK12" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL12" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AM12" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN12" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO12" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP12" s="24" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -49129,7 +54069,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1000"/>
+  <dimension ref="A1:AP1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -49318,6 +54258,46 @@
           <t>Gemini 3 Flash (high)</t>
         </is>
       </c>
+      <c r="AI2" s="23" t="inlineStr">
+        <is>
+          <t>MiniMax M3 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AJ2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.3 (none)</t>
+        </is>
+      </c>
+      <c r="AK2" s="23" t="inlineStr">
+        <is>
+          <t>GLM-5.2 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AL2" s="23" t="inlineStr">
+        <is>
+          <t>MiniMax M3 (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AM2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.3 (high)</t>
+        </is>
+      </c>
+      <c r="AN2" s="23" t="inlineStr">
+        <is>
+          <t>Solar Pro 3 (high)</t>
+        </is>
+      </c>
+      <c r="AO2" s="23" t="inlineStr">
+        <is>
+          <t>GLM-5.2 (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AP2" s="23" t="inlineStr">
+        <is>
+          <t>Solar Pro 3 (low)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -49424,6 +54404,32 @@
       <c r="AH3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI3" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP3" s="26" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -49530,6 +54536,32 @@
       <c r="AH4" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI4" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ4" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK4" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL4" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM4" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN4" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO4" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP4" s="26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -49636,6 +54668,32 @@
       <c r="AH5" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI5" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ5" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK5" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL5" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM5" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN5" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO5" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP5" s="26" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -49742,6 +54800,32 @@
       <c r="AH6" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AI6" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ6" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK6" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL6" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM6" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN6" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP6" s="26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -49848,6 +54932,32 @@
       <c r="AH7" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI7" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ7" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK7" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL7" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM7" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN7" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO7" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP7" s="26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -49954,6 +55064,32 @@
       <c r="AH8" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI8" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ8" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK8" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL8" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM8" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN8" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO8" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP8" s="26" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -50060,6 +55196,36 @@
       <c r="AH9" s="24" t="n">
         <v>97</v>
       </c>
+      <c r="AI9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AK9" s="26" t="n">
+        <v>97</v>
+      </c>
+      <c r="AL9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AM9" s="26" t="n">
+        <v>97</v>
+      </c>
+      <c r="AN9" s="26" t="n">
+        <v>97</v>
+      </c>
+      <c r="AO9" s="26" t="n">
+        <v>97</v>
+      </c>
+      <c r="AP9" s="25" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -50172,6 +55338,40 @@
       <c r="AH10" s="25" t="n">
         <v>17</v>
       </c>
+      <c r="AI10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AK10" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AL10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AM10" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN10" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AP10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -50281,6 +55481,30 @@
       </c>
       <c r="AH12" s="24" t="n">
         <v>22</v>
+      </c>
+      <c r="AI12" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK12" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL12" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AM12" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AN12" s="24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO12" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP12" s="24" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -54249,7 +59473,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH37"/>
+  <dimension ref="A1:AP37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -54436,6 +59660,46 @@
           <t>Gemini 3 Flash (high)</t>
         </is>
       </c>
+      <c r="AI2" s="23" t="inlineStr">
+        <is>
+          <t>MiniMax M3 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AJ2" s="23" t="inlineStr">
+        <is>
+          <t>GLM-5.2 (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AK2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.3 (high)</t>
+        </is>
+      </c>
+      <c r="AL2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.3 (none)</t>
+        </is>
+      </c>
+      <c r="AM2" s="23" t="inlineStr">
+        <is>
+          <t>Solar Pro 3 (high)</t>
+        </is>
+      </c>
+      <c r="AN2" s="23" t="inlineStr">
+        <is>
+          <t>GLM-5.2 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AO2" s="23" t="inlineStr">
+        <is>
+          <t>MiniMax M3 (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AP2" s="23" t="inlineStr">
+        <is>
+          <t>Solar Pro 3 (low)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -54540,6 +59804,32 @@
       <c r="AH3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI3" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP3" s="26" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -54644,6 +59934,32 @@
       <c r="AH4" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AI4" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ4" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK4" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL4" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM4" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN4" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP4" s="26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -54750,6 +60066,34 @@
       <c r="AH5" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI5" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ5" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK5" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL5" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AM5" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN5" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO5" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP5" s="26" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -54854,6 +60198,34 @@
       <c r="AH6" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI6" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ6" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK6" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL6" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AM6" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN6" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO6" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP6" s="26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -54960,6 +60332,32 @@
       <c r="AH7" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI7" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ7" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK7" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL7" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM7" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN7" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO7" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP7" s="26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -55064,6 +60462,32 @@
       <c r="AH8" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI8" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ8" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK8" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL8" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM8" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN8" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO8" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP8" s="26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -55170,6 +60594,34 @@
       <c r="AH9" s="24" t="n">
         <v>360</v>
       </c>
+      <c r="AI9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ9" s="25" t="n">
+        <v>100</v>
+      </c>
+      <c r="AK9" s="26" t="n">
+        <v>360</v>
+      </c>
+      <c r="AL9" s="25" t="n">
+        <v>256</v>
+      </c>
+      <c r="AM9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AN9" s="26" t="n">
+        <v>360</v>
+      </c>
+      <c r="AO9" s="26" t="n">
+        <v>360</v>
+      </c>
+      <c r="AP9" s="25" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -55274,6 +60726,34 @@
       <c r="AH10" s="24" t="n">
         <v>221</v>
       </c>
+      <c r="AI10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AJ10" s="25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK10" s="26" t="n">
+        <v>221</v>
+      </c>
+      <c r="AL10" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AN10" s="25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO10" s="26" t="n">
+        <v>221</v>
+      </c>
+      <c r="AP10" s="25" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -55383,6 +60863,30 @@
       </c>
       <c r="AH12" s="24" t="n">
         <v>26</v>
+      </c>
+      <c r="AI12" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK12" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL12" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM12" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AN12" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO12" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP12" s="24" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -55495,7 +60999,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1000"/>
+  <dimension ref="A1:AP1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -55685,6 +61189,46 @@
           <t>Gemini 3 Flash (high)</t>
         </is>
       </c>
+      <c r="AI2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.3 (none)</t>
+        </is>
+      </c>
+      <c r="AJ2" s="23" t="inlineStr">
+        <is>
+          <t>MiniMax M3 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AK2" s="23" t="inlineStr">
+        <is>
+          <t>MiniMax M3 (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AL2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.3 (high)</t>
+        </is>
+      </c>
+      <c r="AM2" s="23" t="inlineStr">
+        <is>
+          <t>GLM-5.2 (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AN2" s="23" t="inlineStr">
+        <is>
+          <t>GLM-5.2 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AO2" s="23" t="inlineStr">
+        <is>
+          <t>Solar Pro 3 (low)</t>
+        </is>
+      </c>
+      <c r="AP2" s="23" t="inlineStr">
+        <is>
+          <t>Solar Pro 3 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -55789,6 +61333,30 @@
       <c r="AH3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP3" s="26" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -55893,6 +61461,30 @@
       <c r="AH4" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI4" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ4" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK4" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL4" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM4" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN4" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO4" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP4" s="26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -55997,6 +61589,30 @@
       <c r="AH5" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AI5" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ5" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK5" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL5" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM5" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN5" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP5" s="26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -56103,6 +61719,34 @@
       <c r="AH6" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI6" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ6" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK6" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL6" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM6" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN6" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AO6" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP6" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -56205,6 +61849,30 @@
         <v>1</v>
       </c>
       <c r="AH7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI7" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ7" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK7" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL7" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM7" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN7" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP7" s="26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -56311,6 +61979,30 @@
       <c r="AH8" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI8" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ8" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK8" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL8" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM8" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN8" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO8" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP8" s="26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -56415,6 +62107,30 @@
       <c r="AH9" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AI9" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ9" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK9" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL9" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM9" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN9" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP9" s="26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -56519,6 +62235,30 @@
       <c r="AH10" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI10" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ10" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK10" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL10" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM10" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN10" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO10" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP10" s="26" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -56623,6 +62363,30 @@
       <c r="AH11" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI11" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ11" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK11" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL11" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM11" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN11" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO11" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP11" s="26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -56727,6 +62491,30 @@
       <c r="AH12" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI12" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ12" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK12" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL12" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM12" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN12" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO12" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP12" s="26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -56831,6 +62619,30 @@
       <c r="AH13" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AI13" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ13" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK13" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL13" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM13" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN13" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO13" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP13" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -56935,6 +62747,30 @@
       <c r="AH14" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI14" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ14" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK14" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL14" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM14" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN14" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO14" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP14" s="26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -57039,6 +62875,30 @@
       <c r="AH15" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI15" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ15" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK15" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL15" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM15" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN15" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO15" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP15" s="26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -57143,6 +63003,30 @@
       <c r="AH16" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP16" s="26" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -57247,6 +63131,30 @@
       <c r="AH17" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP17" s="26" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -57351,6 +63259,30 @@
       <c r="AH18" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AI18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP18" s="26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -57455,6 +63387,30 @@
       <c r="AH19" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI19" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ19" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK19" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL19" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM19" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN19" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO19" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP19" s="26" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -57559,6 +63515,30 @@
       <c r="AH20" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI20" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ20" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK20" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL20" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM20" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN20" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO20" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP20" s="26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -57663,6 +63643,30 @@
       <c r="AH21" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AI21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP21" s="26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -57767,6 +63771,30 @@
       <c r="AH22" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI22" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ22" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK22" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL22" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM22" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN22" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO22" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP22" s="26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -57871,6 +63899,30 @@
       <c r="AH23" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI23" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ23" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK23" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL23" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM23" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN23" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO23" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP23" s="26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -57975,6 +64027,30 @@
       <c r="AH24" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AI24" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ24" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK24" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL24" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM24" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN24" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO24" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP24" s="26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -58079,6 +64155,30 @@
       <c r="AH25" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI25" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ25" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK25" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL25" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM25" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN25" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO25" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP25" s="26" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -58183,6 +64283,30 @@
       <c r="AH26" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI26" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ26" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK26" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL26" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM26" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN26" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO26" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP26" s="26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -58289,6 +64413,32 @@
       <c r="AH27" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI27" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ27" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK27" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL27" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM27" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN27" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AO27" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP27" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -58393,6 +64543,30 @@
       <c r="AH28" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI28" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ28" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK28" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL28" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM28" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN28" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO28" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP28" s="26" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -58497,6 +64671,30 @@
       <c r="AH29" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI29" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ29" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK29" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL29" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM29" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN29" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO29" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP29" s="26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -58601,6 +64799,30 @@
       <c r="AH30" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI30" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ30" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK30" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL30" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM30" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN30" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO30" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP30" s="26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -58705,6 +64927,30 @@
       <c r="AH31" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI31" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ31" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK31" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL31" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM31" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN31" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO31" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP31" s="26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -58809,6 +65055,30 @@
       <c r="AH32" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI32" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ32" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK32" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL32" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM32" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN32" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO32" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP32" s="26" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -58915,6 +65185,30 @@
       <c r="AH33" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AI33" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ33" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK33" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL33" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM33" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN33" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO33" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP33" s="26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -59021,6 +65315,30 @@
       <c r="AH34" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI34" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ34" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK34" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL34" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM34" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN34" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO34" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP34" s="26" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -59127,6 +65445,30 @@
       <c r="AH35" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI35" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ35" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK35" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL35" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM35" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN35" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO35" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP35" s="26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -59233,6 +65575,30 @@
       <c r="AH36" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI36" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ36" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK36" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL36" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM36" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN36" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO36" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP36" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -59339,6 +65705,30 @@
       <c r="AH37" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI37" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ37" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK37" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL37" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM37" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN37" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO37" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP37" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -59445,6 +65835,30 @@
       <c r="AH38" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI38" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ38" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK38" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL38" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM38" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN38" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO38" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP38" s="26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -59551,6 +65965,30 @@
       <c r="AH39" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI39" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ39" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK39" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL39" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM39" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN39" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO39" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP39" s="26" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -59657,6 +66095,30 @@
       <c r="AH40" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI40" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ40" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK40" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL40" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM40" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN40" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO40" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP40" s="26" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -59763,6 +66225,30 @@
       <c r="AH41" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AI41" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ41" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK41" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL41" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM41" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN41" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO41" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP41" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -59871,6 +66357,30 @@
       <c r="AH42" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI42" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ42" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK42" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL42" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM42" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN42" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO42" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP42" s="26" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -59977,6 +66487,30 @@
       <c r="AH43" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI43" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ43" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK43" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL43" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM43" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN43" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO43" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP43" s="26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -60083,6 +66617,30 @@
       <c r="AH44" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI44" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ44" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK44" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL44" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM44" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN44" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO44" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP44" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -60189,6 +66747,30 @@
       <c r="AH45" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI45" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ45" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK45" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL45" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM45" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN45" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO45" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP45" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -60295,6 +66877,30 @@
       <c r="AH46" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI46" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ46" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK46" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL46" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM46" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN46" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO46" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP46" s="26" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -60401,6 +67007,30 @@
       <c r="AH47" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI47" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ47" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK47" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL47" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM47" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN47" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO47" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP47" s="26" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n"/>
@@ -60510,6 +67140,30 @@
       </c>
       <c r="AH49" s="24" t="n">
         <v>97</v>
+      </c>
+      <c r="AI49" s="24" t="n">
+        <v>93</v>
+      </c>
+      <c r="AJ49" s="24" t="n">
+        <v>94</v>
+      </c>
+      <c r="AK49" s="24" t="n">
+        <v>89</v>
+      </c>
+      <c r="AL49" s="24" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM49" s="24" t="n">
+        <v>86</v>
+      </c>
+      <c r="AN49" s="24" t="n">
+        <v>94</v>
+      </c>
+      <c r="AO49" s="24" t="n">
+        <v>83</v>
+      </c>
+      <c r="AP49" s="24" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="50">
@@ -64330,7 +70984,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1000"/>
+  <dimension ref="A1:AP1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -64521,6 +71175,46 @@
           <t>Gemini 3 Flash (minimal)</t>
         </is>
       </c>
+      <c r="AI2" s="23" t="inlineStr">
+        <is>
+          <t>GLM-5.2 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AJ2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.3 (none)</t>
+        </is>
+      </c>
+      <c r="AK2" s="23" t="inlineStr">
+        <is>
+          <t>GLM-5.2 (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AL2" s="23" t="inlineStr">
+        <is>
+          <t>MiniMax M3 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AM2" s="23" t="inlineStr">
+        <is>
+          <t>Solar Pro 3 (high)</t>
+        </is>
+      </c>
+      <c r="AN2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.3 (high)</t>
+        </is>
+      </c>
+      <c r="AO2" s="23" t="inlineStr">
+        <is>
+          <t>MiniMax M3 (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AP2" s="23" t="inlineStr">
+        <is>
+          <t>Solar Pro 3 (low)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -64625,6 +71319,30 @@
       <c r="AH3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO3" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP3" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -64729,6 +71447,30 @@
       <c r="AH4" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI4" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ4" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK4" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL4" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM4" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN4" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO4" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP4" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -64833,6 +71575,30 @@
       <c r="AH5" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AI5" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ5" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK5" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL5" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM5" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN5" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP5" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -64937,6 +71703,30 @@
       <c r="AH6" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI6" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ6" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK6" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL6" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM6" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN6" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO6" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP6" s="26" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -65040,6 +71830,30 @@
       </c>
       <c r="AH7" s="24" t="n">
         <v>2</v>
+      </c>
+      <c r="AI7" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ7" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK7" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL7" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM7" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN7" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO7" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP7" s="25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -65145,6 +71959,30 @@
       <c r="AH8" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI8" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ8" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK8" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL8" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM8" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN8" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO8" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP8" s="26" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -65249,6 +72087,30 @@
       <c r="AH9" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI9" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ9" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK9" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL9" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM9" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN9" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO9" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP9" s="26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -65353,6 +72215,30 @@
       <c r="AH10" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI10" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ10" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK10" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL10" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM10" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN10" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO10" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP10" s="26" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -65457,6 +72343,30 @@
       <c r="AH11" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO11" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP11" s="26" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -65561,6 +72471,30 @@
       <c r="AH12" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AI12" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ12" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK12" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL12" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM12" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN12" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO12" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP12" s="26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -65665,6 +72599,30 @@
       <c r="AH13" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP13" s="26" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -65769,6 +72727,30 @@
       <c r="AH14" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI14" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ14" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK14" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL14" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM14" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN14" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO14" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP14" s="26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -65873,6 +72855,30 @@
       <c r="AH15" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI15" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ15" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK15" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL15" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM15" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN15" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO15" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP15" s="26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -65977,6 +72983,30 @@
       <c r="AH16" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI16" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ16" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK16" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL16" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM16" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN16" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO16" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP16" s="26" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -66081,6 +73111,30 @@
       <c r="AH17" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AI17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP17" s="26" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -66185,6 +73239,30 @@
       <c r="AH18" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AI18" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ18" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK18" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL18" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM18" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN18" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO18" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP18" s="26" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -66289,6 +73367,30 @@
       <c r="AH19" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI19" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ19" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK19" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL19" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM19" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN19" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO19" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP19" s="26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -66393,6 +73495,30 @@
       <c r="AH20" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AI20" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ20" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK20" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL20" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM20" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN20" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO20" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP20" s="26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -66497,6 +73623,30 @@
       <c r="AH21" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AI21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO21" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP21" s="26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -66601,6 +73751,30 @@
       <c r="AH22" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AI22" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ22" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK22" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL22" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM22" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN22" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO22" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP22" s="26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n"/>
@@ -66710,6 +73884,30 @@
       </c>
       <c r="AH24" s="24" t="n">
         <v>50</v>
+      </c>
+      <c r="AI24" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ24" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK24" s="24" t="n">
+        <v>45</v>
+      </c>
+      <c r="AL24" s="24" t="n">
+        <v>41</v>
+      </c>
+      <c r="AM24" s="24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AN24" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO24" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP24" s="24" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="25">

--- a/2026 수능 LLM 풀이 hard.xlsx
+++ b/2026 수능 LLM 풀이 hard.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP1000"/>
+  <dimension ref="A1:AQ1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -710,6 +710,11 @@
           <t>Solar Pro 3 (low)</t>
         </is>
       </c>
+      <c r="AQ2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-5.5 Pro</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -838,6 +843,9 @@
       <c r="AP3" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AQ3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -966,6 +974,9 @@
       <c r="AP4" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AQ4" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -1094,6 +1105,9 @@
       <c r="AP5" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AQ5" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1224,6 +1238,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ6" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -1353,6 +1370,9 @@
         <is>
           <t>(포기)</t>
         </is>
+      </c>
+      <c r="AQ7" s="24" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -1484,6 +1504,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ8" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -1614,6 +1637,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ9" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -1744,6 +1770,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ10" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -1874,6 +1903,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ11" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -2002,6 +2034,9 @@
       <c r="AP12" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AQ12" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -2132,6 +2167,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ13" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -2260,6 +2298,9 @@
       <c r="AP14" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AQ14" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -2388,6 +2429,9 @@
       <c r="AP15" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AQ15" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -2516,6 +2560,9 @@
       <c r="AP16" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AQ16" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -2644,6 +2691,9 @@
       <c r="AP17" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AQ17" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -2772,6 +2822,9 @@
       <c r="AP18" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AQ18" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -2900,6 +2953,9 @@
       <c r="AP19" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AQ19" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -3028,6 +3084,9 @@
       <c r="AP20" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AQ20" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -3156,6 +3215,9 @@
       <c r="AP21" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AQ21" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -3284,6 +3346,9 @@
       <c r="AP22" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AQ22" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -3412,6 +3477,9 @@
       <c r="AP23" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AQ23" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -3540,6 +3608,9 @@
       <c r="AP24" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AQ24" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -3668,6 +3739,9 @@
       <c r="AP25" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AQ25" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -3796,6 +3870,9 @@
       <c r="AP26" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AQ26" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -3924,6 +4001,9 @@
       <c r="AP27" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AQ27" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -4052,6 +4132,9 @@
       <c r="AP28" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AQ28" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -4182,6 +4265,9 @@
       <c r="AP29" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AQ29" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -4312,6 +4398,9 @@
       <c r="AP30" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AQ30" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -4442,6 +4531,9 @@
       <c r="AP31" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AQ31" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -4572,6 +4664,9 @@
       <c r="AP32" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AQ32" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -4702,6 +4797,9 @@
       <c r="AP33" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AQ33" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -4832,6 +4930,9 @@
       <c r="AP34" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AQ34" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -4962,6 +5063,9 @@
       <c r="AP35" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AQ35" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -5092,6 +5196,9 @@
       <c r="AP36" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AQ36" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n"/>
@@ -5225,6 +5332,9 @@
       </c>
       <c r="AP38" s="24" t="n">
         <v>56</v>
+      </c>
+      <c r="AQ38" s="24" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="39">
@@ -9089,7 +9199,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP1000"/>
+  <dimension ref="A1:AQ1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -9316,6 +9426,11 @@
           <t>Solar Pro 3 (low)</t>
         </is>
       </c>
+      <c r="AQ2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-5.5 Pro</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
@@ -9450,6 +9565,9 @@
       <c r="AP3" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AQ3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="n">
@@ -9588,6 +9706,9 @@
       <c r="AP4" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AQ4" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="n">
@@ -9722,6 +9843,9 @@
       <c r="AP5" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="AQ5" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="n">
@@ -9862,6 +9986,9 @@
       <c r="AP6" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AQ6" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="n">
@@ -10004,6 +10131,9 @@
         <v>4</v>
       </c>
       <c r="AP7" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ7" s="24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10152,6 +10282,9 @@
       <c r="AP8" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AQ8" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="n">
@@ -10296,6 +10429,9 @@
       <c r="AP9" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AQ9" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="n">
@@ -10440,6 +10576,9 @@
       <c r="AP10" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AQ10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="n">
@@ -10582,6 +10721,9 @@
       <c r="AP11" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AQ11" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="n">
@@ -10724,6 +10866,9 @@
       <c r="AP12" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AQ12" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
@@ -10868,6 +11013,9 @@
       <c r="AP13" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AQ13" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="n">
@@ -11014,6 +11162,9 @@
       <c r="AP14" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AQ14" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="n">
@@ -11164,6 +11315,9 @@
       <c r="AP15" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AQ15" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="n">
@@ -11312,6 +11466,9 @@
       <c r="AP16" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AQ16" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="n">
@@ -11460,6 +11617,9 @@
       <c r="AP17" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AQ17" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n">
@@ -11608,6 +11768,9 @@
       <c r="AP18" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AQ18" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="n">
@@ -11756,6 +11919,9 @@
       <c r="AP19" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AQ19" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="n">
@@ -11904,6 +12070,9 @@
       <c r="AP20" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AQ20" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="n">
@@ -12052,6 +12221,9 @@
       <c r="AP21" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="AQ21" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="n">
@@ -12200,6 +12372,9 @@
       <c r="AP22" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AQ22" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="n"/>
@@ -12333,6 +12508,9 @@
       </c>
       <c r="AP24" s="24" t="n">
         <v>19</v>
+      </c>
+      <c r="AQ24" s="24" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="25">
@@ -16253,7 +16431,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP1000"/>
+  <dimension ref="A1:AQ1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -16480,6 +16658,11 @@
           <t>Solar Pro 3 (high)</t>
         </is>
       </c>
+      <c r="AQ2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-5.5 Pro</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
@@ -16622,6 +16805,9 @@
       <c r="AP3" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AQ3" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="n">
@@ -16764,6 +16950,9 @@
       <c r="AP4" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AQ4" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="n">
@@ -16908,6 +17097,9 @@
       <c r="AP5" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AQ5" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="n">
@@ -17052,6 +17244,9 @@
       <c r="AP6" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AQ6" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="n">
@@ -17195,6 +17390,9 @@
       </c>
       <c r="AP7" s="25" t="n">
         <v>1</v>
+      </c>
+      <c r="AQ7" s="24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -17342,6 +17540,9 @@
       <c r="AP8" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AQ8" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="n">
@@ -17488,6 +17689,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ9" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="n">
@@ -17636,6 +17840,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="n">
@@ -17786,6 +17993,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ11" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="n">
@@ -17934,6 +18144,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ12" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
@@ -18086,6 +18299,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ13" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="n">
@@ -18236,6 +18452,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ14" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="n">
@@ -18386,6 +18605,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ15" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="n">
@@ -18536,6 +18758,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ16" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="n">
@@ -18686,6 +18911,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ17" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n">
@@ -18840,6 +19068,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ18" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="n">
@@ -18992,6 +19223,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ19" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="n">
@@ -19146,6 +19380,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ20" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="n">
@@ -19302,6 +19539,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ21" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="n">
@@ -19456,6 +19696,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ22" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="n"/>
@@ -19589,6 +19832,9 @@
       </c>
       <c r="AP24" s="24" t="n">
         <v>9</v>
+      </c>
+      <c r="AQ24" s="24" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="25">
@@ -23509,7 +23755,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP1000"/>
+  <dimension ref="A1:AQ1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -23736,6 +23982,11 @@
           <t>Solar Pro 3 (low)</t>
         </is>
       </c>
+      <c r="AQ2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-5.5 Pro</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
@@ -23874,6 +24125,9 @@
       <c r="AP3" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AQ3" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="n">
@@ -24012,6 +24266,9 @@
       <c r="AP4" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AQ4" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="n">
@@ -24150,6 +24407,9 @@
       <c r="AP5" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AQ5" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="n">
@@ -24288,6 +24548,9 @@
       <c r="AP6" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AQ6" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="n">
@@ -24427,6 +24690,9 @@
         <is>
           <t>(포기)</t>
         </is>
+      </c>
+      <c r="AQ7" s="24" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -24568,6 +24834,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ8" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="n">
@@ -24706,6 +24975,9 @@
       <c r="AP9" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AQ9" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="n">
@@ -24844,6 +25116,9 @@
       <c r="AP10" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AQ10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="n">
@@ -24986,6 +25261,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ11" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="n">
@@ -25126,6 +25404,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ12" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
@@ -25268,6 +25549,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ13" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="n">
@@ -25408,6 +25692,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ14" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="n">
@@ -25550,6 +25837,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ15" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="n">
@@ -25694,6 +25984,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ16" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="n">
@@ -25838,6 +26131,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ17" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n">
@@ -25982,6 +26278,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ18" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="n">
@@ -26126,6 +26425,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ19" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="n">
@@ -26270,6 +26572,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ20" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="n">
@@ -26416,6 +26721,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ21" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="n">
@@ -26560,6 +26868,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ22" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="n"/>
@@ -26693,6 +27004,9 @@
       </c>
       <c r="AP24" s="24" t="n">
         <v>7</v>
+      </c>
+      <c r="AQ24" s="24" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="25">
@@ -30613,7 +30927,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP1000"/>
+  <dimension ref="A1:AQ1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -30840,6 +31154,11 @@
           <t>MiniMax M3 (Thinking)</t>
         </is>
       </c>
+      <c r="AQ2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-5.5 Pro</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
@@ -30970,6 +31289,9 @@
       <c r="AP3" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AQ3" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="n">
@@ -31102,6 +31424,9 @@
       <c r="AP4" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AQ4" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="n">
@@ -31234,6 +31559,9 @@
       <c r="AP5" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AQ5" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="n">
@@ -31366,6 +31694,9 @@
       <c r="AP6" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AQ6" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="n">
@@ -31496,6 +31827,9 @@
         <v>5</v>
       </c>
       <c r="AP7" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ7" s="24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31632,6 +31966,9 @@
       <c r="AP8" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AQ8" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="n">
@@ -31766,6 +32103,9 @@
       <c r="AP9" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="AQ9" s="25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="n">
@@ -31900,6 +32240,9 @@
       <c r="AP10" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AQ10" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="n">
@@ -32034,6 +32377,9 @@
       <c r="AP11" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AQ11" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="n">
@@ -32170,6 +32516,9 @@
       <c r="AP12" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AQ12" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
@@ -32304,6 +32653,9 @@
       <c r="AP13" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="AQ13" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="n">
@@ -32438,6 +32790,9 @@
       <c r="AP14" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AQ14" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="n">
@@ -32574,6 +32929,9 @@
       <c r="AP15" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AQ15" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="n">
@@ -32708,6 +33066,9 @@
       <c r="AP16" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AQ16" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="n">
@@ -32842,6 +33203,9 @@
       <c r="AP17" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AQ17" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n">
@@ -32976,6 +33340,9 @@
       <c r="AP18" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AQ18" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="n">
@@ -33110,6 +33477,9 @@
       <c r="AP19" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AQ19" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="n">
@@ -33244,6 +33614,9 @@
       <c r="AP20" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AQ20" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="n">
@@ -33378,6 +33751,9 @@
       <c r="AP21" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AQ21" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="n">
@@ -33514,6 +33890,9 @@
       <c r="AP22" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AQ22" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="n"/>
@@ -33647,6 +34026,9 @@
       </c>
       <c r="AP24" s="24" t="n">
         <v>36</v>
+      </c>
+      <c r="AQ24" s="24" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="25">
@@ -37567,7 +37949,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP1000"/>
+  <dimension ref="A1:AQ1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -37796,6 +38178,11 @@
           <t>Solar Pro 3 (low)</t>
         </is>
       </c>
+      <c r="AQ2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-5.5 Pro</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -37924,6 +38311,9 @@
       <c r="AP3" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AQ3" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -38052,6 +38442,9 @@
       <c r="AP4" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="AQ4" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -38182,6 +38575,9 @@
       <c r="AP5" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AQ5" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -38312,6 +38708,9 @@
       <c r="AP6" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AQ6" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -38442,6 +38841,9 @@
       <c r="AP7" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AQ7" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -38572,6 +38974,9 @@
       <c r="AP8" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AQ8" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -38702,6 +39107,9 @@
       <c r="AP9" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AQ9" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -38832,6 +39240,9 @@
       <c r="AP10" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AQ10" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -38962,6 +39373,9 @@
       <c r="AP11" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AQ11" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -39092,6 +39506,9 @@
       <c r="AP12" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AQ12" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -39224,6 +39641,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ13" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
@@ -39357,6 +39777,9 @@
       </c>
       <c r="AP15" s="24" t="n">
         <v>15</v>
+      </c>
+      <c r="AQ15" s="24" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="16">
@@ -43313,7 +43736,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP1000"/>
+  <dimension ref="A1:AQ1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -43544,6 +43967,11 @@
           <t>Solar Pro 3 (high)</t>
         </is>
       </c>
+      <c r="AQ2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-5.5 Pro</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -43674,6 +44102,9 @@
       <c r="AP3" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AQ3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -43806,6 +44237,9 @@
       <c r="AP4" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AQ4" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -43940,6 +44374,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ5" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -44072,6 +44509,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ6" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -44204,6 +44644,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ7" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -44336,6 +44779,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ8" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -44470,6 +44916,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ9" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -44602,6 +45051,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -44734,6 +45186,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ11" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -44866,6 +45321,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ12" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -44998,6 +45456,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ13" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
@@ -45131,6 +45592,9 @@
       </c>
       <c r="AP15" s="24" t="n">
         <v>0</v>
+      </c>
+      <c r="AQ15" s="24" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="16">
@@ -49087,7 +49551,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP37"/>
+  <dimension ref="A1:AQ37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -49314,6 +49778,11 @@
           <t>GLM-5.2 (Non-Thinking)</t>
         </is>
       </c>
+      <c r="AQ2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-5.5 Pro</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -49446,6 +49915,9 @@
       <c r="AP3" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AQ3" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -49578,6 +50050,9 @@
       <c r="AP4" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AQ4" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -49710,6 +50185,9 @@
       <c r="AP5" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AQ5" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -49842,6 +50320,9 @@
       <c r="AP6" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AQ6" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -49972,6 +50453,9 @@
         <v>3</v>
       </c>
       <c r="AP7" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ7" s="24" t="n">
         <v>3</v>
       </c>
     </row>
@@ -50106,6 +50590,9 @@
       <c r="AP8" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AQ8" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -50238,6 +50725,9 @@
       <c r="AP9" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AQ9" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -50372,6 +50862,9 @@
       <c r="AP10" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AQ10" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -50506,6 +50999,9 @@
       <c r="AP11" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AQ11" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -50646,6 +51142,9 @@
       <c r="AP12" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AQ12" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -50782,6 +51281,9 @@
       <c r="AP13" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AQ13" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -50918,6 +51420,9 @@
       <c r="AP14" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AQ14" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -51054,6 +51559,9 @@
       <c r="AP15" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AQ15" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -51194,6 +51702,9 @@
       <c r="AP16" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AQ16" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -51336,6 +51847,9 @@
       <c r="AP17" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AQ17" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -51472,6 +51986,9 @@
       <c r="AP18" s="26" t="n">
         <v>9</v>
       </c>
+      <c r="AQ18" s="24" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -51608,6 +52125,9 @@
       <c r="AP19" s="26" t="n">
         <v>16</v>
       </c>
+      <c r="AQ19" s="24" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -51748,6 +52268,9 @@
       <c r="AP20" s="26" t="n">
         <v>12</v>
       </c>
+      <c r="AQ20" s="24" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -51888,6 +52411,9 @@
       <c r="AP21" s="26" t="n">
         <v>15</v>
       </c>
+      <c r="AQ21" s="24" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -52036,6 +52562,9 @@
       <c r="AP22" s="25" t="n">
         <v>-18</v>
       </c>
+      <c r="AQ22" s="24" t="n">
+        <v>130</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -52190,6 +52719,9 @@
       <c r="AP23" s="25" t="n">
         <v>-10</v>
       </c>
+      <c r="AQ23" s="24" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -52346,6 +52878,9 @@
       <c r="AP24" s="25" t="n">
         <v>1474</v>
       </c>
+      <c r="AQ24" s="24" t="n">
+        <v>457</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n"/>
@@ -52479,6 +53014,9 @@
       </c>
       <c r="AP26" s="24" t="n">
         <v>38</v>
+      </c>
+      <c r="AQ26" s="24" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="27">
@@ -52539,7 +53077,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP37"/>
+  <dimension ref="A1:AQ37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -52766,6 +53304,11 @@
           <t>GLM-5.2 (Non-Thinking)</t>
         </is>
       </c>
+      <c r="AQ2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-5.5 Pro</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -52894,6 +53437,9 @@
       <c r="AP3" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AQ3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -53022,6 +53568,9 @@
       <c r="AP4" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AQ4" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -53152,6 +53701,9 @@
       <c r="AP5" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AQ5" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -53280,6 +53832,9 @@
       <c r="AP6" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AQ6" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -53410,6 +53965,9 @@
       <c r="AP7" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AQ7" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -53548,6 +54106,9 @@
       <c r="AP8" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AQ8" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -53684,6 +54245,9 @@
       <c r="AP9" s="25" t="n">
         <v>457</v>
       </c>
+      <c r="AQ9" s="24" t="n">
+        <v>977</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -53824,6 +54388,9 @@
       <c r="AP10" s="25" t="n">
         <v>78</v>
       </c>
+      <c r="AQ10" s="24" t="n">
+        <v>262</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -53957,6 +54524,9 @@
       </c>
       <c r="AP12" s="24" t="n">
         <v>12</v>
+      </c>
+      <c r="AQ12" s="24" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="13">
@@ -54069,7 +54639,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP1000"/>
+  <dimension ref="A1:AQ1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -54298,6 +54868,11 @@
           <t>Solar Pro 3 (low)</t>
         </is>
       </c>
+      <c r="AQ2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-5.5 Pro</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -54430,6 +55005,9 @@
       <c r="AP3" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AQ3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -54562,6 +55140,9 @@
       <c r="AP4" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AQ4" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -54694,6 +55275,9 @@
       <c r="AP5" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AQ5" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -54826,6 +55410,9 @@
       <c r="AP6" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AQ6" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -54958,6 +55545,9 @@
       <c r="AP7" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AQ7" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -55090,6 +55680,9 @@
       <c r="AP8" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AQ8" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -55226,6 +55819,9 @@
       <c r="AP9" s="25" t="n">
         <v>43</v>
       </c>
+      <c r="AQ9" s="24" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -55372,6 +55968,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ10" s="24" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -55505,6 +56104,9 @@
       </c>
       <c r="AP12" s="24" t="n">
         <v>18</v>
+      </c>
+      <c r="AQ12" s="24" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="13">
@@ -59473,7 +60075,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP37"/>
+  <dimension ref="A1:AQ37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -59700,6 +60302,11 @@
           <t>Solar Pro 3 (low)</t>
         </is>
       </c>
+      <c r="AQ2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-5.5 Pro</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -59830,6 +60437,9 @@
       <c r="AP3" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AQ3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -59960,6 +60570,9 @@
       <c r="AP4" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AQ4" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -60094,6 +60707,9 @@
       <c r="AP5" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AQ5" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -60226,6 +60842,9 @@
       <c r="AP6" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AQ6" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -60358,6 +60977,9 @@
       <c r="AP7" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AQ7" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -60488,6 +61110,9 @@
       <c r="AP8" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AQ8" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -60622,6 +61247,9 @@
       <c r="AP9" s="25" t="n">
         <v>72</v>
       </c>
+      <c r="AQ9" s="24" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -60754,6 +61382,9 @@
       <c r="AP10" s="25" t="n">
         <v>21</v>
       </c>
+      <c r="AQ10" s="24" t="n">
+        <v>221</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -60887,6 +61518,9 @@
       </c>
       <c r="AP12" s="24" t="n">
         <v>18</v>
+      </c>
+      <c r="AQ12" s="24" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="13">
@@ -60999,7 +61633,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP1000"/>
+  <dimension ref="A1:AQ1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -61229,6 +61863,11 @@
           <t>Solar Pro 3 (high)</t>
         </is>
       </c>
+      <c r="AQ2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-5.5 Pro</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -61357,6 +61996,9 @@
       <c r="AP3" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AQ3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -61485,6 +62127,9 @@
       <c r="AP4" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AQ4" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -61613,6 +62258,9 @@
       <c r="AP5" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AQ5" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -61747,6 +62395,9 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AQ6" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -61873,6 +62524,9 @@
         <v>4</v>
       </c>
       <c r="AP7" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ7" s="24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -62003,6 +62657,9 @@
       <c r="AP8" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AQ8" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -62131,6 +62788,9 @@
       <c r="AP9" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AQ9" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -62259,6 +62919,9 @@
       <c r="AP10" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AQ10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -62387,6 +63050,9 @@
       <c r="AP11" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AQ11" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -62515,6 +63181,9 @@
       <c r="AP12" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AQ12" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -62643,6 +63312,9 @@
       <c r="AP13" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AQ13" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -62771,6 +63443,9 @@
       <c r="AP14" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AQ14" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -62899,6 +63574,9 @@
       <c r="AP15" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AQ15" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -63027,6 +63705,9 @@
       <c r="AP16" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AQ16" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -63155,6 +63836,9 @@
       <c r="AP17" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AQ17" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -63283,6 +63967,9 @@
       <c r="AP18" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AQ18" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -63411,6 +64098,9 @@
       <c r="AP19" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AQ19" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -63539,6 +64229,9 @@
       <c r="AP20" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AQ20" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -63667,6 +64360,9 @@
       <c r="AP21" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AQ21" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -63795,6 +64491,9 @@
       <c r="AP22" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AQ22" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -63923,6 +64622,9 @@
       <c r="AP23" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AQ23" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -64051,6 +64753,9 @@
       <c r="AP24" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AQ24" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -64179,6 +64884,9 @@
       <c r="AP25" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AQ25" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -64307,6 +65015,9 @@
       <c r="AP26" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AQ26" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -64439,6 +65150,9 @@
       <c r="AP27" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AQ27" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -64567,6 +65281,9 @@
       <c r="AP28" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AQ28" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -64695,6 +65412,9 @@
       <c r="AP29" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AQ29" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -64823,6 +65543,9 @@
       <c r="AP30" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AQ30" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -64951,6 +65674,9 @@
       <c r="AP31" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AQ31" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -65079,6 +65805,9 @@
       <c r="AP32" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AQ32" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -65209,6 +65938,9 @@
       <c r="AP33" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AQ33" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -65339,6 +66071,9 @@
       <c r="AP34" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AQ34" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -65469,6 +66204,9 @@
       <c r="AP35" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AQ35" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -65599,6 +66337,9 @@
       <c r="AP36" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AQ36" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -65729,6 +66470,9 @@
       <c r="AP37" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AQ37" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -65859,6 +66603,9 @@
       <c r="AP38" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AQ38" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -65989,6 +66736,9 @@
       <c r="AP39" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AQ39" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -66119,6 +66869,9 @@
       <c r="AP40" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AQ40" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -66249,6 +67002,9 @@
       <c r="AP41" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AQ41" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -66381,6 +67137,9 @@
       <c r="AP42" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AQ42" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -66511,6 +67270,9 @@
       <c r="AP43" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AQ43" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -66641,6 +67403,9 @@
       <c r="AP44" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AQ44" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -66771,6 +67536,9 @@
       <c r="AP45" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AQ45" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -66901,6 +67669,9 @@
       <c r="AP46" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AQ46" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -67031,6 +67802,9 @@
       <c r="AP47" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AQ47" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n"/>
@@ -67164,6 +67938,9 @@
       </c>
       <c r="AP49" s="24" t="n">
         <v>82</v>
+      </c>
+      <c r="AQ49" s="24" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="50">
@@ -70984,7 +71761,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP1000"/>
+  <dimension ref="A1:AQ1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -71215,6 +71992,11 @@
           <t>Solar Pro 3 (low)</t>
         </is>
       </c>
+      <c r="AQ2" s="23" t="inlineStr">
+        <is>
+          <t>GPT-5.5 Pro</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -71343,6 +72125,9 @@
       <c r="AP3" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AQ3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -71471,6 +72256,9 @@
       <c r="AP4" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AQ4" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -71599,6 +72387,9 @@
       <c r="AP5" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AQ5" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -71727,6 +72518,9 @@
       <c r="AP6" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AQ6" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -71854,6 +72648,9 @@
       </c>
       <c r="AP7" s="25" t="n">
         <v>5</v>
+      </c>
+      <c r="AQ7" s="24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -71983,6 +72780,9 @@
       <c r="AP8" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AQ8" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -72111,6 +72911,9 @@
       <c r="AP9" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AQ9" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -72239,6 +73042,9 @@
       <c r="AP10" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AQ10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -72367,6 +73173,9 @@
       <c r="AP11" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AQ11" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -72495,6 +73304,9 @@
       <c r="AP12" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AQ12" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -72623,6 +73435,9 @@
       <c r="AP13" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AQ13" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -72751,6 +73566,9 @@
       <c r="AP14" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AQ14" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -72879,6 +73697,9 @@
       <c r="AP15" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AQ15" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -73007,6 +73828,9 @@
       <c r="AP16" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AQ16" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -73135,6 +73959,9 @@
       <c r="AP17" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="AQ17" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -73263,6 +74090,9 @@
       <c r="AP18" s="26" t="n">
         <v>5</v>
       </c>
+      <c r="AQ18" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -73391,6 +74221,9 @@
       <c r="AP19" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AQ19" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -73519,6 +74352,9 @@
       <c r="AP20" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="AQ20" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -73647,6 +74483,9 @@
       <c r="AP21" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="AQ21" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -73775,6 +74614,9 @@
       <c r="AP22" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="AQ22" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n"/>
@@ -73908,6 +74750,9 @@
       </c>
       <c r="AP24" s="24" t="n">
         <v>40</v>
+      </c>
+      <c r="AQ24" s="24" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="25">

--- a/2026 수능 LLM 풀이 hard.xlsx
+++ b/2026 수능 LLM 풀이 hard.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ1000"/>
+  <dimension ref="A1:AW1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -715,6 +715,36 @@
           <t>GPT-5.5 Pro</t>
         </is>
       </c>
+      <c r="AR2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.7 Max (Thinking)</t>
+        </is>
+      </c>
+      <c r="AS2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.7 Max (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AT2" s="23" t="inlineStr">
+        <is>
+          <t>K-EXAONE 236B A23B (Thinking)</t>
+        </is>
+      </c>
+      <c r="AU2" s="23" t="inlineStr">
+        <is>
+          <t>K-EXAONE 236B A23B (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AV2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.6 27B (Thinking)</t>
+        </is>
+      </c>
+      <c r="AW2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.6 27B (Non-Thinking)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -846,6 +876,24 @@
       <c r="AQ3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -977,6 +1025,24 @@
       <c r="AQ4" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW4" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -1108,6 +1174,24 @@
       <c r="AQ5" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR5" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS5" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT5" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU5" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV5" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW5" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1241,6 +1325,24 @@
       <c r="AQ6" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW6" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -1372,6 +1474,24 @@
         </is>
       </c>
       <c r="AQ7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW7" s="24" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1507,6 +1627,24 @@
       <c r="AQ8" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW8" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -1640,6 +1778,24 @@
       <c r="AQ9" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR9" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS9" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT9" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU9" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV9" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW9" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -1773,6 +1929,24 @@
       <c r="AQ10" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR10" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS10" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT10" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU10" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV10" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW10" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -1906,6 +2080,24 @@
       <c r="AQ11" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR11" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS11" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT11" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU11" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV11" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW11" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -2037,6 +2229,24 @@
       <c r="AQ12" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR12" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS12" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT12" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU12" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV12" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW12" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -2170,6 +2380,24 @@
       <c r="AQ13" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW13" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -2301,6 +2529,24 @@
       <c r="AQ14" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW14" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -2432,6 +2678,24 @@
       <c r="AQ15" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR15" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS15" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT15" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU15" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV15" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW15" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -2563,6 +2827,26 @@
       <c r="AQ16" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR16" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS16" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT16" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU16" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AV16" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW16" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -2694,6 +2978,26 @@
       <c r="AQ17" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR17" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS17" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT17" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU17" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AV17" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW17" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -2825,6 +3129,26 @@
       <c r="AQ18" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR18" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS18" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT18" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU18" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AV18" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW18" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -2956,6 +3280,26 @@
       <c r="AQ19" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR19" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS19" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT19" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU19" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AV19" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW19" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -3087,6 +3431,26 @@
       <c r="AQ20" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT20" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU20" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AV20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW20" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -3218,6 +3582,26 @@
       <c r="AQ21" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR21" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS21" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT21" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU21" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AV21" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW21" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -3349,6 +3733,26 @@
       <c r="AQ22" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR22" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS22" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT22" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU22" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AV22" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW22" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -3480,6 +3884,26 @@
       <c r="AQ23" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR23" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS23" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT23" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU23" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AV23" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW23" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -3611,6 +4035,26 @@
       <c r="AQ24" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR24" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS24" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT24" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU24" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AV24" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW24" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -3742,6 +4186,26 @@
       <c r="AQ25" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR25" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS25" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT25" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU25" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AV25" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW25" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -3873,6 +4337,26 @@
       <c r="AQ26" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR26" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS26" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT26" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU26" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AV26" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW26" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -4004,6 +4488,26 @@
       <c r="AQ27" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR27" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS27" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT27" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU27" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AV27" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW27" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -4135,6 +4639,26 @@
       <c r="AQ28" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR28" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS28" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT28" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU28" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AV28" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW28" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -4268,6 +4792,26 @@
       <c r="AQ29" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR29" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS29" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT29" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU29" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AV29" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW29" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -4401,6 +4945,26 @@
       <c r="AQ30" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR30" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS30" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT30" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU30" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AV30" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW30" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -4534,6 +5098,26 @@
       <c r="AQ31" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR31" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS31" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT31" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU31" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AV31" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW31" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -4667,6 +5251,26 @@
       <c r="AQ32" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR32" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS32" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT32" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU32" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AV32" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW32" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -4800,6 +5404,26 @@
       <c r="AQ33" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR33" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS33" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT33" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU33" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AV33" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW33" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -4933,6 +5557,26 @@
       <c r="AQ34" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR34" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS34" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT34" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU34" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AV34" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW34" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -5066,6 +5710,26 @@
       <c r="AQ35" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR35" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS35" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT35" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU35" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AV35" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW35" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -5199,6 +5863,26 @@
       <c r="AQ36" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR36" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS36" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT36" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU36" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AV36" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW36" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n"/>
@@ -5335,6 +6019,24 @@
       </c>
       <c r="AQ38" s="24" t="n">
         <v>76</v>
+      </c>
+      <c r="AR38" s="24" t="n">
+        <v>68</v>
+      </c>
+      <c r="AS38" s="24" t="n">
+        <v>69</v>
+      </c>
+      <c r="AT38" s="24" t="n">
+        <v>43</v>
+      </c>
+      <c r="AU38" s="24" t="n">
+        <v>29</v>
+      </c>
+      <c r="AV38" s="24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AW38" s="24" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="39">
@@ -9199,7 +9901,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ1000"/>
+  <dimension ref="A1:AW1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -9431,6 +10133,36 @@
           <t>GPT-5.5 Pro</t>
         </is>
       </c>
+      <c r="AR2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.7 Max (Thinking)</t>
+        </is>
+      </c>
+      <c r="AS2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.6 27B (Thinking)</t>
+        </is>
+      </c>
+      <c r="AT2" s="23" t="inlineStr">
+        <is>
+          <t>K-EXAONE 236B A23B (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AU2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.7 Max (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AV2" s="23" t="inlineStr">
+        <is>
+          <t>K-EXAONE 236B A23B (Thinking)</t>
+        </is>
+      </c>
+      <c r="AW2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.6 27B (Non-Thinking)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
@@ -9568,6 +10300,28 @@
       <c r="AQ3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR3" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT3" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AU3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV3" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW3" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="n">
@@ -9709,6 +10463,24 @@
       <c r="AQ4" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT4" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV4" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW4" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="n">
@@ -9846,6 +10618,24 @@
       <c r="AQ5" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW5" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="n">
@@ -9989,6 +10779,24 @@
       <c r="AQ6" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR6" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS6" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT6" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU6" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV6" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW6" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="n">
@@ -10135,6 +10943,24 @@
       </c>
       <c r="AQ7" s="24" t="n">
         <v>1</v>
+      </c>
+      <c r="AR7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT7" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU7" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW7" s="25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -10285,6 +11111,26 @@
       <c r="AQ8" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR8" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS8" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT8" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AU8" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV8" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW8" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="n">
@@ -10432,6 +11278,28 @@
       <c r="AQ9" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR9" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS9" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AU9" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW9" s="25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="n">
@@ -10579,6 +11447,26 @@
       <c r="AQ10" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AU10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="n">
@@ -10724,6 +11612,26 @@
       <c r="AQ11" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT11" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AU11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW11" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="n">
@@ -10869,6 +11777,26 @@
       <c r="AQ12" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR12" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS12" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT12" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AU12" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV12" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW12" s="25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
@@ -11016,6 +11944,28 @@
       <c r="AQ13" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR13" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS13" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT13" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AU13" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV13" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW13" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="n">
@@ -11165,6 +12115,26 @@
       <c r="AQ14" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT14" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AU14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW14" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="n">
@@ -11318,6 +12288,28 @@
       <c r="AQ15" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR15" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS15" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT15" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AU15" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV15" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW15" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="n">
@@ -11469,6 +12461,28 @@
       <c r="AQ16" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR16" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS16" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT16" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AU16" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV16" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW16" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="n">
@@ -11620,6 +12634,28 @@
       <c r="AQ17" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR17" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS17" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT17" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AU17" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV17" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW17" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n">
@@ -11771,6 +12807,26 @@
       <c r="AQ18" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS18" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT18" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AU18" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW18" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="n">
@@ -11922,6 +12978,28 @@
       <c r="AQ19" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR19" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS19" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT19" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AU19" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV19" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW19" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="n">
@@ -12073,6 +13151,28 @@
       <c r="AQ20" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR20" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS20" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT20" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AU20" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV20" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW20" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="n">
@@ -12224,6 +13324,28 @@
       <c r="AQ21" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR21" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS21" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT21" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AU21" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV21" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW21" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="n">
@@ -12375,6 +13497,28 @@
       <c r="AQ22" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR22" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS22" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT22" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AU22" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV22" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW22" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="n"/>
@@ -12511,6 +13655,24 @@
       </c>
       <c r="AQ24" s="24" t="n">
         <v>50</v>
+      </c>
+      <c r="AR24" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS24" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT24" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU24" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AV24" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW24" s="24" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="25">
@@ -16431,7 +17593,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ1000"/>
+  <dimension ref="A1:AW1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -16663,6 +17825,36 @@
           <t>GPT-5.5 Pro</t>
         </is>
       </c>
+      <c r="AR2" s="23" t="inlineStr">
+        <is>
+          <t>K-EXAONE 236B A23B (Thinking)</t>
+        </is>
+      </c>
+      <c r="AS2" s="23" t="inlineStr">
+        <is>
+          <t>K-EXAONE 236B A23B (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AT2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.6 27B (Thinking)</t>
+        </is>
+      </c>
+      <c r="AU2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.7 Max (Thinking)</t>
+        </is>
+      </c>
+      <c r="AV2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.7 Max (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AW2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.6 27B (Non-Thinking)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
@@ -16808,6 +18000,24 @@
       <c r="AQ3" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR3" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS3" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT3" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU3" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV3" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW3" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="n">
@@ -16953,6 +18163,24 @@
       <c r="AQ4" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR4" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS4" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW4" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="n">
@@ -17100,6 +18328,24 @@
       <c r="AQ5" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR5" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS5" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW5" s="25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="n">
@@ -17247,6 +18493,24 @@
       <c r="AQ6" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV6" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW6" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="n">
@@ -17392,6 +18656,24 @@
         <v>1</v>
       </c>
       <c r="AQ7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR7" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS7" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW7" s="24" t="n">
         <v>2</v>
       </c>
     </row>
@@ -17543,6 +18825,24 @@
       <c r="AQ8" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR8" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS8" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT8" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU8" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV8" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW8" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="n">
@@ -17692,6 +18992,24 @@
       <c r="AQ9" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR9" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS9" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT9" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU9" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV9" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW9" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="n">
@@ -17843,6 +19161,24 @@
       <c r="AQ10" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR10" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS10" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="n">
@@ -17996,6 +19332,26 @@
       <c r="AQ11" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR11" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AS11" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT11" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU11" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV11" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW11" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="n">
@@ -18147,6 +19503,26 @@
       <c r="AQ12" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR12" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AS12" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV12" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW12" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
@@ -18302,6 +19678,26 @@
       <c r="AQ13" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR13" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AS13" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT13" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU13" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV13" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW13" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="n">
@@ -18455,6 +19851,26 @@
       <c r="AQ14" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR14" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AS14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV14" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW14" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="n">
@@ -18608,6 +20024,26 @@
       <c r="AQ15" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR15" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AS15" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT15" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU15" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV15" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW15" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="n">
@@ -18761,6 +20197,26 @@
       <c r="AQ16" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR16" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AS16" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT16" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU16" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV16" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW16" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="n">
@@ -18914,6 +20370,26 @@
       <c r="AQ17" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR17" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AS17" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT17" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU17" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV17" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW17" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n">
@@ -19071,6 +20547,26 @@
       <c r="AQ18" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR18" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AS18" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT18" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU18" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV18" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW18" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="n">
@@ -19226,6 +20722,26 @@
       <c r="AQ19" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR19" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AS19" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT19" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU19" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV19" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW19" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="n">
@@ -19383,6 +20899,26 @@
       <c r="AQ20" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR20" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AS20" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT20" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU20" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV20" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW20" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="n">
@@ -19542,6 +21078,26 @@
       <c r="AQ21" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR21" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AS21" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT21" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU21" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV21" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW21" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="n">
@@ -19699,6 +21255,26 @@
       <c r="AQ22" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR22" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AS22" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT22" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU22" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV22" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW22" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="n"/>
@@ -19835,6 +21411,24 @@
       </c>
       <c r="AQ24" s="24" t="n">
         <v>50</v>
+      </c>
+      <c r="AR24" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS24" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT24" s="24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AU24" s="24" t="n">
+        <v>48</v>
+      </c>
+      <c r="AV24" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW24" s="24" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="25">
@@ -23755,7 +25349,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ1000"/>
+  <dimension ref="A1:AW1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -23987,6 +25581,36 @@
           <t>GPT-5.5 Pro</t>
         </is>
       </c>
+      <c r="AR2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.7 Max (Thinking)</t>
+        </is>
+      </c>
+      <c r="AS2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.6 27B (Thinking)</t>
+        </is>
+      </c>
+      <c r="AT2" s="23" t="inlineStr">
+        <is>
+          <t>K-EXAONE 236B A23B (Thinking)</t>
+        </is>
+      </c>
+      <c r="AU2" s="23" t="inlineStr">
+        <is>
+          <t>K-EXAONE 236B A23B (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AV2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.7 Max (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AW2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.6 27B (Non-Thinking)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
@@ -24128,6 +25752,24 @@
       <c r="AQ3" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR3" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS3" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT3" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV3" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW3" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="n">
@@ -24269,6 +25911,24 @@
       <c r="AQ4" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW4" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="n">
@@ -24410,6 +26070,24 @@
       <c r="AQ5" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR5" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT5" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU5" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV5" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW5" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="n">
@@ -24551,6 +26229,24 @@
       <c r="AQ6" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW6" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="n">
@@ -24693,6 +26389,24 @@
       </c>
       <c r="AQ7" s="24" t="n">
         <v>4</v>
+      </c>
+      <c r="AR7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW7" s="25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -24837,6 +26551,24 @@
       <c r="AQ8" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR8" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS8" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT8" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU8" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV8" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW8" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="n">
@@ -24978,6 +26710,24 @@
       <c r="AQ9" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR9" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS9" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT9" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU9" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV9" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW9" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="n">
@@ -25119,6 +26869,26 @@
       <c r="AQ10" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="n">
@@ -25264,6 +27034,24 @@
       <c r="AQ11" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR11" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS11" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT11" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU11" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV11" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW11" s="25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="n">
@@ -25407,6 +27195,24 @@
       <c r="AQ12" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT12" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU12" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV12" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW12" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
@@ -25552,6 +27358,24 @@
       <c r="AQ13" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR13" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS13" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT13" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU13" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV13" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW13" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="n">
@@ -25695,6 +27519,24 @@
       <c r="AQ14" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU14" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV14" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW14" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="n">
@@ -25840,6 +27682,24 @@
       <c r="AQ15" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR15" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS15" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT15" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU15" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV15" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW15" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="n">
@@ -25987,6 +27847,24 @@
       <c r="AQ16" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR16" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS16" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT16" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU16" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV16" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW16" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="n">
@@ -26134,6 +28012,24 @@
       <c r="AQ17" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR17" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS17" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT17" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU17" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV17" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW17" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n">
@@ -26281,6 +28177,24 @@
       <c r="AQ18" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR18" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS18" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT18" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU18" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV18" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW18" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="n">
@@ -26428,6 +28342,24 @@
       <c r="AQ19" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR19" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS19" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT19" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU19" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV19" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW19" s="25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="n">
@@ -26575,6 +28507,24 @@
       <c r="AQ20" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR20" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS20" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT20" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU20" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV20" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW20" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="n">
@@ -26724,6 +28674,24 @@
       <c r="AQ21" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR21" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS21" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT21" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU21" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV21" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW21" s="25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="n">
@@ -26871,6 +28839,24 @@
       <c r="AQ22" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR22" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS22" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT22" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU22" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV22" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW22" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="n"/>
@@ -27007,6 +28993,24 @@
       </c>
       <c r="AQ24" s="24" t="n">
         <v>50</v>
+      </c>
+      <c r="AR24" s="24" t="n">
+        <v>27</v>
+      </c>
+      <c r="AS24" s="24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT24" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AU24" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AV24" s="24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW24" s="24" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="25">
@@ -30927,7 +32931,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ1000"/>
+  <dimension ref="A1:AW1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -31159,6 +33163,36 @@
           <t>GPT-5.5 Pro</t>
         </is>
       </c>
+      <c r="AR2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.6 27B (Thinking)</t>
+        </is>
+      </c>
+      <c r="AS2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.7 Max (Thinking)</t>
+        </is>
+      </c>
+      <c r="AT2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.7 Max (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AU2" s="23" t="inlineStr">
+        <is>
+          <t>K-EXAONE 236B A23B (Thinking)</t>
+        </is>
+      </c>
+      <c r="AV2" s="23" t="inlineStr">
+        <is>
+          <t>K-EXAONE 236B A23B (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AW2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.6 27B (Non-Thinking)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
@@ -31292,6 +33326,26 @@
       <c r="AQ3" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR3" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AS3" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT3" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU3" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV3" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW3" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="n">
@@ -31427,6 +33481,26 @@
       <c r="AQ4" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR4" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AS4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW4" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="n">
@@ -31562,6 +33636,26 @@
       <c r="AQ5" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR5" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AS5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW5" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="n">
@@ -31697,6 +33791,26 @@
       <c r="AQ6" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR6" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AS6" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT6" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU6" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV6" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW6" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="n">
@@ -31830,6 +33944,26 @@
         <v>1</v>
       </c>
       <c r="AQ7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR7" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AS7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW7" s="24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31969,6 +34103,26 @@
       <c r="AQ8" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR8" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AS8" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT8" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV8" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW8" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="n">
@@ -32106,6 +34260,26 @@
       <c r="AQ9" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="AR9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AS9" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT9" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV9" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW9" s="25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="n">
@@ -32243,6 +34417,26 @@
       <c r="AQ10" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AR10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AS10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT10" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV10" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW10" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="n">
@@ -32380,6 +34574,28 @@
       <c r="AQ11" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR11" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AS11" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT11" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU11" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV11" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW11" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="n">
@@ -32519,6 +34735,30 @@
       <c r="AQ12" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR12" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AS12" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT12" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU12" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AV12" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW12" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
@@ -32656,6 +34896,28 @@
       <c r="AQ13" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR13" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AS13" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT13" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU13" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV13" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW13" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="n">
@@ -32793,6 +35055,28 @@
       <c r="AQ14" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR14" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AS14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT14" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV14" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW14" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="n">
@@ -32932,6 +35216,28 @@
       <c r="AQ15" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR15" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AS15" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT15" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU15" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV15" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW15" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="n">
@@ -33069,6 +35375,30 @@
       <c r="AQ16" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR16" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AS16" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT16" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU16" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AV16" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW16" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="n">
@@ -33206,6 +35536,32 @@
       <c r="AQ17" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR17" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AS17" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT17" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU17" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AV17" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW17" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n">
@@ -33343,6 +35699,28 @@
       <c r="AQ18" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR18" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AS18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV18" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW18" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="n">
@@ -33480,6 +35858,28 @@
       <c r="AQ19" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR19" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AS19" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT19" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU19" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV19" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW19" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="n">
@@ -33617,6 +36017,28 @@
       <c r="AQ20" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR20" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AS20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV20" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW20" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="n">
@@ -33754,6 +36176,28 @@
       <c r="AQ21" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR21" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AS21" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT21" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU21" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV21" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW21" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="n">
@@ -33893,6 +36337,30 @@
       <c r="AQ22" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR22" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AS22" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT22" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU22" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AV22" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW22" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="n"/>
@@ -34029,6 +36497,24 @@
       </c>
       <c r="AQ24" s="24" t="n">
         <v>45</v>
+      </c>
+      <c r="AR24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" s="24" t="n">
+        <v>41</v>
+      </c>
+      <c r="AT24" s="24" t="n">
+        <v>27</v>
+      </c>
+      <c r="AU24" s="24" t="n">
+        <v>31</v>
+      </c>
+      <c r="AV24" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW24" s="24" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="25">
@@ -37949,7 +40435,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ1000"/>
+  <dimension ref="A1:AW1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -38183,6 +40669,36 @@
           <t>GPT-5.5 Pro</t>
         </is>
       </c>
+      <c r="AR2" s="23" t="inlineStr">
+        <is>
+          <t>K-EXAONE 236B A23B (Thinking)</t>
+        </is>
+      </c>
+      <c r="AS2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.6 27B (Thinking)</t>
+        </is>
+      </c>
+      <c r="AT2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.7 Max (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AU2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.6 27B (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AV2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.7 Max (Thinking)</t>
+        </is>
+      </c>
+      <c r="AW2" s="23" t="inlineStr">
+        <is>
+          <t>K-EXAONE 236B A23B (Non-Thinking)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -38314,6 +40830,24 @@
       <c r="AQ3" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR3" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS3" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT3" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU3" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV3" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW3" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -38445,6 +40979,24 @@
       <c r="AQ4" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW4" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -38578,6 +41130,24 @@
       <c r="AQ5" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW5" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -38711,6 +41281,24 @@
       <c r="AQ6" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT6" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU6" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW6" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -38844,6 +41432,24 @@
       <c r="AQ7" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT7" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU7" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW7" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -38977,6 +41583,24 @@
       <c r="AQ8" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU8" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW8" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -39110,6 +41734,24 @@
       <c r="AQ9" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW9" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -39243,6 +41885,24 @@
       <c r="AQ10" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR10" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS10" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT10" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU10" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV10" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW10" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -39376,6 +42036,24 @@
       <c r="AQ11" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW11" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -39509,6 +42187,24 @@
       <c r="AQ12" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR12" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS12" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT12" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU12" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV12" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW12" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -39644,6 +42340,24 @@
       <c r="AQ13" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR13" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS13" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT13" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU13" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV13" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW13" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
@@ -39780,6 +42494,24 @@
       </c>
       <c r="AQ15" s="24" t="n">
         <v>24</v>
+      </c>
+      <c r="AR15" s="24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS15" s="24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT15" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU15" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AV15" s="24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW15" s="24" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -43736,7 +46468,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ1000"/>
+  <dimension ref="A1:AW1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -43972,6 +46704,36 @@
           <t>GPT-5.5 Pro</t>
         </is>
       </c>
+      <c r="AR2" s="23" t="inlineStr">
+        <is>
+          <t>K-EXAONE 236B A23B (Thinking)</t>
+        </is>
+      </c>
+      <c r="AS2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.6 27B (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AT2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.6 27B (Thinking)</t>
+        </is>
+      </c>
+      <c r="AU2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.7 Max (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AV2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.7 Max (Thinking)</t>
+        </is>
+      </c>
+      <c r="AW2" s="23" t="inlineStr">
+        <is>
+          <t>K-EXAONE 236B A23B (Non-Thinking)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -44105,6 +46867,24 @@
       <c r="AQ3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -44240,6 +47020,24 @@
       <c r="AQ4" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS4" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU4" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW4" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -44377,6 +47175,24 @@
       <c r="AQ5" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR5" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS5" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT5" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU5" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV5" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW5" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -44512,6 +47328,24 @@
       <c r="AQ6" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR6" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS6" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT6" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU6" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV6" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW6" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -44647,6 +47481,24 @@
       <c r="AQ7" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS7" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT7" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV7" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW7" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -44782,6 +47634,24 @@
       <c r="AQ8" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS8" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW8" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -44919,6 +47789,24 @@
       <c r="AQ9" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR9" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS9" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT9" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW9" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -45054,6 +47942,24 @@
       <c r="AQ10" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -45189,6 +48095,24 @@
       <c r="AQ11" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR11" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS11" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT11" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU11" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV11" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW11" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -45324,6 +48248,24 @@
       <c r="AQ12" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR12" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS12" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT12" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU12" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV12" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW12" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -45459,6 +48401,24 @@
       <c r="AQ13" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW13" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
@@ -45595,6 +48555,24 @@
       </c>
       <c r="AQ15" s="24" t="n">
         <v>24</v>
+      </c>
+      <c r="AR15" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS15" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT15" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU15" s="24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AV15" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW15" s="24" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -49551,7 +52529,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ37"/>
+  <dimension ref="A1:AW37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -49783,6 +52761,36 @@
           <t>GPT-5.5 Pro</t>
         </is>
       </c>
+      <c r="AR2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.7 Max (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AS2" s="23" t="inlineStr">
+        <is>
+          <t>K-EXAONE 236B A23B (Thinking)</t>
+        </is>
+      </c>
+      <c r="AT2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.7 Max (Thinking)</t>
+        </is>
+      </c>
+      <c r="AU2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.6 27B (Thinking)</t>
+        </is>
+      </c>
+      <c r="AV2" s="23" t="inlineStr">
+        <is>
+          <t>K-EXAONE 236B A23B (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AW2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.6 27B (Non-Thinking)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -49918,6 +52926,24 @@
       <c r="AQ3" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR3" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS3" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT3" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV3" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW3" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -50053,6 +53079,24 @@
       <c r="AQ4" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW4" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -50188,6 +53232,24 @@
       <c r="AQ5" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR5" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS5" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT5" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU5" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV5" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW5" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -50323,6 +53385,24 @@
       <c r="AQ6" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW6" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -50457,6 +53537,24 @@
       </c>
       <c r="AQ7" s="24" t="n">
         <v>3</v>
+      </c>
+      <c r="AR7" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS7" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT7" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU7" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV7" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW7" s="25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -50593,6 +53691,24 @@
       <c r="AQ8" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW8" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -50728,6 +53844,24 @@
       <c r="AQ9" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR9" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS9" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT9" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU9" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV9" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW9" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -50865,6 +53999,24 @@
       <c r="AQ10" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR10" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS10" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT10" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU10" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV10" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW10" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -51002,6 +54154,24 @@
       <c r="AQ11" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR11" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS11" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT11" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU11" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV11" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW11" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -51145,6 +54315,24 @@
       <c r="AQ12" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR12" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS12" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT12" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU12" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV12" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW12" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -51284,6 +54472,26 @@
       <c r="AQ13" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR13" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV13" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW13" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -51423,6 +54631,26 @@
       <c r="AQ14" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV14" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW14" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -51562,6 +54790,26 @@
       <c r="AQ15" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR15" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS15" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT15" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU15" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV15" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW15" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -51705,6 +54953,26 @@
       <c r="AQ16" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR16" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS16" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT16" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU16" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV16" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW16" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -51850,6 +55118,26 @@
       <c r="AQ17" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR17" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS17" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT17" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU17" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV17" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW17" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -51989,6 +55277,26 @@
       <c r="AQ18" s="24" t="n">
         <v>9</v>
       </c>
+      <c r="AR18" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS18" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT18" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU18" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV18" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW18" s="24" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -52128,6 +55436,26 @@
       <c r="AQ19" s="24" t="n">
         <v>16</v>
       </c>
+      <c r="AR19" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS19" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT19" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU19" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AV19" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW19" s="24" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -52271,6 +55599,26 @@
       <c r="AQ20" s="24" t="n">
         <v>12</v>
       </c>
+      <c r="AR20" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS20" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT20" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU20" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV20" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW20" s="24" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -52414,6 +55762,26 @@
       <c r="AQ21" s="24" t="n">
         <v>15</v>
       </c>
+      <c r="AR21" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS21" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT21" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU21" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AV21" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW21" s="24" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -52565,6 +55933,28 @@
       <c r="AQ22" s="24" t="n">
         <v>130</v>
       </c>
+      <c r="AR22" s="25" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS22" s="24" t="n">
+        <v>130</v>
+      </c>
+      <c r="AT22" s="24" t="n">
+        <v>130</v>
+      </c>
+      <c r="AU22" s="24" t="n">
+        <v>130</v>
+      </c>
+      <c r="AV22" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW22" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -52722,6 +56112,28 @@
       <c r="AQ23" s="24" t="n">
         <v>65</v>
       </c>
+      <c r="AR23" s="25" t="n">
+        <v>245</v>
+      </c>
+      <c r="AS23" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AT23" s="24" t="n">
+        <v>65</v>
+      </c>
+      <c r="AU23" s="24" t="n">
+        <v>65</v>
+      </c>
+      <c r="AV23" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW23" s="25" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -52881,6 +56293,26 @@
       <c r="AQ24" s="24" t="n">
         <v>457</v>
       </c>
+      <c r="AR24" s="25" t="n">
+        <v>167</v>
+      </c>
+      <c r="AS24" s="24" t="n">
+        <v>457</v>
+      </c>
+      <c r="AT24" s="24" t="n">
+        <v>457</v>
+      </c>
+      <c r="AU24" s="24" t="n">
+        <v>457</v>
+      </c>
+      <c r="AV24" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW24" s="25" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n"/>
@@ -53017,6 +56449,24 @@
       </c>
       <c r="AQ26" s="24" t="n">
         <v>74</v>
+      </c>
+      <c r="AR26" s="24" t="n">
+        <v>54</v>
+      </c>
+      <c r="AS26" s="24" t="n">
+        <v>70</v>
+      </c>
+      <c r="AT26" s="24" t="n">
+        <v>74</v>
+      </c>
+      <c r="AU26" s="24" t="n">
+        <v>74</v>
+      </c>
+      <c r="AV26" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AW26" s="24" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="27">
@@ -53077,7 +56527,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ37"/>
+  <dimension ref="A1:AW37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -53309,6 +56759,36 @@
           <t>GPT-5.5 Pro</t>
         </is>
       </c>
+      <c r="AR2" s="23" t="inlineStr">
+        <is>
+          <t>K-EXAONE 236B A23B (Thinking)</t>
+        </is>
+      </c>
+      <c r="AS2" s="23" t="inlineStr">
+        <is>
+          <t>K-EXAONE 236B A23B (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AT2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.6 27B (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AU2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.7 Max (Thinking)</t>
+        </is>
+      </c>
+      <c r="AV2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.6 27B (Thinking)</t>
+        </is>
+      </c>
+      <c r="AW2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.7 Max (Non-Thinking)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -53440,6 +56920,24 @@
       <c r="AQ3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -53571,6 +57069,24 @@
       <c r="AQ4" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW4" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -53704,6 +57220,24 @@
       <c r="AQ5" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR5" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS5" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT5" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU5" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV5" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW5" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -53835,6 +57369,24 @@
       <c r="AQ6" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW6" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -53968,6 +57520,24 @@
       <c r="AQ7" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW7" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -54109,6 +57679,24 @@
       <c r="AQ8" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR8" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS8" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW8" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -54248,6 +57836,24 @@
       <c r="AQ9" s="24" t="n">
         <v>977</v>
       </c>
+      <c r="AR9" s="25" t="n">
+        <v>97</v>
+      </c>
+      <c r="AS9" s="25" t="n">
+        <v>97</v>
+      </c>
+      <c r="AT9" s="24" t="n">
+        <v>977</v>
+      </c>
+      <c r="AU9" s="24" t="n">
+        <v>977</v>
+      </c>
+      <c r="AV9" s="25" t="n">
+        <v>97</v>
+      </c>
+      <c r="AW9" s="24" t="n">
+        <v>977</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -54391,6 +57997,24 @@
       <c r="AQ10" s="24" t="n">
         <v>262</v>
       </c>
+      <c r="AR10" s="25" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS10" s="25" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT10" s="25" t="n">
+        <v>180</v>
+      </c>
+      <c r="AU10" s="24" t="n">
+        <v>262</v>
+      </c>
+      <c r="AV10" s="25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW10" s="25" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -54527,6 +58151,24 @@
       </c>
       <c r="AQ12" s="24" t="n">
         <v>26</v>
+      </c>
+      <c r="AR12" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS12" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT12" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AU12" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AV12" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW12" s="24" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -54639,7 +58281,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ1000"/>
+  <dimension ref="A1:AW1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -54873,6 +58515,36 @@
           <t>GPT-5.5 Pro</t>
         </is>
       </c>
+      <c r="AR2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.6 27B (Thinking)</t>
+        </is>
+      </c>
+      <c r="AS2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.7 Max (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AT2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.7 Max (Thinking)</t>
+        </is>
+      </c>
+      <c r="AU2" s="23" t="inlineStr">
+        <is>
+          <t>K-EXAONE 236B A23B (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AV2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.6 27B (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AW2" s="23" t="inlineStr">
+        <is>
+          <t>K-EXAONE 236B A23B (Thinking)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -55008,6 +58680,24 @@
       <c r="AQ3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -55143,6 +58833,24 @@
       <c r="AQ4" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW4" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -55278,6 +58986,24 @@
       <c r="AQ5" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW5" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -55413,6 +59139,24 @@
       <c r="AQ6" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW6" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -55548,6 +59292,24 @@
       <c r="AQ7" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW7" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -55683,6 +59445,24 @@
       <c r="AQ8" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW8" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -55822,6 +59602,28 @@
       <c r="AQ9" s="24" t="n">
         <v>97</v>
       </c>
+      <c r="AR9" s="24" t="n">
+        <v>97</v>
+      </c>
+      <c r="AS9" s="24" t="n">
+        <v>97</v>
+      </c>
+      <c r="AT9" s="24" t="n">
+        <v>97</v>
+      </c>
+      <c r="AU9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AV9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW9" s="24" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -55971,6 +59773,28 @@
       <c r="AQ10" s="24" t="n">
         <v>11</v>
       </c>
+      <c r="AR10" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS10" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT10" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AV10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AW10" s="25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -56107,6 +59931,24 @@
       </c>
       <c r="AQ12" s="24" t="n">
         <v>26</v>
+      </c>
+      <c r="AR12" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS12" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT12" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AU12" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AV12" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW12" s="24" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -60075,7 +63917,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ37"/>
+  <dimension ref="A1:AW37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -60307,6 +64149,36 @@
           <t>GPT-5.5 Pro</t>
         </is>
       </c>
+      <c r="AR2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.7 Max (Thinking)</t>
+        </is>
+      </c>
+      <c r="AS2" s="23" t="inlineStr">
+        <is>
+          <t>K-EXAONE 236B A23B (Thinking)</t>
+        </is>
+      </c>
+      <c r="AT2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.6 27B (Thinking)</t>
+        </is>
+      </c>
+      <c r="AU2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.6 27B (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AV2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.7 Max (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AW2" s="23" t="inlineStr">
+        <is>
+          <t>K-EXAONE 236B A23B (Non-Thinking)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -60440,6 +64312,24 @@
       <c r="AQ3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -60573,6 +64463,24 @@
       <c r="AQ4" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW4" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -60710,6 +64618,24 @@
       <c r="AQ5" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR5" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS5" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT5" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU5" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV5" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW5" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -60845,6 +64771,24 @@
       <c r="AQ6" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR6" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS6" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT6" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU6" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV6" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW6" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -60980,6 +64924,24 @@
       <c r="AQ7" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU7" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW7" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -61113,6 +65075,24 @@
       <c r="AQ8" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR8" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS8" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT8" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU8" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV8" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW8" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -61250,6 +65230,26 @@
       <c r="AQ9" s="24" t="n">
         <v>360</v>
       </c>
+      <c r="AR9" s="24" t="n">
+        <v>360</v>
+      </c>
+      <c r="AS9" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="AT9" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="AU9" s="25" t="n">
+        <v>27</v>
+      </c>
+      <c r="AV9" s="25" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -61385,6 +65385,28 @@
       <c r="AQ10" s="24" t="n">
         <v>221</v>
       </c>
+      <c r="AR10" s="24" t="n">
+        <v>221</v>
+      </c>
+      <c r="AS10" s="25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AU10" s="25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AV10" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -61521,6 +65543,24 @@
       </c>
       <c r="AQ12" s="24" t="n">
         <v>26</v>
+      </c>
+      <c r="AR12" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS12" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT12" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AU12" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV12" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW12" s="24" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -61633,7 +65673,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ1000"/>
+  <dimension ref="A1:AW1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -61868,6 +65908,36 @@
           <t>GPT-5.5 Pro</t>
         </is>
       </c>
+      <c r="AR2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.6 27B (Thinking)</t>
+        </is>
+      </c>
+      <c r="AS2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.7 Max (Thinking)</t>
+        </is>
+      </c>
+      <c r="AT2" s="23" t="inlineStr">
+        <is>
+          <t>K-EXAONE 236B A23B (Thinking)</t>
+        </is>
+      </c>
+      <c r="AU2" s="23" t="inlineStr">
+        <is>
+          <t>K-EXAONE 236B A23B (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AV2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.6 27B (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AW2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.7 Max (Non-Thinking)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -61999,6 +66069,24 @@
       <c r="AQ3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -62130,6 +66218,24 @@
       <c r="AQ4" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW4" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -62261,6 +66367,24 @@
       <c r="AQ5" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW5" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -62398,6 +66522,24 @@
       <c r="AQ6" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS6" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU6" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV6" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW6" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -62527,6 +66669,24 @@
         <v>1</v>
       </c>
       <c r="AQ7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW7" s="24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -62660,6 +66820,24 @@
       <c r="AQ8" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR8" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS8" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT8" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU8" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV8" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW8" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -62791,6 +66969,24 @@
       <c r="AQ9" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR9" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS9" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT9" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV9" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW9" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -62922,6 +67118,24 @@
       <c r="AQ10" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -63053,6 +67267,24 @@
       <c r="AQ11" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR11" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS11" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT11" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU11" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV11" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW11" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -63184,6 +67416,24 @@
       <c r="AQ12" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR12" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS12" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT12" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU12" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV12" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW12" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -63315,6 +67565,24 @@
       <c r="AQ13" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR13" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS13" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT13" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU13" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV13" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW13" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -63446,6 +67714,24 @@
       <c r="AQ14" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW14" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -63577,6 +67863,24 @@
       <c r="AQ15" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR15" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS15" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT15" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU15" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV15" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW15" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -63708,6 +68012,24 @@
       <c r="AQ16" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR16" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS16" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT16" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU16" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV16" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW16" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -63839,6 +68161,24 @@
       <c r="AQ17" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR17" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS17" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT17" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU17" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV17" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW17" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -63970,6 +68310,24 @@
       <c r="AQ18" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR18" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS18" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT18" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU18" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV18" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW18" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -64101,6 +68459,24 @@
       <c r="AQ19" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR19" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS19" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT19" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU19" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV19" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW19" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -64232,6 +68608,24 @@
       <c r="AQ20" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW20" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -64363,6 +68757,24 @@
       <c r="AQ21" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW21" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -64494,6 +68906,24 @@
       <c r="AQ22" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR22" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS22" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT22" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU22" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV22" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW22" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -64625,6 +69055,24 @@
       <c r="AQ23" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR23" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS23" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT23" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU23" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV23" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW23" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -64756,6 +69204,24 @@
       <c r="AQ24" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR24" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS24" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT24" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU24" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV24" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW24" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -64887,6 +69353,24 @@
       <c r="AQ25" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR25" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS25" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT25" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU25" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV25" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW25" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -65018,6 +69502,24 @@
       <c r="AQ26" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR26" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS26" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT26" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU26" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV26" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW26" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -65153,6 +69655,24 @@
       <c r="AQ27" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR27" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS27" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT27" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU27" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV27" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW27" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -65284,6 +69804,24 @@
       <c r="AQ28" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR28" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS28" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT28" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU28" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV28" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW28" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -65415,6 +69953,24 @@
       <c r="AQ29" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR29" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS29" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT29" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU29" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV29" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW29" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -65546,6 +70102,24 @@
       <c r="AQ30" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR30" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS30" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT30" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU30" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV30" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW30" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -65677,6 +70251,24 @@
       <c r="AQ31" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR31" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS31" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT31" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU31" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV31" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW31" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -65808,6 +70400,24 @@
       <c r="AQ32" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR32" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS32" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT32" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU32" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV32" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW32" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -65941,6 +70551,24 @@
       <c r="AQ33" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR33" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS33" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT33" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU33" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV33" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW33" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -66074,6 +70702,24 @@
       <c r="AQ34" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR34" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS34" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT34" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU34" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV34" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW34" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -66207,6 +70853,24 @@
       <c r="AQ35" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR35" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS35" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT35" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU35" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV35" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW35" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -66340,6 +71004,24 @@
       <c r="AQ36" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR36" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS36" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT36" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU36" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV36" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW36" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -66473,6 +71155,24 @@
       <c r="AQ37" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR37" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS37" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT37" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU37" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV37" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW37" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -66606,6 +71306,24 @@
       <c r="AQ38" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR38" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS38" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT38" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU38" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV38" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW38" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -66739,6 +71457,24 @@
       <c r="AQ39" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR39" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS39" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT39" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU39" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV39" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW39" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -66872,6 +71608,24 @@
       <c r="AQ40" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR40" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS40" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT40" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU40" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV40" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW40" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -67005,6 +71759,24 @@
       <c r="AQ41" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR41" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS41" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT41" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU41" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV41" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW41" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -67140,6 +71912,24 @@
       <c r="AQ42" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR42" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS42" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT42" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU42" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV42" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW42" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -67273,6 +72063,24 @@
       <c r="AQ43" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR43" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS43" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT43" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU43" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV43" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW43" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -67406,6 +72214,24 @@
       <c r="AQ44" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR44" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS44" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT44" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU44" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV44" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW44" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -67539,6 +72365,24 @@
       <c r="AQ45" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR45" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS45" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT45" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU45" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV45" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW45" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -67672,6 +72516,24 @@
       <c r="AQ46" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR46" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS46" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT46" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU46" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV46" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW46" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -67805,6 +72667,24 @@
       <c r="AQ47" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR47" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS47" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT47" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU47" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV47" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW47" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n"/>
@@ -67941,6 +72821,24 @@
       </c>
       <c r="AQ49" s="24" t="n">
         <v>100</v>
+      </c>
+      <c r="AR49" s="24" t="n">
+        <v>94</v>
+      </c>
+      <c r="AS49" s="24" t="n">
+        <v>98</v>
+      </c>
+      <c r="AT49" s="24" t="n">
+        <v>82</v>
+      </c>
+      <c r="AU49" s="24" t="n">
+        <v>81</v>
+      </c>
+      <c r="AV49" s="24" t="n">
+        <v>86</v>
+      </c>
+      <c r="AW49" s="24" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="50">
@@ -71761,7 +76659,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ1000"/>
+  <dimension ref="A1:AW1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -71997,6 +76895,36 @@
           <t>GPT-5.5 Pro</t>
         </is>
       </c>
+      <c r="AR2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.7 Max (Thinking)</t>
+        </is>
+      </c>
+      <c r="AS2" s="23" t="inlineStr">
+        <is>
+          <t>K-EXAONE 236B A23B (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AT2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.6 27B (Thinking)</t>
+        </is>
+      </c>
+      <c r="AU2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.7 Max (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AV2" s="23" t="inlineStr">
+        <is>
+          <t>K-EXAONE 236B A23B (Thinking)</t>
+        </is>
+      </c>
+      <c r="AW2" s="23" t="inlineStr">
+        <is>
+          <t>Qwen3.6 27B (Non-Thinking)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -72128,6 +77056,24 @@
       <c r="AQ3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR3" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU3" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV3" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -72259,6 +77205,26 @@
       <c r="AQ4" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR4" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS4" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AT4" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU4" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV4" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW4" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -72390,6 +77356,24 @@
       <c r="AQ5" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT5" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW5" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -72521,6 +77505,24 @@
       <c r="AQ6" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS6" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW6" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -72650,6 +77652,24 @@
         <v>5</v>
       </c>
       <c r="AQ7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW7" s="24" t="n">
         <v>2</v>
       </c>
     </row>
@@ -72783,6 +77803,24 @@
       <c r="AQ8" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT8" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV8" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW8" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -72914,6 +77952,24 @@
       <c r="AQ9" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW9" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -73045,6 +78101,24 @@
       <c r="AQ10" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -73176,6 +78250,24 @@
       <c r="AQ11" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW11" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -73307,6 +78399,24 @@
       <c r="AQ12" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW12" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -73438,6 +78548,24 @@
       <c r="AQ13" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW13" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -73569,6 +78697,24 @@
       <c r="AQ14" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT14" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW14" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -73700,6 +78846,24 @@
       <c r="AQ15" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR15" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS15" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT15" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU15" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV15" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW15" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -73831,6 +78995,24 @@
       <c r="AQ16" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR16" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS16" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT16" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU16" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV16" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW16" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -73962,6 +79144,24 @@
       <c r="AQ17" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AR17" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS17" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT17" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU17" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV17" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW17" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -74093,6 +79293,24 @@
       <c r="AQ18" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AR18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW18" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -74224,6 +79442,24 @@
       <c r="AQ19" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR19" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS19" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT19" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU19" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV19" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW19" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -74355,6 +79591,24 @@
       <c r="AQ20" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AR20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW20" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -74486,6 +79740,24 @@
       <c r="AQ21" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AR21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW21" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -74617,6 +79889,26 @@
       <c r="AQ22" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AR22" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS22" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AT22" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU22" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV22" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW22" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n"/>
@@ -74753,6 +80045,24 @@
       </c>
       <c r="AQ24" s="24" t="n">
         <v>50</v>
+      </c>
+      <c r="AR24" s="24" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS24" s="24" t="n">
+        <v>43</v>
+      </c>
+      <c r="AT24" s="24" t="n">
+        <v>41</v>
+      </c>
+      <c r="AU24" s="24" t="n">
+        <v>48</v>
+      </c>
+      <c r="AV24" s="24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AW24" s="24" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="25">

--- a/2026 수능 LLM 풀이 hard.xlsx
+++ b/2026 수능 LLM 풀이 hard.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW1000"/>
+  <dimension ref="A1:AZ1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -745,6 +745,21 @@
           <t>Qwen3.6 27B (Non-Thinking)</t>
         </is>
       </c>
+      <c r="AX2" s="23" t="inlineStr">
+        <is>
+          <t>Kimi K2.6 (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AY2" s="23" t="inlineStr">
+        <is>
+          <t>Kimi K2.6 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AZ2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro (32K Thinking)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -894,6 +909,15 @@
       <c r="AW3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -1043,6 +1067,15 @@
       <c r="AW4" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ4" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -1192,6 +1225,15 @@
       <c r="AW5" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AX5" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY5" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ5" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1343,6 +1385,15 @@
       <c r="AW6" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AX6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ6" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -1492,6 +1543,15 @@
         <v>4</v>
       </c>
       <c r="AW7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ7" s="24" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1645,6 +1705,15 @@
       <c r="AW8" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AX8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ8" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -1796,6 +1865,15 @@
       <c r="AW9" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX9" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY9" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ9" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -1947,6 +2025,15 @@
       <c r="AW10" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX10" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY10" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ10" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -2098,6 +2185,15 @@
       <c r="AW11" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX11" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY11" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ11" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -2247,6 +2343,15 @@
       <c r="AW12" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX12" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY12" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ12" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -2398,6 +2503,15 @@
       <c r="AW13" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ13" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -2547,6 +2661,15 @@
       <c r="AW14" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AX14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ14" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -2696,6 +2819,15 @@
       <c r="AW15" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AX15" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY15" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ15" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -2847,6 +2979,15 @@
       <c r="AW16" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX16" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY16" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ16" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -2998,6 +3139,15 @@
       <c r="AW17" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AX17" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY17" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ17" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -3149,6 +3299,15 @@
       <c r="AW18" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AX18" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY18" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ18" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -3300,6 +3459,15 @@
       <c r="AW19" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX19" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY19" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ19" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -3451,6 +3619,15 @@
       <c r="AW20" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AX20" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ20" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -3602,6 +3779,15 @@
       <c r="AW21" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AX21" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY21" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ21" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -3753,6 +3939,15 @@
       <c r="AW22" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX22" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY22" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ22" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -3904,6 +4099,15 @@
       <c r="AW23" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AX23" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY23" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ23" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -4055,6 +4259,15 @@
       <c r="AW24" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX24" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY24" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ24" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -4206,6 +4419,15 @@
       <c r="AW25" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AX25" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY25" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ25" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -4357,6 +4579,15 @@
       <c r="AW26" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AX26" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY26" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ26" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -4508,6 +4739,15 @@
       <c r="AW27" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AX27" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY27" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ27" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -4659,6 +4899,15 @@
       <c r="AW28" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AX28" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY28" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ28" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -4812,6 +5061,15 @@
       <c r="AW29" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX29" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY29" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ29" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -4965,6 +5223,15 @@
       <c r="AW30" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX30" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY30" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ30" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -5118,6 +5385,15 @@
       <c r="AW31" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AX31" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY31" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ31" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -5271,6 +5547,15 @@
       <c r="AW32" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX32" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY32" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ32" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -5424,6 +5709,15 @@
       <c r="AW33" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AX33" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY33" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ33" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -5577,6 +5871,15 @@
       <c r="AW34" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AX34" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY34" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ34" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -5730,6 +6033,15 @@
       <c r="AW35" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AX35" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY35" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ35" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -5883,6 +6195,15 @@
       <c r="AW36" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AX36" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY36" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ36" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n"/>
@@ -6037,6 +6358,15 @@
       </c>
       <c r="AW38" s="24" t="n">
         <v>63</v>
+      </c>
+      <c r="AX38" s="24" t="n">
+        <v>65</v>
+      </c>
+      <c r="AY38" s="24" t="n">
+        <v>74</v>
+      </c>
+      <c r="AZ38" s="24" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="39">
@@ -9901,7 +10231,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW1000"/>
+  <dimension ref="A1:AZ1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -10163,6 +10493,21 @@
           <t>Qwen3.6 27B (Non-Thinking)</t>
         </is>
       </c>
+      <c r="AX2" s="23" t="inlineStr">
+        <is>
+          <t>Kimi K2.6 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AY2" s="23" t="inlineStr">
+        <is>
+          <t>Kimi K2.6 (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AZ2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro (32K Thinking)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
@@ -10322,6 +10667,15 @@
       <c r="AW3" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AX3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY3" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="n">
@@ -10481,6 +10835,15 @@
       <c r="AW4" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AX4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY4" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ4" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="n">
@@ -10636,6 +10999,15 @@
       <c r="AW5" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ5" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="n">
@@ -10797,6 +11169,15 @@
       <c r="AW6" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AX6" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY6" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ6" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="n">
@@ -10961,6 +11342,15 @@
       </c>
       <c r="AW7" s="25" t="n">
         <v>4</v>
+      </c>
+      <c r="AX7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY7" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ7" s="24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -11131,6 +11521,15 @@
       <c r="AW8" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AX8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY8" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ8" s="25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="n">
@@ -11300,6 +11699,15 @@
       <c r="AW9" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="AX9" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY9" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ9" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="n">
@@ -11467,6 +11875,15 @@
       <c r="AW10" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="n">
@@ -11632,6 +12049,15 @@
       <c r="AW11" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ11" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="n">
@@ -11797,6 +12223,15 @@
       <c r="AW12" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="AX12" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY12" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ12" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
@@ -11966,6 +12401,15 @@
       <c r="AW13" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AX13" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY13" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ13" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="n">
@@ -12135,6 +12579,17 @@
       <c r="AW14" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AX14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ14" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="n">
@@ -12310,6 +12765,17 @@
       <c r="AW15" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX15" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY15" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ15" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="n">
@@ -12483,6 +12949,17 @@
       <c r="AW16" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AX16" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY16" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ16" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="n">
@@ -12656,6 +13133,17 @@
       <c r="AW17" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AX17" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY17" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ17" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n">
@@ -12827,6 +13315,17 @@
       <c r="AW18" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ18" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="n">
@@ -13000,6 +13499,17 @@
       <c r="AW19" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX19" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY19" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ19" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="n">
@@ -13173,6 +13683,17 @@
       <c r="AW20" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AX20" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY20" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ20" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="n">
@@ -13346,6 +13867,17 @@
       <c r="AW21" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AX21" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY21" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ21" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="n">
@@ -13519,6 +14051,17 @@
       <c r="AW22" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AX22" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY22" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ22" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="n"/>
@@ -13673,6 +14216,15 @@
       </c>
       <c r="AW24" s="24" t="n">
         <v>29</v>
+      </c>
+      <c r="AX24" s="24" t="n">
+        <v>30</v>
+      </c>
+      <c r="AY24" s="24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ24" s="24" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="25">
@@ -17593,7 +18145,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW1000"/>
+  <dimension ref="A1:AZ1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -17855,6 +18407,21 @@
           <t>Qwen3.6 27B (Non-Thinking)</t>
         </is>
       </c>
+      <c r="AX2" s="23" t="inlineStr">
+        <is>
+          <t>Kimi K2.6 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AY2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro (32K Thinking)</t>
+        </is>
+      </c>
+      <c r="AZ2" s="23" t="inlineStr">
+        <is>
+          <t>Kimi K2.6 (Non-Thinking)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
@@ -18018,6 +18585,15 @@
       <c r="AW3" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX3" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY3" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ3" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="n">
@@ -18181,6 +18757,15 @@
       <c r="AW4" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ4" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="n">
@@ -18346,6 +18931,15 @@
       <c r="AW5" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="AX5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ5" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="n">
@@ -18511,6 +19105,15 @@
       <c r="AW6" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AX6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ6" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="n">
@@ -18675,6 +19278,15 @@
       </c>
       <c r="AW7" s="24" t="n">
         <v>2</v>
+      </c>
+      <c r="AX7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ7" s="25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -18843,6 +19455,15 @@
       <c r="AW8" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AX8" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY8" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ8" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="n">
@@ -19010,6 +19631,15 @@
       <c r="AW9" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX9" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY9" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ9" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="n">
@@ -19179,6 +19809,15 @@
       <c r="AW10" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="n">
@@ -19352,6 +19991,15 @@
       <c r="AW11" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AX11" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY11" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ11" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="n">
@@ -19523,6 +20171,15 @@
       <c r="AW12" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AX12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ12" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
@@ -19698,6 +20355,15 @@
       <c r="AW13" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AX13" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY13" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ13" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="n">
@@ -19871,6 +20537,15 @@
       <c r="AW14" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AX14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ14" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="n">
@@ -20044,6 +20719,15 @@
       <c r="AW15" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AX15" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY15" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ15" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="n">
@@ -20217,6 +20901,15 @@
       <c r="AW16" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AX16" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY16" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ16" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="n">
@@ -20390,6 +21083,15 @@
       <c r="AW17" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AX17" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY17" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ17" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n">
@@ -20567,6 +21269,15 @@
       <c r="AW18" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AX18" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY18" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ18" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="n">
@@ -20742,6 +21453,15 @@
       <c r="AW19" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX19" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY19" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ19" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="n">
@@ -20919,6 +21639,15 @@
       <c r="AW20" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX20" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY20" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ20" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="n">
@@ -21098,6 +21827,15 @@
       <c r="AW21" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AX21" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY21" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ21" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="n">
@@ -21275,6 +22013,15 @@
       <c r="AW22" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AX22" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY22" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ22" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="n"/>
@@ -21429,6 +22176,15 @@
       </c>
       <c r="AW24" s="24" t="n">
         <v>29</v>
+      </c>
+      <c r="AX24" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AY24" s="24" t="n">
+        <v>45</v>
+      </c>
+      <c r="AZ24" s="24" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="25">
@@ -25349,7 +26105,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW1000"/>
+  <dimension ref="A1:AZ1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -25611,6 +26367,21 @@
           <t>Qwen3.6 27B (Non-Thinking)</t>
         </is>
       </c>
+      <c r="AX2" s="23" t="inlineStr">
+        <is>
+          <t>Kimi K2.6 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AY2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro (32K Thinking)</t>
+        </is>
+      </c>
+      <c r="AZ2" s="23" t="inlineStr">
+        <is>
+          <t>Kimi K2.6 (Non-Thinking)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
@@ -25770,6 +26541,17 @@
       <c r="AW3" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX3" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY3" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AZ3" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="n">
@@ -25929,6 +26711,17 @@
       <c r="AW4" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AX4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY4" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AZ4" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="n">
@@ -26088,6 +26881,17 @@
       <c r="AW5" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AX5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY5" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AZ5" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="n">
@@ -26247,6 +27051,17 @@
       <c r="AW6" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY6" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AZ6" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="n">
@@ -26407,6 +27222,17 @@
       </c>
       <c r="AW7" s="25" t="n">
         <v>2</v>
+      </c>
+      <c r="AX7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY7" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AZ7" s="24" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -26569,6 +27395,17 @@
       <c r="AW8" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX8" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY8" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AZ8" s="25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="n">
@@ -26728,6 +27565,17 @@
       <c r="AW9" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX9" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AZ9" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="n">
@@ -26889,6 +27737,17 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AX10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AZ10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="n">
@@ -27052,6 +27911,17 @@
       <c r="AW11" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="AX11" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY11" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AZ11" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="n">
@@ -27213,6 +28083,17 @@
       <c r="AW12" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AX12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY12" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AZ12" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
@@ -27376,6 +28257,17 @@
       <c r="AW13" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AX13" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY13" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AZ13" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="n">
@@ -27537,6 +28429,17 @@
       <c r="AW14" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AX14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY14" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AZ14" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="n">
@@ -27700,6 +28603,17 @@
       <c r="AW15" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AX15" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY15" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AZ15" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="n">
@@ -27865,6 +28779,17 @@
       <c r="AW16" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AX16" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY16" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AZ16" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="n">
@@ -28030,6 +28955,17 @@
       <c r="AW17" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AX17" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY17" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AZ17" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n">
@@ -28195,6 +29131,17 @@
       <c r="AW18" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AX18" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY18" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AZ18" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="n">
@@ -28360,6 +29307,17 @@
       <c r="AW19" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="AX19" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY19" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AZ19" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="n">
@@ -28525,6 +29483,17 @@
       <c r="AW20" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AX20" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY20" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AZ20" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="n">
@@ -28692,6 +29661,17 @@
       <c r="AW21" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="AX21" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY21" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AZ21" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="n">
@@ -28857,6 +29837,17 @@
       <c r="AW22" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AX22" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY22" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
+      <c r="AZ22" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="n"/>
@@ -29011,6 +30002,15 @@
       </c>
       <c r="AW24" s="24" t="n">
         <v>22</v>
+      </c>
+      <c r="AX24" s="24" t="n">
+        <v>31</v>
+      </c>
+      <c r="AY24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" s="24" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="25">
@@ -32931,7 +33931,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW1000"/>
+  <dimension ref="A1:AZ1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -33193,6 +34193,21 @@
           <t>Qwen3.6 27B (Non-Thinking)</t>
         </is>
       </c>
+      <c r="AX2" s="23" t="inlineStr">
+        <is>
+          <t>Kimi K2.6 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AY2" s="23" t="inlineStr">
+        <is>
+          <t>Kimi K2.6 (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AZ2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro (32K Thinking)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
@@ -33346,6 +34361,15 @@
       <c r="AW3" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AX3" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY3" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ3" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="n">
@@ -33501,6 +34525,15 @@
       <c r="AW4" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AX4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ4" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="n">
@@ -33656,6 +34689,15 @@
       <c r="AW5" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AX5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ5" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="n">
@@ -33811,6 +34853,15 @@
       <c r="AW6" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AX6" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY6" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ6" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="n">
@@ -33964,6 +35015,15 @@
         <v>1</v>
       </c>
       <c r="AW7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ7" s="24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -34123,6 +35183,15 @@
       <c r="AW8" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AX8" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY8" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ8" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="n">
@@ -34280,6 +35349,15 @@
       <c r="AW9" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="AX9" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY9" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ9" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="n">
@@ -34437,6 +35515,15 @@
       <c r="AW10" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AX10" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY10" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ10" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="n">
@@ -34596,6 +35683,15 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AX11" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY11" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ11" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="n">
@@ -34759,6 +35855,15 @@
       <c r="AW12" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AX12" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY12" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ12" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
@@ -34918,6 +36023,15 @@
       <c r="AW13" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AX13" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY13" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ13" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="n">
@@ -35077,6 +36191,15 @@
       <c r="AW14" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AX14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ14" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="n">
@@ -35238,6 +36361,15 @@
       <c r="AW15" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AX15" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY15" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ15" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="n">
@@ -35399,6 +36531,15 @@
       <c r="AW16" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AX16" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY16" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ16" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="n">
@@ -35562,6 +36703,17 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AX17" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY17" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ17" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n">
@@ -35721,6 +36873,17 @@
       <c r="AW18" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ18" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="n">
@@ -35880,6 +37043,17 @@
       <c r="AW19" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AX19" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY19" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ19" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="n">
@@ -36039,6 +37213,17 @@
       <c r="AW20" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AX20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ20" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="n">
@@ -36198,6 +37383,17 @@
       <c r="AW21" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX21" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY21" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ21" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="n">
@@ -36361,6 +37557,17 @@
       <c r="AW22" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX22" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY22" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ22" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="n"/>
@@ -36515,6 +37722,15 @@
       </c>
       <c r="AW24" s="24" t="n">
         <v>26</v>
+      </c>
+      <c r="AX24" s="24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AY24" s="24" t="n">
+        <v>43</v>
+      </c>
+      <c r="AZ24" s="24" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="25">
@@ -40435,7 +41651,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW1000"/>
+  <dimension ref="A1:AZ1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -40699,6 +41915,21 @@
           <t>K-EXAONE 236B A23B (Non-Thinking)</t>
         </is>
       </c>
+      <c r="AX2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro (32K Thinking)</t>
+        </is>
+      </c>
+      <c r="AY2" s="23" t="inlineStr">
+        <is>
+          <t>Kimi K2.6 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AZ2" s="23" t="inlineStr">
+        <is>
+          <t>Kimi K2.6 (Non-Thinking)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -40848,6 +42079,15 @@
       <c r="AW3" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AX3" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY3" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ3" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -40997,6 +42237,15 @@
       <c r="AW4" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AX4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ4" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -41148,6 +42397,15 @@
       <c r="AW5" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ5" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -41299,6 +42557,15 @@
       <c r="AW6" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AX6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ6" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -41450,6 +42717,15 @@
       <c r="AW7" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AX7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ7" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -41601,6 +42877,15 @@
       <c r="AW8" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ8" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -41752,6 +43037,15 @@
       <c r="AW9" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AX9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ9" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -41903,6 +43197,15 @@
       <c r="AW10" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AX10" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY10" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ10" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -42054,6 +43357,15 @@
       <c r="AW11" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ11" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -42205,6 +43517,15 @@
       <c r="AW12" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AX12" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY12" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ12" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -42358,6 +43679,15 @@
       <c r="AW13" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX13" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY13" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ13" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
@@ -42511,6 +43841,15 @@
         <v>24</v>
       </c>
       <c r="AW15" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX15" s="24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AY15" s="24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ15" s="24" t="n">
         <v>20</v>
       </c>
     </row>
@@ -46468,7 +47807,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW1000"/>
+  <dimension ref="A1:AZ1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -46734,6 +48073,21 @@
           <t>K-EXAONE 236B A23B (Non-Thinking)</t>
         </is>
       </c>
+      <c r="AX2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro (32K Thinking)</t>
+        </is>
+      </c>
+      <c r="AY2" s="23" t="inlineStr">
+        <is>
+          <t>Kimi K2.6 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AZ2" s="23" t="inlineStr">
+        <is>
+          <t>Kimi K2.6 (Non-Thinking)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -46885,6 +48239,15 @@
       <c r="AW3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -47038,6 +48401,15 @@
       <c r="AW4" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AX4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY4" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ4" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -47193,6 +48565,15 @@
       <c r="AW5" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AX5" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY5" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ5" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -47346,6 +48727,15 @@
       <c r="AW6" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AX6" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY6" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ6" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -47499,6 +48889,15 @@
       <c r="AW7" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AX7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ7" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -47652,6 +49051,15 @@
       <c r="AW8" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AX8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ8" s="25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -47807,6 +49215,15 @@
       <c r="AW9" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AX9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ9" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -47960,6 +49377,15 @@
       <c r="AW10" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -48113,6 +49539,15 @@
       <c r="AW11" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AX11" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY11" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ11" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -48266,6 +49701,15 @@
       <c r="AW12" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AX12" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY12" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ12" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -48419,6 +49863,15 @@
       <c r="AW13" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AX13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ13" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
@@ -48573,6 +50026,15 @@
       </c>
       <c r="AW15" s="24" t="n">
         <v>9</v>
+      </c>
+      <c r="AX15" s="24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AY15" s="24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ15" s="24" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -52529,7 +53991,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW37"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -52791,6 +54253,21 @@
           <t>Qwen3.6 27B (Non-Thinking)</t>
         </is>
       </c>
+      <c r="AX2" s="23" t="inlineStr">
+        <is>
+          <t>Kimi K2.6 (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AY2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro (32K Thinking)</t>
+        </is>
+      </c>
+      <c r="AZ2" s="23" t="inlineStr">
+        <is>
+          <t>Kimi K2.6 (Thinking)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -52944,6 +54421,15 @@
       <c r="AW3" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AX3" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY3" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ3" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -53097,6 +54583,15 @@
       <c r="AW4" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AX4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ4" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -53250,6 +54745,15 @@
       <c r="AW5" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX5" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY5" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ5" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -53403,6 +54907,15 @@
       <c r="AW6" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ6" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -53555,6 +55068,15 @@
       </c>
       <c r="AW7" s="25" t="n">
         <v>4</v>
+      </c>
+      <c r="AX7" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY7" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ7" s="24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -53709,6 +55231,15 @@
       <c r="AW8" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AX8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ8" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -53862,6 +55393,15 @@
       <c r="AW9" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX9" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY9" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ9" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -54017,6 +55557,15 @@
       <c r="AW10" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AX10" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY10" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ10" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -54172,6 +55721,15 @@
       <c r="AW11" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AX11" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY11" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ11" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -54333,6 +55891,15 @@
       <c r="AW12" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX12" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY12" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ12" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -54492,6 +56059,15 @@
       <c r="AW13" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ13" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -54651,6 +56227,15 @@
       <c r="AW14" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AX14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ14" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -54810,6 +56395,15 @@
       <c r="AW15" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AX15" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY15" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ15" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -54973,6 +56567,15 @@
       <c r="AW16" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AX16" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY16" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ16" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -55138,6 +56741,15 @@
       <c r="AW17" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AX17" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY17" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ17" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -55297,6 +56909,15 @@
       <c r="AW18" s="24" t="n">
         <v>9</v>
       </c>
+      <c r="AX18" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY18" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ18" s="24" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -55456,6 +57077,15 @@
       <c r="AW19" s="24" t="n">
         <v>16</v>
       </c>
+      <c r="AX19" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY19" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ19" s="24" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -55619,6 +57249,15 @@
       <c r="AW20" s="24" t="n">
         <v>12</v>
       </c>
+      <c r="AX20" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY20" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ20" s="24" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -55782,6 +57421,15 @@
       <c r="AW21" s="24" t="n">
         <v>15</v>
       </c>
+      <c r="AX21" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY21" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ21" s="24" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -55955,6 +57603,15 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AX22" s="24" t="n">
+        <v>130</v>
+      </c>
+      <c r="AY22" s="24" t="n">
+        <v>130</v>
+      </c>
+      <c r="AZ22" s="24" t="n">
+        <v>130</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -56134,6 +57791,15 @@
       <c r="AW23" s="25" t="n">
         <v>60</v>
       </c>
+      <c r="AX23" s="25" t="n">
+        <v>50</v>
+      </c>
+      <c r="AY23" s="24" t="n">
+        <v>65</v>
+      </c>
+      <c r="AZ23" s="24" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -56313,6 +57979,15 @@
       <c r="AW24" s="25" t="n">
         <v>49</v>
       </c>
+      <c r="AX24" s="24" t="n">
+        <v>457</v>
+      </c>
+      <c r="AY24" s="24" t="n">
+        <v>457</v>
+      </c>
+      <c r="AZ24" s="24" t="n">
+        <v>457</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n"/>
@@ -56467,6 +58142,15 @@
       </c>
       <c r="AW26" s="24" t="n">
         <v>51</v>
+      </c>
+      <c r="AX26" s="24" t="n">
+        <v>70</v>
+      </c>
+      <c r="AY26" s="24" t="n">
+        <v>74</v>
+      </c>
+      <c r="AZ26" s="24" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="27">
@@ -56527,7 +58211,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW37"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -56789,6 +58473,21 @@
           <t>Qwen3.7 Max (Non-Thinking)</t>
         </is>
       </c>
+      <c r="AX2" s="23" t="inlineStr">
+        <is>
+          <t>Kimi K2.6 (Non-Thinking)</t>
+        </is>
+      </c>
+      <c r="AY2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro (32K Thinking)</t>
+        </is>
+      </c>
+      <c r="AZ2" s="23" t="inlineStr">
+        <is>
+          <t>Kimi K2.6 (Thinking)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -56938,6 +58637,15 @@
       <c r="AW3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -57087,6 +58795,15 @@
       <c r="AW4" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AX4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ4" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -57238,6 +58955,15 @@
       <c r="AW5" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AX5" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY5" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ5" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -57387,6 +59113,15 @@
       <c r="AW6" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ6" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -57538,6 +59273,15 @@
       <c r="AW7" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AX7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ7" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -57697,6 +59441,15 @@
       <c r="AW8" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AX8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ8" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -57854,6 +59607,15 @@
       <c r="AW9" s="24" t="n">
         <v>977</v>
       </c>
+      <c r="AX9" s="24" t="n">
+        <v>977</v>
+      </c>
+      <c r="AY9" s="24" t="n">
+        <v>977</v>
+      </c>
+      <c r="AZ9" s="24" t="n">
+        <v>977</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -58015,6 +59777,15 @@
       <c r="AW10" s="25" t="n">
         <v>56</v>
       </c>
+      <c r="AX10" s="24" t="n">
+        <v>262</v>
+      </c>
+      <c r="AY10" s="24" t="n">
+        <v>262</v>
+      </c>
+      <c r="AZ10" s="24" t="n">
+        <v>262</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -58169,6 +59940,15 @@
       </c>
       <c r="AW12" s="24" t="n">
         <v>22</v>
+      </c>
+      <c r="AX12" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AY12" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AZ12" s="24" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="13">
@@ -58281,7 +60061,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW1000"/>
+  <dimension ref="A1:AZ1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -58545,6 +60325,21 @@
           <t>K-EXAONE 236B A23B (Thinking)</t>
         </is>
       </c>
+      <c r="AX2" s="23" t="inlineStr">
+        <is>
+          <t>Kimi K2.6 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AY2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro (32K Thinking)</t>
+        </is>
+      </c>
+      <c r="AZ2" s="23" t="inlineStr">
+        <is>
+          <t>Kimi K2.6 (Non-Thinking)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -58698,6 +60493,15 @@
       <c r="AW3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -58851,6 +60655,15 @@
       <c r="AW4" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AX4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ4" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -59004,6 +60817,15 @@
       <c r="AW5" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ5" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -59157,6 +60979,15 @@
       <c r="AW6" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AX6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ6" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -59310,6 +61141,15 @@
       <c r="AW7" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AX7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ7" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -59463,6 +61303,15 @@
       <c r="AW8" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ8" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -59624,6 +61473,15 @@
       <c r="AW9" s="24" t="n">
         <v>97</v>
       </c>
+      <c r="AX9" s="24" t="n">
+        <v>97</v>
+      </c>
+      <c r="AY9" s="24" t="n">
+        <v>97</v>
+      </c>
+      <c r="AZ9" s="24" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -59795,6 +61653,15 @@
       <c r="AW10" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="AX10" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY10" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ10" s="25" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -59948,6 +61815,15 @@
         <v>18</v>
       </c>
       <c r="AW12" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX12" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AY12" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AZ12" s="24" t="n">
         <v>22</v>
       </c>
     </row>
@@ -63917,7 +65793,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW37"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -64179,6 +66055,21 @@
           <t>K-EXAONE 236B A23B (Non-Thinking)</t>
         </is>
       </c>
+      <c r="AX2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro (32K Thinking)</t>
+        </is>
+      </c>
+      <c r="AY2" s="23" t="inlineStr">
+        <is>
+          <t>Kimi K2.6 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AZ2" s="23" t="inlineStr">
+        <is>
+          <t>Kimi K2.6 (Non-Thinking)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -64330,6 +66221,15 @@
       <c r="AW3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -64481,6 +66381,15 @@
       <c r="AW4" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AX4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ4" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -64636,6 +66545,15 @@
       <c r="AW5" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX5" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY5" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ5" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -64789,6 +66707,15 @@
       <c r="AW6" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AX6" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY6" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ6" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -64942,6 +66869,15 @@
       <c r="AW7" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AX7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ7" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -65093,6 +67029,15 @@
       <c r="AW8" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AX8" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY8" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ8" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -65250,6 +67195,15 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AX9" s="24" t="n">
+        <v>360</v>
+      </c>
+      <c r="AY9" s="24" t="n">
+        <v>360</v>
+      </c>
+      <c r="AZ9" s="25" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -65407,6 +67361,15 @@
           <t>(포기)</t>
         </is>
       </c>
+      <c r="AX10" s="24" t="n">
+        <v>221</v>
+      </c>
+      <c r="AY10" s="24" t="n">
+        <v>221</v>
+      </c>
+      <c r="AZ10" s="24" t="n">
+        <v>221</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -65561,6 +67524,15 @@
       </c>
       <c r="AW12" s="24" t="n">
         <v>14</v>
+      </c>
+      <c r="AX12" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AY12" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AZ12" s="24" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -65673,7 +67645,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW1000"/>
+  <dimension ref="A1:AZ1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -65938,6 +67910,21 @@
           <t>Qwen3.7 Max (Non-Thinking)</t>
         </is>
       </c>
+      <c r="AX2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro (32K Thinking)</t>
+        </is>
+      </c>
+      <c r="AY2" s="23" t="inlineStr">
+        <is>
+          <t>Kimi K2.6 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AZ2" s="23" t="inlineStr">
+        <is>
+          <t>Kimi K2.6 (Non-Thinking)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -66087,6 +68074,15 @@
       <c r="AW3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -66236,6 +68232,15 @@
       <c r="AW4" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AX4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ4" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -66385,6 +68390,15 @@
       <c r="AW5" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AX5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ5" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -66540,6 +68554,15 @@
       <c r="AW6" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AX6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ6" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -66687,6 +68710,15 @@
         <v>1</v>
       </c>
       <c r="AW7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ7" s="24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -66838,6 +68870,15 @@
       <c r="AW8" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AX8" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY8" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ8" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -66987,6 +69028,15 @@
       <c r="AW9" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AX9" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY9" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ9" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -67136,6 +69186,15 @@
       <c r="AW10" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -67285,6 +69344,15 @@
       <c r="AW11" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AX11" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY11" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ11" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -67434,6 +69502,15 @@
       <c r="AW12" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AX12" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY12" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ12" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -67583,6 +69660,15 @@
       <c r="AW13" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AX13" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY13" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ13" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -67732,6 +69818,15 @@
       <c r="AW14" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AX14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ14" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -67881,6 +69976,15 @@
       <c r="AW15" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AX15" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY15" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ15" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -68030,6 +70134,15 @@
       <c r="AW16" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX16" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY16" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ16" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -68179,6 +70292,15 @@
       <c r="AW17" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX17" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY17" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ17" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -68328,6 +70450,15 @@
       <c r="AW18" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AX18" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY18" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ18" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -68477,6 +70608,15 @@
       <c r="AW19" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX19" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY19" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ19" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -68626,6 +70766,15 @@
       <c r="AW20" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AX20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ20" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -68775,6 +70924,15 @@
       <c r="AW21" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AX21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ21" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -68924,6 +71082,15 @@
       <c r="AW22" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AX22" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY22" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ22" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -69073,6 +71240,15 @@
       <c r="AW23" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AX23" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY23" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ23" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -69222,6 +71398,15 @@
       <c r="AW24" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AX24" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY24" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ24" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -69371,6 +71556,15 @@
       <c r="AW25" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX25" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY25" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ25" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -69520,6 +71714,15 @@
       <c r="AW26" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AX26" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY26" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ26" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -69673,6 +71876,15 @@
       <c r="AW27" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AX27" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY27" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ27" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -69822,6 +72034,15 @@
       <c r="AW28" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX28" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY28" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ28" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -69971,6 +72192,15 @@
       <c r="AW29" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AX29" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY29" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ29" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -70120,6 +72350,15 @@
       <c r="AW30" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AX30" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY30" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ30" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -70269,6 +72508,15 @@
       <c r="AW31" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AX31" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY31" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ31" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -70418,6 +72666,15 @@
       <c r="AW32" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX32" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY32" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ32" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -70569,6 +72826,15 @@
       <c r="AW33" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AX33" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY33" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ33" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -70720,6 +72986,15 @@
       <c r="AW34" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX34" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY34" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ34" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -70871,6 +73146,15 @@
       <c r="AW35" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AX35" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY35" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ35" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -71022,6 +73306,15 @@
       <c r="AW36" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX36" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY36" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ36" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -71173,6 +73466,15 @@
       <c r="AW37" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AX37" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY37" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ37" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -71324,6 +73626,15 @@
       <c r="AW38" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AX38" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY38" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ38" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -71475,6 +73786,15 @@
       <c r="AW39" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX39" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY39" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ39" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -71626,6 +73946,15 @@
       <c r="AW40" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX40" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY40" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ40" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -71777,6 +74106,15 @@
       <c r="AW41" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX41" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY41" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ41" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -71930,6 +74268,15 @@
       <c r="AW42" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX42" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY42" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ42" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -72081,6 +74428,15 @@
       <c r="AW43" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AX43" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY43" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ43" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -72232,6 +74588,15 @@
       <c r="AW44" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX44" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY44" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ44" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -72383,6 +74748,15 @@
       <c r="AW45" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX45" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY45" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ45" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -72534,6 +74908,15 @@
       <c r="AW46" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX46" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY46" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ46" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -72685,6 +75068,15 @@
       <c r="AW47" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX47" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY47" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ47" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n"/>
@@ -72839,6 +75231,15 @@
       </c>
       <c r="AW49" s="24" t="n">
         <v>96</v>
+      </c>
+      <c r="AX49" s="24" t="n">
+        <v>100</v>
+      </c>
+      <c r="AY49" s="24" t="n">
+        <v>92</v>
+      </c>
+      <c r="AZ49" s="24" t="n">
+        <v>93</v>
       </c>
     </row>
     <row r="50">
@@ -76659,7 +79060,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW1000"/>
+  <dimension ref="A1:AZ1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -76925,6 +79326,21 @@
           <t>Qwen3.6 27B (Non-Thinking)</t>
         </is>
       </c>
+      <c r="AX2" s="23" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro (32K Thinking)</t>
+        </is>
+      </c>
+      <c r="AY2" s="23" t="inlineStr">
+        <is>
+          <t>Kimi K2.6 (Thinking)</t>
+        </is>
+      </c>
+      <c r="AZ2" s="23" t="inlineStr">
+        <is>
+          <t>Kimi K2.6 (Non-Thinking)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -77074,6 +79490,15 @@
       <c r="AW3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -77225,6 +79650,15 @@
       <c r="AW4" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AX4" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY4" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ4" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -77374,6 +79808,15 @@
       <c r="AW5" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="AX5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ5" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -77523,6 +79966,15 @@
       <c r="AW6" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ6" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -77670,6 +80122,15 @@
         <v>2</v>
       </c>
       <c r="AW7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ7" s="24" t="n">
         <v>2</v>
       </c>
     </row>
@@ -77821,6 +80282,15 @@
       <c r="AW8" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY8" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ8" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -77970,6 +80440,15 @@
       <c r="AW9" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AX9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ9" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -78119,6 +80598,15 @@
       <c r="AW10" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -78268,6 +80756,15 @@
       <c r="AW11" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AX11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ11" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -78417,6 +80914,15 @@
       <c r="AW12" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AX12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ12" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -78566,6 +81072,15 @@
       <c r="AW13" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AX13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ13" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -78715,6 +81230,15 @@
       <c r="AW14" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="AX14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY14" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ14" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -78864,6 +81388,15 @@
       <c r="AW15" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="AX15" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY15" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ15" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -79013,6 +81546,15 @@
       <c r="AW16" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX16" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY16" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ16" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -79162,6 +81704,15 @@
       <c r="AW17" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="AX17" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY17" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ17" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -79311,6 +81862,15 @@
       <c r="AW18" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="AX18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ18" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -79460,6 +82020,15 @@
       <c r="AW19" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="AX19" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY19" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ19" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -79609,6 +82178,15 @@
       <c r="AW20" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="AX20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ20" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -79758,6 +82336,15 @@
       <c r="AW21" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="AX21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ21" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -79909,6 +82496,15 @@
       <c r="AW22" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="AX22" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY22" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ22" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n"/>
@@ -80063,6 +82659,15 @@
       </c>
       <c r="AW24" s="24" t="n">
         <v>31</v>
+      </c>
+      <c r="AX24" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AY24" s="24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AZ24" s="24" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="25">

--- a/2026 수능 LLM 풀이 hard.xlsx
+++ b/2026 수능 LLM 풀이 hard.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ1000"/>
+  <dimension ref="A1:BB1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -760,6 +760,16 @@
           <t>Gemini 2.5 Pro (32K Thinking)</t>
         </is>
       </c>
+      <c r="BA2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 5 (high)</t>
+        </is>
+      </c>
+      <c r="BB2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 5</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -918,6 +928,12 @@
       <c r="AZ3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BA3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -1076,6 +1092,12 @@
       <c r="AZ4" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BA4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB4" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -1234,6 +1256,12 @@
       <c r="AZ5" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BA5" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB5" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1394,6 +1422,12 @@
       <c r="AZ6" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BA6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB6" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -1552,6 +1586,12 @@
         <v>4</v>
       </c>
       <c r="AZ7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB7" s="24" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1714,6 +1754,12 @@
       <c r="AZ8" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BA8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB8" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -1731,8 +1777,8 @@
       <c r="E9" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="25" t="n">
-        <v>2</v>
+      <c r="F9" s="26" t="n">
+        <v>5</v>
       </c>
       <c r="G9" s="26" t="n">
         <v>5</v>
@@ -1873,6 +1919,12 @@
       </c>
       <c r="AZ9" s="24" t="n">
         <v>5</v>
+      </c>
+      <c r="BA9" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB9" s="25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -2034,6 +2086,12 @@
       <c r="AZ10" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BA10" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB10" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -2194,6 +2252,12 @@
       <c r="AZ11" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BA11" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB11" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -2352,6 +2416,12 @@
       <c r="AZ12" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BA12" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB12" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -2512,6 +2582,12 @@
       <c r="AZ13" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BA13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB13" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -2670,6 +2746,12 @@
       <c r="AZ14" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BA14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB14" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -2828,6 +2910,12 @@
       <c r="AZ15" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BA15" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB15" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -2988,6 +3076,12 @@
       <c r="AZ16" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BA16" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB16" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -3148,6 +3242,12 @@
       <c r="AZ17" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BA17" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB17" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -3165,8 +3265,8 @@
       <c r="E18" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="F18" s="25" t="n">
-        <v>3</v>
+      <c r="F18" s="26" t="n">
+        <v>2</v>
       </c>
       <c r="G18" s="26" t="n">
         <v>2</v>
@@ -3307,6 +3407,12 @@
       </c>
       <c r="AZ18" s="24" t="n">
         <v>2</v>
+      </c>
+      <c r="BA18" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB18" s="25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -3325,8 +3431,8 @@
       <c r="E19" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="F19" s="25" t="n">
-        <v>2</v>
+      <c r="F19" s="26" t="n">
+        <v>3</v>
       </c>
       <c r="G19" s="26" t="n">
         <v>3</v>
@@ -3467,6 +3573,12 @@
       </c>
       <c r="AZ19" s="24" t="n">
         <v>3</v>
+      </c>
+      <c r="BA19" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB19" s="25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -3628,6 +3740,12 @@
       <c r="AZ20" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BA20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB20" s="25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -3788,6 +3906,12 @@
       <c r="AZ21" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BA21" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB21" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -3948,6 +4072,12 @@
       <c r="AZ22" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BA22" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB22" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -4108,6 +4238,12 @@
       <c r="AZ23" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BA23" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB23" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -4268,6 +4404,12 @@
       <c r="AZ24" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BA24" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB24" s="25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -4428,6 +4570,12 @@
       <c r="AZ25" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BA25" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB25" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -4588,6 +4736,12 @@
       <c r="AZ26" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BA26" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB26" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -4748,6 +4902,12 @@
       <c r="AZ27" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BA27" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB27" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -4908,6 +5068,12 @@
       <c r="AZ28" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BA28" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB28" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -5070,6 +5236,12 @@
       <c r="AZ29" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BA29" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB29" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -5232,6 +5404,12 @@
       <c r="AZ30" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BA30" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB30" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -5394,6 +5572,12 @@
       <c r="AZ31" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BA31" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB31" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -5556,6 +5740,12 @@
       <c r="AZ32" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BA32" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB32" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -5718,6 +5908,12 @@
       <c r="AZ33" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BA33" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB33" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -5880,6 +6076,12 @@
       <c r="AZ34" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BA34" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB34" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -6042,6 +6244,12 @@
       <c r="AZ35" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BA35" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB35" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -6204,6 +6412,12 @@
       <c r="AZ36" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BA36" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB36" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n"/>
@@ -6228,7 +6442,7 @@
         <v>55</v>
       </c>
       <c r="F38" s="24" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G38" s="24" t="n">
         <v>76</v>
@@ -6367,6 +6581,12 @@
       </c>
       <c r="AZ38" s="24" t="n">
         <v>76</v>
+      </c>
+      <c r="BA38" s="24" t="n">
+        <v>76</v>
+      </c>
+      <c r="BB38" s="24" t="n">
+        <v>47</v>
       </c>
     </row>
     <row r="39">
@@ -10231,7 +10451,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ1000"/>
+  <dimension ref="A1:BB1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -10508,6 +10728,16 @@
           <t>Gemini 2.5 Pro (32K Thinking)</t>
         </is>
       </c>
+      <c r="BA2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 5 (high)</t>
+        </is>
+      </c>
+      <c r="BB2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 5</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
@@ -10531,8 +10761,10 @@
       <c r="G3" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="H3" s="26" t="n">
-        <v>3</v>
+      <c r="H3" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I3" s="25" t="inlineStr">
         <is>
@@ -10675,6 +10907,12 @@
       </c>
       <c r="AZ3" s="24" t="n">
         <v>3</v>
+      </c>
+      <c r="BA3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB3" s="25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -10693,14 +10931,16 @@
       <c r="E4" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="F4" s="25" t="n">
-        <v>1</v>
+      <c r="F4" s="26" t="n">
+        <v>4</v>
       </c>
       <c r="G4" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="H4" s="26" t="n">
-        <v>4</v>
+      <c r="H4" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I4" s="25" t="inlineStr">
         <is>
@@ -10843,6 +11083,12 @@
       </c>
       <c r="AZ4" s="24" t="n">
         <v>4</v>
+      </c>
+      <c r="BA4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB4" s="25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -10867,8 +11113,10 @@
       <c r="G5" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="H5" s="26" t="n">
-        <v>3</v>
+      <c r="H5" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I5" s="25" t="inlineStr">
         <is>
@@ -11006,6 +11254,12 @@
         <v>3</v>
       </c>
       <c r="AZ5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB5" s="24" t="n">
         <v>3</v>
       </c>
     </row>
@@ -11033,8 +11287,10 @@
       <c r="G6" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="H6" s="25" t="n">
-        <v>5</v>
+      <c r="H6" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I6" s="25" t="inlineStr">
         <is>
@@ -11177,6 +11433,12 @@
       </c>
       <c r="AZ6" s="24" t="n">
         <v>4</v>
+      </c>
+      <c r="BA6" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB6" s="25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -11197,14 +11459,16 @@
       <c r="E7" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="25" t="n">
-        <v>2</v>
+      <c r="F7" s="26" t="n">
+        <v>1</v>
       </c>
       <c r="G7" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="26" t="n">
-        <v>1</v>
+      <c r="H7" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I7" s="25" t="inlineStr">
         <is>
@@ -11351,6 +11615,12 @@
       </c>
       <c r="AZ7" s="24" t="n">
         <v>1</v>
+      </c>
+      <c r="BA7" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB7" s="25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -11377,8 +11647,10 @@
       <c r="G8" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="H8" s="25" t="n">
-        <v>4</v>
+      <c r="H8" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I8" s="25" t="inlineStr">
         <is>
@@ -11529,6 +11801,12 @@
       </c>
       <c r="AZ8" s="25" t="n">
         <v>1</v>
+      </c>
+      <c r="BA8" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB8" s="25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -11553,8 +11831,10 @@
       <c r="G9" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="H9" s="26" t="n">
-        <v>3</v>
+      <c r="H9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I9" s="25" t="inlineStr">
         <is>
@@ -11706,6 +11986,12 @@
         <v>1</v>
       </c>
       <c r="AZ9" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA9" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB9" s="24" t="n">
         <v>3</v>
       </c>
     </row>
@@ -11731,8 +12017,10 @@
       <c r="G10" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="H10" s="26" t="n">
-        <v>5</v>
+      <c r="H10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I10" s="25" t="inlineStr">
         <is>
@@ -11883,6 +12171,12 @@
       </c>
       <c r="AZ10" s="24" t="n">
         <v>5</v>
+      </c>
+      <c r="BA10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB10" s="25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -11907,8 +12201,10 @@
       <c r="G11" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="H11" s="26" t="n">
-        <v>3</v>
+      <c r="H11" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I11" s="25" t="inlineStr">
         <is>
@@ -12057,6 +12353,12 @@
       </c>
       <c r="AZ11" s="24" t="n">
         <v>3</v>
+      </c>
+      <c r="BA11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB11" s="25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -12075,14 +12377,16 @@
       <c r="E12" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="25" t="n">
-        <v>3</v>
+      <c r="F12" s="26" t="n">
+        <v>5</v>
       </c>
       <c r="G12" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="H12" s="26" t="n">
-        <v>5</v>
+      <c r="H12" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I12" s="25" t="inlineStr">
         <is>
@@ -12231,6 +12535,12 @@
       </c>
       <c r="AZ12" s="24" t="n">
         <v>5</v>
+      </c>
+      <c r="BA12" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB12" s="25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -12255,8 +12565,10 @@
       <c r="G13" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="H13" s="25" t="n">
-        <v>5</v>
+      <c r="H13" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I13" s="25" t="inlineStr">
         <is>
@@ -12409,6 +12721,12 @@
       </c>
       <c r="AZ13" s="25" t="n">
         <v>5</v>
+      </c>
+      <c r="BA13" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB13" s="25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -12433,8 +12751,10 @@
       <c r="G14" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="26" t="n">
-        <v>1</v>
+      <c r="H14" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I14" s="25" t="inlineStr">
         <is>
@@ -12589,6 +12909,12 @@
         <is>
           <t>(포기)</t>
         </is>
+      </c>
+      <c r="BA14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB14" s="25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -12610,13 +12936,15 @@
         <v>3</v>
       </c>
       <c r="F15" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G15" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="H15" s="25" t="n">
-        <v>3</v>
+      <c r="H15" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I15" s="25" t="inlineStr">
         <is>
@@ -12775,6 +13103,12 @@
         <is>
           <t>(포기)</t>
         </is>
+      </c>
+      <c r="BA15" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB15" s="25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -12801,8 +13135,10 @@
       <c r="G16" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="H16" s="26" t="n">
-        <v>2</v>
+      <c r="H16" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I16" s="25" t="inlineStr">
         <is>
@@ -12959,6 +13295,12 @@
         <is>
           <t>(포기)</t>
         </is>
+      </c>
+      <c r="BA16" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB16" s="25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -12980,13 +13322,15 @@
         <v>5</v>
       </c>
       <c r="F17" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G17" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="H17" s="25" t="n">
-        <v>3</v>
+      <c r="H17" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I17" s="25" t="inlineStr">
         <is>
@@ -13143,6 +13487,12 @@
         <is>
           <t>(포기)</t>
         </is>
+      </c>
+      <c r="BA17" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB17" s="25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -13167,8 +13517,10 @@
       <c r="G18" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="H18" s="26" t="n">
-        <v>5</v>
+      <c r="H18" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I18" s="25" t="inlineStr">
         <is>
@@ -13325,6 +13677,12 @@
         <is>
           <t>(포기)</t>
         </is>
+      </c>
+      <c r="BA18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB18" s="25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -13345,14 +13703,16 @@
       <c r="E19" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="F19" s="25" t="n">
-        <v>4</v>
+      <c r="F19" s="26" t="n">
+        <v>5</v>
       </c>
       <c r="G19" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="H19" s="25" t="n">
-        <v>4</v>
+      <c r="H19" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I19" s="25" t="inlineStr">
         <is>
@@ -13509,6 +13869,12 @@
         <is>
           <t>(포기)</t>
         </is>
+      </c>
+      <c r="BA19" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB19" s="24" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -13529,14 +13895,16 @@
       <c r="E20" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="F20" s="25" t="n">
-        <v>4</v>
+      <c r="F20" s="26" t="n">
+        <v>2</v>
       </c>
       <c r="G20" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="H20" s="25" t="n">
-        <v>3</v>
+      <c r="H20" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I20" s="25" t="inlineStr">
         <is>
@@ -13693,6 +14061,12 @@
         <is>
           <t>(포기)</t>
         </is>
+      </c>
+      <c r="BA20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB20" s="24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -13713,14 +14087,16 @@
       <c r="E21" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="F21" s="25" t="n">
-        <v>2</v>
+      <c r="F21" s="26" t="n">
+        <v>4</v>
       </c>
       <c r="G21" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="H21" s="26" t="n">
-        <v>4</v>
+      <c r="H21" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I21" s="25" t="inlineStr">
         <is>
@@ -13877,6 +14253,12 @@
         <is>
           <t>(포기)</t>
         </is>
+      </c>
+      <c r="BA21" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB21" s="24" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -13898,13 +14280,15 @@
         <v>5</v>
       </c>
       <c r="F22" s="25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G22" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="H22" s="25" t="n">
-        <v>4</v>
+      <c r="H22" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I22" s="25" t="inlineStr">
         <is>
@@ -14061,6 +14445,12 @@
         <is>
           <t>(포기)</t>
         </is>
+      </c>
+      <c r="BA22" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB22" s="25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -14086,13 +14476,13 @@
         <v>18</v>
       </c>
       <c r="F24" s="24" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="G24" s="24" t="n">
         <v>27</v>
       </c>
       <c r="H24" s="24" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I24" s="24" t="n">
         <v>0</v>
@@ -14225,6 +14615,12 @@
       </c>
       <c r="AZ24" s="24" t="n">
         <v>22</v>
+      </c>
+      <c r="BA24" s="24" t="n">
+        <v>33</v>
+      </c>
+      <c r="BB24" s="24" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="25">
@@ -18145,7 +18541,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ1000"/>
+  <dimension ref="A1:BB1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -18422,6 +18818,16 @@
           <t>Kimi K2.6 (Non-Thinking)</t>
         </is>
       </c>
+      <c r="BA2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 5</t>
+        </is>
+      </c>
+      <c r="BB2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 5 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
@@ -18445,8 +18851,10 @@
       <c r="G3" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="H3" s="26" t="n">
-        <v>5</v>
+      <c r="H3" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I3" s="25" t="inlineStr">
         <is>
@@ -18592,6 +19000,12 @@
         <v>5</v>
       </c>
       <c r="AZ3" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA3" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB3" s="24" t="n">
         <v>5</v>
       </c>
     </row>
@@ -18617,8 +19031,10 @@
       <c r="G4" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="H4" s="26" t="n">
-        <v>5</v>
+      <c r="H4" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I4" s="25" t="inlineStr">
         <is>
@@ -18765,6 +19181,12 @@
       </c>
       <c r="AZ4" s="25" t="n">
         <v>4</v>
+      </c>
+      <c r="BA4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB4" s="24" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -18789,8 +19211,10 @@
       <c r="G5" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="26" t="n">
-        <v>3</v>
+      <c r="H5" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I5" s="25" t="inlineStr">
         <is>
@@ -18938,6 +19362,12 @@
         <v>3</v>
       </c>
       <c r="AZ5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB5" s="24" t="n">
         <v>3</v>
       </c>
     </row>
@@ -18963,8 +19393,10 @@
       <c r="G6" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="H6" s="25" t="n">
-        <v>3</v>
+      <c r="H6" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I6" s="25" t="inlineStr">
         <is>
@@ -19112,6 +19544,12 @@
         <v>1</v>
       </c>
       <c r="AZ6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA6" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB6" s="24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -19137,8 +19575,10 @@
       <c r="G7" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="H7" s="26" t="n">
-        <v>2</v>
+      <c r="H7" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I7" s="25" t="inlineStr">
         <is>
@@ -19287,6 +19727,12 @@
       </c>
       <c r="AZ7" s="25" t="n">
         <v>3</v>
+      </c>
+      <c r="BA7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB7" s="24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -19311,8 +19757,10 @@
       <c r="G8" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="H8" s="26" t="n">
-        <v>4</v>
+      <c r="H8" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I8" s="25" t="inlineStr">
         <is>
@@ -19462,6 +19910,12 @@
         <v>4</v>
       </c>
       <c r="AZ8" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA8" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB8" s="24" t="n">
         <v>4</v>
       </c>
     </row>
@@ -19487,8 +19941,10 @@
       <c r="G9" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="H9" s="26" t="n">
-        <v>3</v>
+      <c r="H9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I9" s="25" t="inlineStr">
         <is>
@@ -19638,6 +20094,12 @@
         <v>3</v>
       </c>
       <c r="AZ9" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA9" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB9" s="24" t="n">
         <v>3</v>
       </c>
     </row>
@@ -19663,8 +20125,10 @@
       <c r="G10" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="H10" s="25" t="n">
-        <v>3</v>
+      <c r="H10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I10" s="25" t="inlineStr">
         <is>
@@ -19816,6 +20280,12 @@
         <v>5</v>
       </c>
       <c r="AZ10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB10" s="24" t="n">
         <v>5</v>
       </c>
     </row>
@@ -19838,13 +20308,15 @@
         <v>5</v>
       </c>
       <c r="F11" s="25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G11" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="H11" s="25" t="n">
-        <v>4</v>
+      <c r="H11" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I11" s="25" t="inlineStr">
         <is>
@@ -19999,6 +20471,12 @@
       </c>
       <c r="AZ11" s="24" t="n">
         <v>2</v>
+      </c>
+      <c r="BA11" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB11" s="25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -20017,14 +20495,16 @@
       <c r="E12" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="25" t="n">
-        <v>2</v>
+      <c r="F12" s="26" t="n">
+        <v>1</v>
       </c>
       <c r="G12" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="H12" s="25" t="n">
-        <v>2</v>
+      <c r="H12" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I12" s="25" t="inlineStr">
         <is>
@@ -20179,6 +20659,12 @@
       </c>
       <c r="AZ12" s="25" t="n">
         <v>3</v>
+      </c>
+      <c r="BA12" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB12" s="24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -20205,8 +20691,10 @@
       <c r="G13" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="25" t="n">
-        <v>1</v>
+      <c r="H13" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I13" s="25" t="inlineStr">
         <is>
@@ -20362,6 +20850,12 @@
         <v>2</v>
       </c>
       <c r="AZ13" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA13" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB13" s="24" t="n">
         <v>2</v>
       </c>
     </row>
@@ -20389,8 +20883,10 @@
       <c r="G14" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="H14" s="25" t="n">
-        <v>3</v>
+      <c r="H14" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I14" s="25" t="inlineStr">
         <is>
@@ -20544,6 +21040,12 @@
         <v>2</v>
       </c>
       <c r="AZ14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA14" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB14" s="24" t="n">
         <v>2</v>
       </c>
     </row>
@@ -20566,13 +21068,15 @@
         <v>4</v>
       </c>
       <c r="F15" s="25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G15" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="H15" s="25" t="n">
-        <v>3</v>
+      <c r="H15" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I15" s="25" t="inlineStr">
         <is>
@@ -20727,6 +21231,12 @@
       </c>
       <c r="AZ15" s="24" t="n">
         <v>4</v>
+      </c>
+      <c r="BA15" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB15" s="25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -20747,14 +21257,16 @@
       <c r="E16" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="F16" s="25" t="n">
-        <v>2</v>
+      <c r="F16" s="26" t="n">
+        <v>4</v>
       </c>
       <c r="G16" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="H16" s="25" t="n">
-        <v>1</v>
+      <c r="H16" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I16" s="25" t="inlineStr">
         <is>
@@ -20909,6 +21421,12 @@
       </c>
       <c r="AZ16" s="25" t="n">
         <v>3</v>
+      </c>
+      <c r="BA16" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB16" s="24" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -20935,8 +21453,10 @@
       <c r="G17" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="26" t="n">
-        <v>1</v>
+      <c r="H17" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I17" s="25" t="inlineStr">
         <is>
@@ -21090,6 +21610,12 @@
         <v>1</v>
       </c>
       <c r="AZ17" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA17" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB17" s="24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -21117,8 +21643,10 @@
       <c r="G18" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="H18" s="25" t="n">
-        <v>4</v>
+      <c r="H18" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I18" s="25" t="inlineStr">
         <is>
@@ -21277,6 +21805,12 @@
       </c>
       <c r="AZ18" s="25" t="n">
         <v>2</v>
+      </c>
+      <c r="BA18" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB18" s="24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -21303,8 +21837,10 @@
       <c r="G19" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="H19" s="25" t="n">
-        <v>2</v>
+      <c r="H19" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I19" s="25" t="inlineStr">
         <is>
@@ -21460,6 +21996,12 @@
         <v>5</v>
       </c>
       <c r="AZ19" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA19" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB19" s="24" t="n">
         <v>5</v>
       </c>
     </row>
@@ -21481,14 +22023,16 @@
       <c r="E20" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="F20" s="25" t="n">
-        <v>5</v>
+      <c r="F20" s="26" t="n">
+        <v>3</v>
       </c>
       <c r="G20" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="H20" s="25" t="n">
-        <v>2</v>
+      <c r="H20" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I20" s="25" t="inlineStr">
         <is>
@@ -21646,6 +22190,12 @@
         <v>3</v>
       </c>
       <c r="AZ20" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA20" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB20" s="24" t="n">
         <v>3</v>
       </c>
     </row>
@@ -21667,14 +22217,16 @@
       <c r="E21" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="F21" s="25" t="n">
-        <v>4</v>
+      <c r="F21" s="26" t="n">
+        <v>5</v>
       </c>
       <c r="G21" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="25" t="n">
-        <v>1</v>
+      <c r="H21" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I21" s="25" t="inlineStr">
         <is>
@@ -21835,6 +22387,12 @@
       </c>
       <c r="AZ21" s="25" t="n">
         <v>3</v>
+      </c>
+      <c r="BA21" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB21" s="24" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -21855,14 +22413,16 @@
       <c r="E22" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="25" t="n">
-        <v>2</v>
+      <c r="F22" s="26" t="n">
+        <v>1</v>
       </c>
       <c r="G22" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="H22" s="25" t="n">
-        <v>3</v>
+      <c r="H22" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I22" s="25" t="inlineStr">
         <is>
@@ -22020,6 +22580,12 @@
         <v>1</v>
       </c>
       <c r="AZ22" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA22" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB22" s="24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -22046,13 +22612,13 @@
         <v>23</v>
       </c>
       <c r="F24" s="24" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="G24" s="24" t="n">
         <v>10</v>
       </c>
       <c r="H24" s="24" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I24" s="24" t="n">
         <v>0</v>
@@ -22185,6 +22751,12 @@
       </c>
       <c r="AZ24" s="24" t="n">
         <v>35</v>
+      </c>
+      <c r="BA24" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB24" s="24" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="25">
@@ -26105,7 +26677,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ1000"/>
+  <dimension ref="A1:BB1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -26382,6 +26954,16 @@
           <t>Kimi K2.6 (Non-Thinking)</t>
         </is>
       </c>
+      <c r="BA2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 5 (high)</t>
+        </is>
+      </c>
+      <c r="BB2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 5</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
@@ -26405,8 +26987,10 @@
       <c r="G3" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="H3" s="26" t="n">
-        <v>5</v>
+      <c r="H3" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I3" s="26" t="n">
         <v>5</v>
@@ -26550,6 +27134,12 @@
         </is>
       </c>
       <c r="AZ3" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA3" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB3" s="24" t="n">
         <v>5</v>
       </c>
     </row>
@@ -26575,8 +27165,10 @@
       <c r="G4" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="H4" s="26" t="n">
-        <v>4</v>
+      <c r="H4" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I4" s="26" t="n">
         <v>4</v>
@@ -26720,6 +27312,12 @@
         </is>
       </c>
       <c r="AZ4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB4" s="24" t="n">
         <v>4</v>
       </c>
     </row>
@@ -26739,14 +27337,16 @@
       <c r="E5" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="25" t="n">
-        <v>3</v>
+      <c r="F5" s="26" t="n">
+        <v>1</v>
       </c>
       <c r="G5" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="25" t="n">
-        <v>2</v>
+      <c r="H5" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I5" s="25" t="n">
         <v>3</v>
@@ -26891,6 +27491,12 @@
       </c>
       <c r="AZ5" s="24" t="n">
         <v>1</v>
+      </c>
+      <c r="BA5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB5" s="25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -26915,8 +27521,10 @@
       <c r="G6" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="H6" s="26" t="n">
-        <v>3</v>
+      <c r="H6" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I6" s="26" t="n">
         <v>3</v>
@@ -27060,6 +27668,12 @@
         </is>
       </c>
       <c r="AZ6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB6" s="24" t="n">
         <v>3</v>
       </c>
     </row>
@@ -27085,8 +27699,10 @@
       <c r="G7" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="H7" s="26" t="n">
-        <v>4</v>
+      <c r="H7" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I7" s="26" t="n">
         <v>4</v>
@@ -27233,6 +27849,12 @@
       </c>
       <c r="AZ7" s="24" t="n">
         <v>4</v>
+      </c>
+      <c r="BA7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB7" s="25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -27251,14 +27873,16 @@
       <c r="E8" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="25" t="n">
-        <v>1</v>
+      <c r="F8" s="26" t="n">
+        <v>3</v>
       </c>
       <c r="G8" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="26" t="n">
-        <v>3</v>
+      <c r="H8" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I8" s="26" t="n">
         <v>3</v>
@@ -27405,6 +28029,12 @@
       </c>
       <c r="AZ8" s="25" t="n">
         <v>1</v>
+      </c>
+      <c r="BA8" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB8" s="25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -27429,8 +28059,10 @@
       <c r="G9" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="H9" s="26" t="n">
-        <v>3</v>
+      <c r="H9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I9" s="26" t="n">
         <v>3</v>
@@ -27574,6 +28206,12 @@
         </is>
       </c>
       <c r="AZ9" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA9" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB9" s="24" t="n">
         <v>3</v>
       </c>
     </row>
@@ -27599,8 +28237,10 @@
       <c r="G10" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="H10" s="26" t="n">
-        <v>5</v>
+      <c r="H10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I10" s="26" t="n">
         <v>5</v>
@@ -27746,6 +28386,12 @@
         </is>
       </c>
       <c r="AZ10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB10" s="24" t="n">
         <v>5</v>
       </c>
     </row>
@@ -27767,14 +28413,16 @@
       <c r="E11" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="F11" s="25" t="n">
-        <v>3</v>
+      <c r="F11" s="26" t="n">
+        <v>5</v>
       </c>
       <c r="G11" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="H11" s="25" t="n">
-        <v>4</v>
+      <c r="H11" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I11" s="25" t="n">
         <v>4</v>
@@ -27921,6 +28569,12 @@
       </c>
       <c r="AZ11" s="25" t="n">
         <v>3</v>
+      </c>
+      <c r="BA11" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB11" s="25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -27945,8 +28599,10 @@
       <c r="G12" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="26" t="n">
-        <v>1</v>
+      <c r="H12" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I12" s="26" t="n">
         <v>1</v>
@@ -28093,6 +28749,12 @@
       </c>
       <c r="AZ12" s="25" t="n">
         <v>3</v>
+      </c>
+      <c r="BA12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB12" s="24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -28119,8 +28781,10 @@
       <c r="G13" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="25" t="n">
-        <v>5</v>
+      <c r="H13" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I13" s="26" t="n">
         <v>1</v>
@@ -28267,6 +28931,12 @@
       </c>
       <c r="AZ13" s="25" t="n">
         <v>3</v>
+      </c>
+      <c r="BA13" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB13" s="25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -28291,8 +28961,10 @@
       <c r="G14" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="H14" s="26" t="n">
-        <v>2</v>
+      <c r="H14" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I14" s="26" t="n">
         <v>2</v>
@@ -28439,6 +29111,12 @@
       </c>
       <c r="AZ14" s="24" t="n">
         <v>2</v>
+      </c>
+      <c r="BA14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB14" s="25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -28465,8 +29143,10 @@
       <c r="G15" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="H15" s="26" t="n">
-        <v>2</v>
+      <c r="H15" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I15" s="25" t="n">
         <v>5</v>
@@ -28613,6 +29293,12 @@
       </c>
       <c r="AZ15" s="25" t="n">
         <v>5</v>
+      </c>
+      <c r="BA15" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB15" s="25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -28633,14 +29319,16 @@
       <c r="E16" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="F16" s="25" t="n">
-        <v>3</v>
+      <c r="F16" s="26" t="n">
+        <v>4</v>
       </c>
       <c r="G16" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="H16" s="26" t="n">
-        <v>4</v>
+      <c r="H16" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I16" s="25" t="n">
         <v>1</v>
@@ -28789,6 +29477,12 @@
       </c>
       <c r="AZ16" s="25" t="n">
         <v>3</v>
+      </c>
+      <c r="BA16" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB16" s="24" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -28809,14 +29503,16 @@
       <c r="E17" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="F17" s="25" t="n">
-        <v>4</v>
+      <c r="F17" s="26" t="n">
+        <v>5</v>
       </c>
       <c r="G17" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="H17" s="25" t="n">
-        <v>3</v>
+      <c r="H17" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I17" s="25" t="n">
         <v>4</v>
@@ -28964,6 +29660,12 @@
         </is>
       </c>
       <c r="AZ17" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA17" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB17" s="24" t="n">
         <v>5</v>
       </c>
     </row>
@@ -28991,8 +29693,10 @@
       <c r="G18" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="26" t="n">
-        <v>1</v>
+      <c r="H18" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I18" s="26" t="n">
         <v>1</v>
@@ -29141,6 +29845,12 @@
       </c>
       <c r="AZ18" s="24" t="n">
         <v>1</v>
+      </c>
+      <c r="BA18" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB18" s="25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -29162,13 +29872,15 @@
         <v>4</v>
       </c>
       <c r="F19" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G19" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="H19" s="25" t="n">
-        <v>5</v>
+      <c r="H19" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I19" s="25" t="n">
         <v>4</v>
@@ -29316,6 +30028,12 @@
         </is>
       </c>
       <c r="AZ19" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA19" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB19" s="25" t="n">
         <v>4</v>
       </c>
     </row>
@@ -29337,14 +30055,16 @@
       <c r="E20" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="25" t="n">
-        <v>2</v>
+      <c r="F20" s="26" t="n">
+        <v>1</v>
       </c>
       <c r="G20" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="25" t="n">
-        <v>3</v>
+      <c r="H20" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I20" s="25" t="n">
         <v>2</v>
@@ -29492,6 +30212,12 @@
         </is>
       </c>
       <c r="AZ20" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA20" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB20" s="25" t="n">
         <v>2</v>
       </c>
     </row>
@@ -29519,8 +30245,10 @@
       <c r="G21" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="H21" s="26" t="n">
-        <v>5</v>
+      <c r="H21" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I21" s="25" t="n">
         <v>1</v>
@@ -29671,6 +30399,12 @@
       </c>
       <c r="AZ21" s="24" t="n">
         <v>5</v>
+      </c>
+      <c r="BA21" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB21" s="25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -29695,8 +30429,10 @@
       <c r="G22" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="H22" s="26" t="n">
-        <v>2</v>
+      <c r="H22" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I22" s="25" t="n">
         <v>4</v>
@@ -29846,6 +30582,12 @@
         </is>
       </c>
       <c r="AZ22" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA22" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB22" s="25" t="n">
         <v>4</v>
       </c>
     </row>
@@ -29872,13 +30614,13 @@
         <v>37</v>
       </c>
       <c r="F24" s="24" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="G24" s="24" t="n">
         <v>38</v>
       </c>
       <c r="H24" s="24" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="I24" s="24" t="n">
         <v>26</v>
@@ -30011,6 +30753,12 @@
       </c>
       <c r="AZ24" s="24" t="n">
         <v>27</v>
+      </c>
+      <c r="BA24" s="24" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB24" s="24" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="25">
@@ -33931,7 +34679,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ1000"/>
+  <dimension ref="A1:BB1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -34208,6 +34956,16 @@
           <t>Gemini 2.5 Pro (32K Thinking)</t>
         </is>
       </c>
+      <c r="BA2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 5 (high)</t>
+        </is>
+      </c>
+      <c r="BB2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 5</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
@@ -34225,14 +34983,16 @@
       <c r="E3" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="F3" s="25" t="n">
-        <v>3</v>
+      <c r="F3" s="26" t="n">
+        <v>5</v>
       </c>
       <c r="G3" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="H3" s="25" t="n">
-        <v>3</v>
+      <c r="H3" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I3" s="25" t="n">
         <v>2</v>
@@ -34369,6 +35129,12 @@
       </c>
       <c r="AZ3" s="24" t="n">
         <v>5</v>
+      </c>
+      <c r="BA3" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB3" s="25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -34393,8 +35159,10 @@
       <c r="G4" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="H4" s="26" t="n">
-        <v>2</v>
+      <c r="H4" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I4" s="26" t="n">
         <v>2</v>
@@ -34532,6 +35300,12 @@
         <v>2</v>
       </c>
       <c r="AZ4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB4" s="24" t="n">
         <v>2</v>
       </c>
     </row>
@@ -34557,8 +35331,10 @@
       <c r="G5" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="26" t="n">
-        <v>1</v>
+      <c r="H5" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I5" s="26" t="n">
         <v>1</v>
@@ -34697,6 +35473,12 @@
       </c>
       <c r="AZ5" s="24" t="n">
         <v>1</v>
+      </c>
+      <c r="BA5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB5" s="25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -34721,8 +35503,10 @@
       <c r="G6" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="H6" s="26" t="n">
-        <v>4</v>
+      <c r="H6" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I6" s="26" t="n">
         <v>4</v>
@@ -34861,6 +35645,12 @@
       </c>
       <c r="AZ6" s="24" t="n">
         <v>4</v>
+      </c>
+      <c r="BA6" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB6" s="25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -34885,8 +35675,10 @@
       <c r="G7" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="26" t="n">
-        <v>1</v>
+      <c r="H7" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I7" s="26" t="n">
         <v>1</v>
@@ -35025,6 +35817,12 @@
       </c>
       <c r="AZ7" s="24" t="n">
         <v>1</v>
+      </c>
+      <c r="BA7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB7" s="25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -35049,8 +35847,10 @@
       <c r="G8" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="26" t="n">
-        <v>1</v>
+      <c r="H8" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I8" s="26" t="n">
         <v>1</v>
@@ -35191,6 +35991,12 @@
       </c>
       <c r="AZ8" s="24" t="n">
         <v>1</v>
+      </c>
+      <c r="BA8" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB8" s="25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -35215,8 +36021,10 @@
       <c r="G9" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="25" t="n">
-        <v>1</v>
+      <c r="H9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I9" s="25" t="n">
         <v>4</v>
@@ -35357,6 +36165,12 @@
       </c>
       <c r="AZ9" s="24" t="n">
         <v>2</v>
+      </c>
+      <c r="BA9" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB9" s="25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -35381,8 +36195,10 @@
       <c r="G10" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="H10" s="25" t="n">
-        <v>4</v>
+      <c r="H10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I10" s="25" t="n">
         <v>2</v>
@@ -35523,6 +36339,12 @@
       </c>
       <c r="AZ10" s="25" t="n">
         <v>4</v>
+      </c>
+      <c r="BA10" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB10" s="25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -35541,14 +36363,16 @@
       <c r="E11" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="25" t="n">
-        <v>1</v>
+      <c r="F11" s="26" t="n">
+        <v>4</v>
       </c>
       <c r="G11" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="H11" s="26" t="n">
-        <v>4</v>
+      <c r="H11" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I11" s="26" t="n">
         <v>4</v>
@@ -35690,6 +36514,12 @@
         <v>4</v>
       </c>
       <c r="AZ11" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA11" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB11" s="24" t="n">
         <v>4</v>
       </c>
     </row>
@@ -35715,8 +36545,10 @@
       <c r="G12" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="H12" s="25" t="n">
-        <v>1</v>
+      <c r="H12" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I12" s="25" t="n">
         <v>1</v>
@@ -35863,6 +36695,12 @@
       </c>
       <c r="AZ12" s="24" t="n">
         <v>3</v>
+      </c>
+      <c r="BA12" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB12" s="25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -35887,8 +36725,10 @@
       <c r="G13" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="H13" s="26" t="n">
-        <v>4</v>
+      <c r="H13" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I13" s="26" t="n">
         <v>4</v>
@@ -36030,6 +36870,12 @@
         <v>4</v>
       </c>
       <c r="AZ13" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA13" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB13" s="24" t="n">
         <v>4</v>
       </c>
     </row>
@@ -36055,8 +36901,10 @@
       <c r="G14" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="H14" s="25" t="n">
-        <v>3</v>
+      <c r="H14" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I14" s="25" t="n">
         <v>5</v>
@@ -36198,6 +37046,12 @@
         <v>1</v>
       </c>
       <c r="AZ14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB14" s="24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -36223,8 +37077,10 @@
       <c r="G15" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="H15" s="26" t="n">
-        <v>2</v>
+      <c r="H15" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I15" s="26" t="n">
         <v>2</v>
@@ -36369,6 +37225,12 @@
       </c>
       <c r="AZ15" s="24" t="n">
         <v>2</v>
+      </c>
+      <c r="BA15" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB15" s="25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -36393,8 +37255,10 @@
       <c r="G16" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="H16" s="26" t="n">
-        <v>4</v>
+      <c r="H16" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I16" s="26" t="n">
         <v>4</v>
@@ -36538,6 +37402,12 @@
         <v>4</v>
       </c>
       <c r="AZ16" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA16" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB16" s="24" t="n">
         <v>4</v>
       </c>
     </row>
@@ -36563,8 +37433,10 @@
       <c r="G17" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="H17" s="25" t="n">
-        <v>4</v>
+      <c r="H17" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I17" s="25" t="n">
         <v>4</v>
@@ -36713,6 +37585,12 @@
         <is>
           <t>(포기)</t>
         </is>
+      </c>
+      <c r="BA17" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB17" s="25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -36737,8 +37615,10 @@
       <c r="G18" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="H18" s="25" t="n">
-        <v>3</v>
+      <c r="H18" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I18" s="26" t="n">
         <v>5</v>
@@ -36883,6 +37763,12 @@
         <is>
           <t>(포기)</t>
         </is>
+      </c>
+      <c r="BA18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB18" s="24" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -36907,8 +37793,10 @@
       <c r="G19" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="H19" s="26" t="n">
-        <v>4</v>
+      <c r="H19" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I19" s="25" t="n">
         <v>5</v>
@@ -37053,6 +37941,12 @@
         <is>
           <t>(포기)</t>
         </is>
+      </c>
+      <c r="BA19" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB19" s="25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -37077,8 +37971,10 @@
       <c r="G20" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="H20" s="26" t="n">
-        <v>2</v>
+      <c r="H20" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I20" s="26" t="n">
         <v>2</v>
@@ -37223,6 +38119,12 @@
         <is>
           <t>(포기)</t>
         </is>
+      </c>
+      <c r="BA20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB20" s="24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -37247,8 +38149,10 @@
       <c r="G21" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="H21" s="26" t="n">
-        <v>3</v>
+      <c r="H21" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I21" s="26" t="n">
         <v>3</v>
@@ -37393,6 +38297,12 @@
         <is>
           <t>(포기)</t>
         </is>
+      </c>
+      <c r="BA21" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB21" s="24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -37411,14 +38321,16 @@
       <c r="E22" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="25" t="n">
-        <v>5</v>
+      <c r="F22" s="26" t="n">
+        <v>3</v>
       </c>
       <c r="G22" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="H22" s="25" t="n">
-        <v>1</v>
+      <c r="H22" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="I22" s="25" t="n">
         <v>5</v>
@@ -37567,6 +38479,12 @@
         <is>
           <t>(포기)</t>
         </is>
+      </c>
+      <c r="BA22" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB22" s="25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -37592,13 +38510,13 @@
         <v>40</v>
       </c>
       <c r="F24" s="24" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G24" s="24" t="n">
         <v>40</v>
       </c>
       <c r="H24" s="24" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="I24" s="24" t="n">
         <v>30</v>
@@ -37731,6 +38649,12 @@
       </c>
       <c r="AZ24" s="24" t="n">
         <v>32</v>
+      </c>
+      <c r="BA24" s="24" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB24" s="24" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="25">
@@ -41651,7 +42575,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ1000"/>
+  <dimension ref="A1:BB1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -41930,6 +42854,16 @@
           <t>Kimi K2.6 (Non-Thinking)</t>
         </is>
       </c>
+      <c r="BA2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 5 (high)</t>
+        </is>
+      </c>
+      <c r="BB2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 5</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -42088,6 +43022,12 @@
       <c r="AZ3" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BA3" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB3" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -42246,6 +43186,12 @@
       <c r="AZ4" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BA4" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB4" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -42406,6 +43352,12 @@
       <c r="AZ5" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BA5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB5" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -42423,14 +43375,14 @@
       <c r="E6" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="F6" s="25" t="n">
-        <v>4</v>
+      <c r="F6" s="26" t="n">
+        <v>1</v>
       </c>
       <c r="G6" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="H6" s="25" t="n">
-        <v>5</v>
+      <c r="H6" s="26" t="n">
+        <v>1</v>
       </c>
       <c r="I6" s="26" t="n">
         <v>1</v>
@@ -42565,6 +43517,12 @@
       </c>
       <c r="AZ6" s="25" t="n">
         <v>4</v>
+      </c>
+      <c r="BA6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB6" s="25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -42726,6 +43684,12 @@
       <c r="AZ7" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="BA7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB7" s="25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -42886,6 +43850,12 @@
       <c r="AZ8" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BA8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB8" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -43046,6 +44016,12 @@
       <c r="AZ9" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BA9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB9" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -43206,6 +44182,12 @@
       <c r="AZ10" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BA10" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB10" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -43366,6 +44348,12 @@
       <c r="AZ11" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BA11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB11" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -43526,6 +44514,12 @@
       <c r="AZ12" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BA12" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB12" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -43543,8 +44537,8 @@
       <c r="E13" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="F13" s="25" t="n">
-        <v>4</v>
+      <c r="F13" s="26" t="n">
+        <v>5</v>
       </c>
       <c r="G13" s="26" t="n">
         <v>5</v>
@@ -43687,6 +44681,12 @@
       </c>
       <c r="AZ13" s="24" t="n">
         <v>5</v>
+      </c>
+      <c r="BA13" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB13" s="25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -43712,13 +44712,13 @@
         <v>19</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G15" s="24" t="n">
         <v>22</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I15" s="24" t="n">
         <v>21</v>
@@ -43851,6 +44851,12 @@
       </c>
       <c r="AZ15" s="24" t="n">
         <v>20</v>
+      </c>
+      <c r="BA15" s="24" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB15" s="24" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="16">
@@ -47807,7 +48813,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ1000"/>
+  <dimension ref="A1:BB1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -48088,6 +49094,16 @@
           <t>Kimi K2.6 (Non-Thinking)</t>
         </is>
       </c>
+      <c r="BA2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 5 (high)</t>
+        </is>
+      </c>
+      <c r="BB2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 5</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -48105,8 +49121,10 @@
       <c r="E3" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="F3" s="26" t="n">
-        <v>3</v>
+      <c r="F3" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="G3" s="26" t="n">
         <v>3</v>
@@ -48247,6 +49265,12 @@
       </c>
       <c r="AZ3" s="24" t="n">
         <v>3</v>
+      </c>
+      <c r="BA3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB3" s="25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -48267,8 +49291,10 @@
       <c r="E4" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="25" t="n">
-        <v>5</v>
+      <c r="F4" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="G4" s="26" t="n">
         <v>2</v>
@@ -48409,6 +49435,12 @@
       </c>
       <c r="AZ4" s="24" t="n">
         <v>2</v>
+      </c>
+      <c r="BA4" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB4" s="25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -48429,8 +49461,10 @@
       <c r="E5" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="26" t="n">
-        <v>4</v>
+      <c r="F5" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="G5" s="25" t="n">
         <v>1</v>
@@ -48573,6 +49607,12 @@
       </c>
       <c r="AZ5" s="25" t="n">
         <v>2</v>
+      </c>
+      <c r="BA5" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB5" s="25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -48591,8 +49631,10 @@
       <c r="E6" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="F6" s="25" t="n">
-        <v>2</v>
+      <c r="F6" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="G6" s="25" t="n">
         <v>2</v>
@@ -48734,6 +49776,12 @@
         <v>4</v>
       </c>
       <c r="AZ6" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA6" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB6" s="24" t="n">
         <v>4</v>
       </c>
     </row>
@@ -48753,14 +49801,16 @@
       <c r="E7" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="25" t="n">
-        <v>4</v>
+      <c r="F7" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="G7" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="H7" s="25" t="n">
-        <v>4</v>
+      <c r="H7" s="26" t="n">
+        <v>1</v>
       </c>
       <c r="I7" s="26" t="n">
         <v>1</v>
@@ -48896,6 +49946,12 @@
         <v>1</v>
       </c>
       <c r="AZ7" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB7" s="25" t="n">
         <v>4</v>
       </c>
     </row>
@@ -48915,8 +49971,10 @@
       <c r="E8" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="26" t="n">
-        <v>2</v>
+      <c r="F8" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="G8" s="26" t="n">
         <v>2</v>
@@ -49058,6 +50116,12 @@
         <v>2</v>
       </c>
       <c r="AZ8" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB8" s="25" t="n">
         <v>1</v>
       </c>
     </row>
@@ -49077,8 +50141,10 @@
       <c r="E9" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="26" t="n">
-        <v>4</v>
+      <c r="F9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="G9" s="26" t="n">
         <v>4</v>
@@ -49222,6 +50288,12 @@
         <v>4</v>
       </c>
       <c r="AZ9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB9" s="24" t="n">
         <v>4</v>
       </c>
     </row>
@@ -49241,8 +50313,10 @@
       <c r="E10" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="F10" s="26" t="n">
-        <v>5</v>
+      <c r="F10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="G10" s="26" t="n">
         <v>5</v>
@@ -49384,6 +50458,12 @@
         <v>5</v>
       </c>
       <c r="AZ10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB10" s="24" t="n">
         <v>5</v>
       </c>
     </row>
@@ -49403,8 +50483,10 @@
       <c r="E11" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="F11" s="26" t="n">
-        <v>2</v>
+      <c r="F11" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="G11" s="26" t="n">
         <v>2</v>
@@ -49546,6 +50628,12 @@
         <v>2</v>
       </c>
       <c r="AZ11" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA11" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB11" s="24" t="n">
         <v>2</v>
       </c>
     </row>
@@ -49565,8 +50653,10 @@
       <c r="E12" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="F12" s="26" t="n">
-        <v>4</v>
+      <c r="F12" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="G12" s="26" t="n">
         <v>4</v>
@@ -49708,6 +50798,12 @@
         <v>4</v>
       </c>
       <c r="AZ12" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA12" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB12" s="24" t="n">
         <v>4</v>
       </c>
     </row>
@@ -49727,8 +50823,10 @@
       <c r="E13" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="F13" s="26" t="n">
-        <v>3</v>
+      <c r="F13" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
       <c r="G13" s="26" t="n">
         <v>3</v>
@@ -49870,6 +50968,12 @@
         <v>3</v>
       </c>
       <c r="AZ13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB13" s="24" t="n">
         <v>3</v>
       </c>
     </row>
@@ -49896,13 +51000,13 @@
         <v>13</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G15" s="24" t="n">
         <v>18</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I15" s="24" t="n">
         <v>15</v>
@@ -50035,6 +51139,12 @@
       </c>
       <c r="AZ15" s="24" t="n">
         <v>18</v>
+      </c>
+      <c r="BA15" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="BB15" s="24" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -53991,7 +55101,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ37"/>
+  <dimension ref="A1:BB37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -54268,6 +55378,16 @@
           <t>Kimi K2.6 (Thinking)</t>
         </is>
       </c>
+      <c r="BA2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 5</t>
+        </is>
+      </c>
+      <c r="BB2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 5 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -54430,6 +55550,12 @@
       <c r="AZ3" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BA3" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB3" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -54592,6 +55718,12 @@
       <c r="AZ4" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BA4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB4" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -54754,6 +55886,12 @@
       <c r="AZ5" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BA5" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB5" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -54916,6 +56054,12 @@
       <c r="AZ6" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BA6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB6" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -55076,6 +56220,12 @@
         <v>3</v>
       </c>
       <c r="AZ7" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA7" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB7" s="24" t="n">
         <v>3</v>
       </c>
     </row>
@@ -55240,6 +56390,12 @@
       <c r="AZ8" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BA8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB8" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -55402,6 +56558,12 @@
       <c r="AZ9" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BA9" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB9" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -55566,6 +56728,12 @@
       <c r="AZ10" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BA10" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB10" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -55589,8 +56757,8 @@
       <c r="G11" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="H11" s="25" t="n">
-        <v>3</v>
+      <c r="H11" s="26" t="n">
+        <v>4</v>
       </c>
       <c r="I11" s="26" t="n">
         <v>4</v>
@@ -55728,6 +56896,12 @@
         <v>4</v>
       </c>
       <c r="AZ11" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA11" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB11" s="24" t="n">
         <v>4</v>
       </c>
     </row>
@@ -55900,6 +57074,12 @@
       <c r="AZ12" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BA12" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB12" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -56068,6 +57248,12 @@
       <c r="AZ13" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BA13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB13" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -56236,6 +57422,12 @@
       <c r="AZ14" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BA14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB14" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -56404,6 +57596,12 @@
       <c r="AZ15" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BA15" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB15" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -56576,6 +57774,12 @@
       <c r="AZ16" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BA16" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB16" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -56595,8 +57799,8 @@
       <c r="E17" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="F17" s="25" t="n">
-        <v>3</v>
+      <c r="F17" s="26" t="n">
+        <v>4</v>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
@@ -56748,6 +57952,12 @@
         <v>4</v>
       </c>
       <c r="AZ17" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA17" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB17" s="24" t="n">
         <v>4</v>
       </c>
     </row>
@@ -56918,6 +58128,12 @@
       <c r="AZ18" s="24" t="n">
         <v>9</v>
       </c>
+      <c r="BA18" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB18" s="24" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -57086,6 +58302,12 @@
       <c r="AZ19" s="24" t="n">
         <v>16</v>
       </c>
+      <c r="BA19" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="BB19" s="24" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -57258,6 +58480,12 @@
       <c r="AZ20" s="24" t="n">
         <v>12</v>
       </c>
+      <c r="BA20" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB20" s="24" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -57281,8 +58509,8 @@
       <c r="G21" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="H21" s="25" t="n">
-        <v>20</v>
+      <c r="H21" s="26" t="n">
+        <v>15</v>
       </c>
       <c r="I21" s="26" t="n">
         <v>15</v>
@@ -57428,6 +58656,12 @@
         <v>15</v>
       </c>
       <c r="AZ21" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA21" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB21" s="24" t="n">
         <v>15</v>
       </c>
     </row>
@@ -57612,6 +58846,12 @@
       <c r="AZ22" s="24" t="n">
         <v>130</v>
       </c>
+      <c r="BA22" s="25" t="n">
+        <v>305</v>
+      </c>
+      <c r="BB22" s="24" t="n">
+        <v>130</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -57631,14 +58871,14 @@
       <c r="E23" s="25" t="n">
         <v>39</v>
       </c>
-      <c r="F23" s="25" t="n">
-        <v>39</v>
+      <c r="F23" s="26" t="n">
+        <v>65</v>
       </c>
       <c r="G23" s="25" t="n">
         <v>16</v>
       </c>
-      <c r="H23" s="25" t="n">
-        <v>48</v>
+      <c r="H23" s="26" t="n">
+        <v>65</v>
       </c>
       <c r="I23" s="26" t="n">
         <v>65</v>
@@ -57798,6 +59038,12 @@
         <v>65</v>
       </c>
       <c r="AZ23" s="24" t="n">
+        <v>65</v>
+      </c>
+      <c r="BA23" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="BB23" s="24" t="n">
         <v>65</v>
       </c>
     </row>
@@ -57821,14 +59067,14 @@
       <c r="E24" s="25" t="n">
         <v>17</v>
       </c>
-      <c r="F24" s="25" t="n">
-        <v>41</v>
+      <c r="F24" s="26" t="n">
+        <v>457</v>
       </c>
       <c r="G24" s="25" t="n">
         <v>169</v>
       </c>
-      <c r="H24" s="25" t="n">
-        <v>181</v>
+      <c r="H24" s="26" t="n">
+        <v>457</v>
       </c>
       <c r="I24" s="26" t="n">
         <v>457</v>
@@ -57986,6 +59232,12 @@
         <v>457</v>
       </c>
       <c r="AZ24" s="24" t="n">
+        <v>457</v>
+      </c>
+      <c r="BA24" s="25" t="n">
+        <v>49</v>
+      </c>
+      <c r="BB24" s="24" t="n">
         <v>457</v>
       </c>
     </row>
@@ -58012,13 +59264,13 @@
         <v>62</v>
       </c>
       <c r="F26" s="24" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="G26" s="24" t="n">
         <v>32</v>
       </c>
       <c r="H26" s="24" t="n">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="I26" s="24" t="n">
         <v>74</v>
@@ -58150,6 +59402,12 @@
         <v>74</v>
       </c>
       <c r="AZ26" s="24" t="n">
+        <v>74</v>
+      </c>
+      <c r="BA26" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB26" s="24" t="n">
         <v>74</v>
       </c>
     </row>
@@ -58211,7 +59469,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ37"/>
+  <dimension ref="A1:BB37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -58488,6 +59746,16 @@
           <t>Kimi K2.6 (Thinking)</t>
         </is>
       </c>
+      <c r="BA2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 5</t>
+        </is>
+      </c>
+      <c r="BB2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 5 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -58646,6 +59914,12 @@
       <c r="AZ3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BA3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -58804,6 +60078,12 @@
       <c r="AZ4" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BA4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB4" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -58964,6 +60244,12 @@
       <c r="AZ5" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BA5" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB5" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -59122,6 +60408,12 @@
       <c r="AZ6" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BA6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB6" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -59282,6 +60574,12 @@
       <c r="AZ7" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BA7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB7" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -59307,8 +60605,8 @@
       <c r="G8" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="25" t="n">
-        <v>1</v>
+      <c r="H8" s="26" t="n">
+        <v>2</v>
       </c>
       <c r="I8" s="26" t="n">
         <v>2</v>
@@ -59448,6 +60746,12 @@
         <v>2</v>
       </c>
       <c r="AZ8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA8" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB8" s="24" t="n">
         <v>2</v>
       </c>
     </row>
@@ -59475,8 +60779,8 @@
       <c r="G9" s="26" t="n">
         <v>977</v>
       </c>
-      <c r="H9" s="25" t="n">
-        <v>841</v>
+      <c r="H9" s="26" t="n">
+        <v>977</v>
       </c>
       <c r="I9" s="26" t="n">
         <v>977</v>
@@ -59614,6 +60918,12 @@
         <v>977</v>
       </c>
       <c r="AZ9" s="24" t="n">
+        <v>977</v>
+      </c>
+      <c r="BA9" s="24" t="n">
+        <v>977</v>
+      </c>
+      <c r="BB9" s="24" t="n">
         <v>977</v>
       </c>
     </row>
@@ -59635,14 +60945,14 @@
       <c r="E10" s="26" t="n">
         <v>262</v>
       </c>
-      <c r="F10" s="25" t="n">
-        <v>612</v>
+      <c r="F10" s="26" t="n">
+        <v>262</v>
       </c>
       <c r="G10" s="25" t="n">
         <v>70</v>
       </c>
-      <c r="H10" s="25" t="n">
-        <v>36</v>
+      <c r="H10" s="26" t="n">
+        <v>262</v>
       </c>
       <c r="I10" s="26" t="n">
         <v>262</v>
@@ -59784,6 +61094,12 @@
         <v>262</v>
       </c>
       <c r="AZ10" s="24" t="n">
+        <v>262</v>
+      </c>
+      <c r="BA10" s="25" t="n">
+        <v>350</v>
+      </c>
+      <c r="BB10" s="24" t="n">
         <v>262</v>
       </c>
     </row>
@@ -59810,13 +61126,13 @@
         <v>26</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G12" s="24" t="n">
         <v>18</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="I12" s="24" t="n">
         <v>26</v>
@@ -59948,6 +61264,12 @@
         <v>26</v>
       </c>
       <c r="AZ12" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="BA12" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="BB12" s="24" t="n">
         <v>26</v>
       </c>
     </row>
@@ -60061,7 +61383,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ1000"/>
+  <dimension ref="A1:BB1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -60340,6 +61662,16 @@
           <t>Kimi K2.6 (Non-Thinking)</t>
         </is>
       </c>
+      <c r="BA2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 5</t>
+        </is>
+      </c>
+      <c r="BB2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 5 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -60502,6 +61834,12 @@
       <c r="AZ3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BA3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -60664,6 +62002,12 @@
       <c r="AZ4" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BA4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB4" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -60826,6 +62170,12 @@
       <c r="AZ5" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BA5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB5" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -60988,6 +62338,12 @@
       <c r="AZ6" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BA6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB6" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -61150,6 +62506,12 @@
       <c r="AZ7" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BA7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB7" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -61173,8 +62535,8 @@
       <c r="G8" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="25" t="n">
-        <v>1</v>
+      <c r="H8" s="26" t="n">
+        <v>5</v>
       </c>
       <c r="I8" s="26" t="n">
         <v>5</v>
@@ -61310,6 +62672,12 @@
         <v>5</v>
       </c>
       <c r="AZ8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB8" s="24" t="n">
         <v>5</v>
       </c>
     </row>
@@ -61335,8 +62703,8 @@
       <c r="G9" s="25" t="n">
         <v>109</v>
       </c>
-      <c r="H9" s="25" t="n">
-        <v>183</v>
+      <c r="H9" s="26" t="n">
+        <v>97</v>
       </c>
       <c r="I9" s="26" t="n">
         <v>97</v>
@@ -61480,6 +62848,12 @@
         <v>97</v>
       </c>
       <c r="AZ9" s="24" t="n">
+        <v>97</v>
+      </c>
+      <c r="BA9" s="25" t="n">
+        <v>169</v>
+      </c>
+      <c r="BB9" s="24" t="n">
         <v>97</v>
       </c>
     </row>
@@ -61505,8 +62879,8 @@
       <c r="G10" s="25" t="n">
         <v>13</v>
       </c>
-      <c r="H10" s="25" t="n">
-        <v>23</v>
+      <c r="H10" s="26" t="n">
+        <v>11</v>
       </c>
       <c r="I10" s="26" t="n">
         <v>11</v>
@@ -61661,6 +63035,12 @@
       </c>
       <c r="AZ10" s="25" t="n">
         <v>10</v>
+      </c>
+      <c r="BA10" s="25" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB10" s="24" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -61692,7 +63072,7 @@
         <v>14</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="I12" s="24" t="n">
         <v>26</v>
@@ -61825,6 +63205,12 @@
       </c>
       <c r="AZ12" s="24" t="n">
         <v>22</v>
+      </c>
+      <c r="BA12" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="BB12" s="24" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="13">
@@ -65793,7 +67179,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ37"/>
+  <dimension ref="A1:BB37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -66070,6 +67456,16 @@
           <t>Kimi K2.6 (Non-Thinking)</t>
         </is>
       </c>
+      <c r="BA2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 5</t>
+        </is>
+      </c>
+      <c r="BB2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 5 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -66230,6 +67626,12 @@
       <c r="AZ3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BA3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -66390,6 +67792,12 @@
       <c r="AZ4" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BA4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB4" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -66554,6 +67962,12 @@
       <c r="AZ5" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BA5" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB5" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -66716,6 +68130,12 @@
       <c r="AZ6" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BA6" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB6" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -66878,6 +68298,12 @@
       <c r="AZ7" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BA7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB7" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -66901,8 +68327,8 @@
       <c r="G8" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="H8" s="25" t="n">
-        <v>3</v>
+      <c r="H8" s="26" t="n">
+        <v>4</v>
       </c>
       <c r="I8" s="26" t="n">
         <v>4</v>
@@ -67037,6 +68463,12 @@
       </c>
       <c r="AZ8" s="25" t="n">
         <v>3</v>
+      </c>
+      <c r="BA8" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB8" s="24" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -67055,14 +68487,14 @@
       <c r="E9" s="25" t="n">
         <v>48</v>
       </c>
-      <c r="F9" s="25" t="n">
-        <v>72</v>
+      <c r="F9" s="26" t="n">
+        <v>360</v>
       </c>
       <c r="G9" s="25" t="n">
         <v>75</v>
       </c>
-      <c r="H9" s="25" t="n">
-        <v>185</v>
+      <c r="H9" s="26" t="n">
+        <v>360</v>
       </c>
       <c r="I9" s="26" t="n">
         <v>360</v>
@@ -67203,6 +68635,12 @@
       </c>
       <c r="AZ9" s="25" t="n">
         <v>180</v>
+      </c>
+      <c r="BA9" s="25" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB9" s="24" t="n">
+        <v>360</v>
       </c>
     </row>
     <row r="10">
@@ -67227,8 +68665,8 @@
       <c r="G10" s="25" t="n">
         <v>37</v>
       </c>
-      <c r="H10" s="25" t="n">
-        <v>39</v>
+      <c r="H10" s="26" t="n">
+        <v>221</v>
       </c>
       <c r="I10" s="26" t="n">
         <v>221</v>
@@ -67368,6 +68806,12 @@
         <v>221</v>
       </c>
       <c r="AZ10" s="24" t="n">
+        <v>221</v>
+      </c>
+      <c r="BA10" s="25" t="n">
+        <v>220</v>
+      </c>
+      <c r="BB10" s="24" t="n">
         <v>221</v>
       </c>
     </row>
@@ -67394,13 +68838,13 @@
         <v>22</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G12" s="24" t="n">
         <v>14</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="I12" s="24" t="n">
         <v>26</v>
@@ -67533,6 +68977,12 @@
       </c>
       <c r="AZ12" s="24" t="n">
         <v>18</v>
+      </c>
+      <c r="BA12" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB12" s="24" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="13">
@@ -67645,7 +69095,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ1000"/>
+  <dimension ref="A1:BB1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -67925,6 +69375,16 @@
           <t>Kimi K2.6 (Non-Thinking)</t>
         </is>
       </c>
+      <c r="BA2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 5</t>
+        </is>
+      </c>
+      <c r="BB2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 5 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -68083,6 +69543,12 @@
       <c r="AZ3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BA3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -68241,6 +69707,12 @@
       <c r="AZ4" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BA4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB4" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -68399,6 +69871,12 @@
       <c r="AZ5" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BA5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB5" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -68563,6 +70041,12 @@
       <c r="AZ6" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BA6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB6" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -68719,6 +70203,12 @@
         <v>1</v>
       </c>
       <c r="AZ7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB7" s="24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -68879,6 +70369,12 @@
       <c r="AZ8" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BA8" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB8" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -69037,6 +70533,12 @@
       <c r="AZ9" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BA9" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB9" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -69195,6 +70697,12 @@
       <c r="AZ10" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BA10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -69353,6 +70861,12 @@
       <c r="AZ11" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BA11" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB11" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -69511,6 +71025,12 @@
       <c r="AZ12" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BA12" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB12" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -69669,6 +71189,12 @@
       <c r="AZ13" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BA13" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB13" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -69827,6 +71353,12 @@
       <c r="AZ14" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BA14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB14" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -69985,6 +71517,12 @@
       <c r="AZ15" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BA15" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB15" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -70143,6 +71681,12 @@
       <c r="AZ16" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BA16" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB16" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -70301,6 +71845,12 @@
       <c r="AZ17" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BA17" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB17" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -70459,6 +72009,12 @@
       <c r="AZ18" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BA18" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB18" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -70617,6 +72173,12 @@
       <c r="AZ19" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BA19" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB19" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -70775,6 +72337,12 @@
       <c r="AZ20" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BA20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB20" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -70933,6 +72501,12 @@
       <c r="AZ21" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BA21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB21" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -71091,6 +72665,12 @@
       <c r="AZ22" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BA22" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB22" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -71249,6 +72829,12 @@
       <c r="AZ23" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BA23" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB23" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -71407,6 +72993,12 @@
       <c r="AZ24" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BA24" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB24" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -71565,6 +73157,12 @@
       <c r="AZ25" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BA25" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB25" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -71723,6 +73321,12 @@
       <c r="AZ26" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BA26" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB26" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -71740,14 +73344,14 @@
       <c r="E27" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="F27" s="25" t="n">
-        <v>2</v>
+      <c r="F27" s="26" t="n">
+        <v>4</v>
       </c>
       <c r="G27" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="H27" s="25" t="n">
-        <v>2</v>
+      <c r="H27" s="26" t="n">
+        <v>4</v>
       </c>
       <c r="I27" s="26" t="n">
         <v>4</v>
@@ -71883,6 +73487,12 @@
         <v>4</v>
       </c>
       <c r="AZ27" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA27" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB27" s="24" t="n">
         <v>4</v>
       </c>
     </row>
@@ -72043,6 +73653,12 @@
       <c r="AZ28" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BA28" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB28" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -72201,6 +73817,12 @@
       <c r="AZ29" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BA29" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB29" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -72359,6 +73981,12 @@
       <c r="AZ30" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BA30" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB30" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -72517,6 +74145,12 @@
       <c r="AZ31" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BA31" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB31" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -72675,6 +74309,12 @@
       <c r="AZ32" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BA32" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB32" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -72835,6 +74475,12 @@
       <c r="AZ33" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BA33" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB33" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -72995,6 +74641,12 @@
       <c r="AZ34" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BA34" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB34" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -73155,6 +74807,12 @@
       <c r="AZ35" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BA35" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB35" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -73315,6 +74973,12 @@
       <c r="AZ36" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BA36" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB36" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -73475,6 +75139,12 @@
       <c r="AZ37" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BA37" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB37" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -73492,8 +75162,8 @@
       <c r="E38" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="F38" s="25" t="n">
-        <v>5</v>
+      <c r="F38" s="26" t="n">
+        <v>4</v>
       </c>
       <c r="G38" s="26" t="n">
         <v>4</v>
@@ -73633,6 +75303,12 @@
         <v>4</v>
       </c>
       <c r="AZ38" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA38" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB38" s="24" t="n">
         <v>4</v>
       </c>
     </row>
@@ -73795,6 +75471,12 @@
       <c r="AZ39" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BA39" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB39" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -73955,6 +75637,12 @@
       <c r="AZ40" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="BA40" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB40" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -73972,14 +75660,14 @@
       <c r="E41" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="F41" s="25" t="n">
-        <v>1</v>
+      <c r="F41" s="26" t="n">
+        <v>3</v>
       </c>
       <c r="G41" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="H41" s="25" t="n">
-        <v>4</v>
+      <c r="H41" s="26" t="n">
+        <v>3</v>
       </c>
       <c r="I41" s="26" t="n">
         <v>3</v>
@@ -74114,6 +75802,12 @@
       </c>
       <c r="AZ41" s="25" t="n">
         <v>4</v>
+      </c>
+      <c r="BA41" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB41" s="25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -74277,6 +75971,12 @@
       <c r="AZ42" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BA42" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB42" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -74437,6 +76137,12 @@
       <c r="AZ43" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BA43" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB43" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -74597,6 +76303,12 @@
       <c r="AZ44" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BA44" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB44" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -74757,6 +76469,12 @@
       <c r="AZ45" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BA45" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB45" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -74917,6 +76635,12 @@
       <c r="AZ46" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="BA46" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB46" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -75077,6 +76801,12 @@
       <c r="AZ47" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BA47" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB47" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n"/>
@@ -75101,13 +76831,13 @@
         <v>100</v>
       </c>
       <c r="F49" s="24" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="G49" s="24" t="n">
         <v>92</v>
       </c>
       <c r="H49" s="24" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="I49" s="24" t="n">
         <v>100</v>
@@ -75240,6 +76970,12 @@
       </c>
       <c r="AZ49" s="24" t="n">
         <v>93</v>
+      </c>
+      <c r="BA49" s="24" t="n">
+        <v>89</v>
+      </c>
+      <c r="BB49" s="24" t="n">
+        <v>94</v>
       </c>
     </row>
     <row r="50">
@@ -79060,7 +80796,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ1000"/>
+  <dimension ref="A1:BB1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -79341,6 +81077,16 @@
           <t>Kimi K2.6 (Non-Thinking)</t>
         </is>
       </c>
+      <c r="BA2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 5 (high)</t>
+        </is>
+      </c>
+      <c r="BB2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 5</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -79499,6 +81245,12 @@
       <c r="AZ3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BA3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -79659,6 +81411,12 @@
       <c r="AZ4" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="BA4" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB4" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -79817,6 +81575,12 @@
       <c r="AZ5" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BA5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB5" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -79975,6 +81739,12 @@
       <c r="AZ6" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BA6" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB6" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -80131,6 +81901,12 @@
         <v>2</v>
       </c>
       <c r="AZ7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB7" s="24" t="n">
         <v>2</v>
       </c>
     </row>
@@ -80291,6 +82067,12 @@
       <c r="AZ8" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BA8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB8" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -80449,6 +82231,12 @@
       <c r="AZ9" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BA9" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB9" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -80607,6 +82395,12 @@
       <c r="AZ10" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BA10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -80765,6 +82559,12 @@
       <c r="AZ11" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="BA11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB11" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -80923,6 +82723,12 @@
       <c r="AZ12" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BA12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB12" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -81081,6 +82887,12 @@
       <c r="AZ13" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BA13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB13" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -81239,6 +83051,12 @@
       <c r="AZ14" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="BA14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB14" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -81397,6 +83215,12 @@
       <c r="AZ15" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BA15" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB15" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -81555,6 +83379,12 @@
       <c r="AZ16" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BA16" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB16" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -81713,6 +83543,12 @@
       <c r="AZ17" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BA17" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB17" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -81871,6 +83707,12 @@
       <c r="AZ18" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BA18" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB18" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -82029,6 +83871,12 @@
       <c r="AZ19" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BA19" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB19" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -82187,6 +84035,12 @@
       <c r="AZ20" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="BA20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB20" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -82345,6 +84199,12 @@
       <c r="AZ21" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BA21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB21" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -82505,6 +84365,12 @@
       <c r="AZ22" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="BA22" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB22" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n"/>
@@ -82668,6 +84534,12 @@
       </c>
       <c r="AZ24" s="24" t="n">
         <v>37</v>
+      </c>
+      <c r="BA24" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB24" s="24" t="n">
+        <v>47</v>
       </c>
     </row>
     <row r="25">

--- a/2026 수능 LLM 풀이 hard.xlsx
+++ b/2026 수능 LLM 풀이 hard.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB1000"/>
+  <dimension ref="A1:BC1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -770,6 +770,11 @@
           <t>Claude Sonnet 5</t>
         </is>
       </c>
+      <c r="BC2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Fable 5 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -934,6 +939,9 @@
       <c r="BB3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BC3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -1098,6 +1106,9 @@
       <c r="BB4" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC4" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -1262,6 +1273,9 @@
       <c r="BB5" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC5" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1428,6 +1442,9 @@
       <c r="BB6" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BC6" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -1592,6 +1609,9 @@
         <v>4</v>
       </c>
       <c r="BB7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC7" s="24" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1760,6 +1780,9 @@
       <c r="BB8" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BC8" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -1926,6 +1949,9 @@
       <c r="BB9" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="BC9" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -2092,6 +2118,9 @@
       <c r="BB10" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="BC10" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -2258,6 +2287,9 @@
       <c r="BB11" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC11" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -2422,6 +2454,9 @@
       <c r="BB12" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC12" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -2588,6 +2623,9 @@
       <c r="BB13" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="BC13" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -2752,6 +2790,9 @@
       <c r="BB14" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="BC14" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -2916,6 +2957,9 @@
       <c r="BB15" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BC15" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -3082,6 +3126,9 @@
       <c r="BB16" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC16" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -3248,6 +3295,9 @@
       <c r="BB17" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BC17" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -3414,6 +3464,9 @@
       <c r="BB18" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="BC18" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -3580,6 +3633,9 @@
       <c r="BB19" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="BC19" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -3746,6 +3802,9 @@
       <c r="BB20" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="BC20" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -3912,6 +3971,9 @@
       <c r="BB21" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC21" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -4078,6 +4140,9 @@
       <c r="BB22" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BC22" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -4244,6 +4309,9 @@
       <c r="BB23" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="BC23" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -4410,6 +4478,9 @@
       <c r="BB24" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="BC24" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -4576,6 +4647,9 @@
       <c r="BB25" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BC25" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -4742,6 +4816,9 @@
       <c r="BB26" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="BC26" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -4908,6 +4985,9 @@
       <c r="BB27" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC27" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -5074,6 +5154,9 @@
       <c r="BB28" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BC28" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -5242,6 +5325,9 @@
       <c r="BB29" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC29" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -5410,6 +5496,9 @@
       <c r="BB30" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC30" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -5578,6 +5667,9 @@
       <c r="BB31" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BC31" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -5746,6 +5838,9 @@
       <c r="BB32" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BC32" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -5914,6 +6009,9 @@
       <c r="BB33" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BC33" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -6082,6 +6180,9 @@
       <c r="BB34" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC34" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -6250,6 +6351,9 @@
       <c r="BB35" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="BC35" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -6418,6 +6522,9 @@
       <c r="BB36" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="BC36" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n"/>
@@ -6587,6 +6694,9 @@
       </c>
       <c r="BB38" s="24" t="n">
         <v>47</v>
+      </c>
+      <c r="BC38" s="24" t="n">
+        <v>73</v>
       </c>
     </row>
     <row r="39">
@@ -10451,7 +10561,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB1000"/>
+  <dimension ref="A1:BC1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -10738,6 +10848,11 @@
           <t>Claude Sonnet 5</t>
         </is>
       </c>
+      <c r="BC2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Fable 5 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
@@ -10914,6 +11029,9 @@
       <c r="BB3" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="BC3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="n">
@@ -11090,6 +11208,9 @@
       <c r="BB4" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="BC4" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="n">
@@ -11262,6 +11383,9 @@
       <c r="BB5" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BC5" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="n">
@@ -11440,6 +11564,9 @@
       <c r="BB6" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="BC6" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="n">
@@ -11621,6 +11748,9 @@
       </c>
       <c r="BB7" s="25" t="n">
         <v>3</v>
+      </c>
+      <c r="BC7" s="24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -11808,6 +11938,9 @@
       <c r="BB8" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="BC8" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="n">
@@ -11994,6 +12127,9 @@
       <c r="BB9" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BC9" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="n">
@@ -12178,6 +12314,9 @@
       <c r="BB10" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="BC10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="n">
@@ -12360,6 +12499,9 @@
       <c r="BB11" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="BC11" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="n">
@@ -12542,6 +12684,9 @@
       <c r="BB12" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="BC12" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
@@ -12728,6 +12873,9 @@
       <c r="BB13" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="BC13" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="n">
@@ -12916,6 +13064,9 @@
       <c r="BB14" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="BC14" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="n">
@@ -13110,6 +13261,9 @@
       <c r="BB15" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="BC15" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="n">
@@ -13302,6 +13456,9 @@
       <c r="BB16" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="BC16" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="n">
@@ -13494,6 +13651,9 @@
       <c r="BB17" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="BC17" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n">
@@ -13684,6 +13844,9 @@
       <c r="BB18" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="BC18" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="n">
@@ -13876,6 +14039,9 @@
       <c r="BB19" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC19" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="n">
@@ -14068,6 +14234,9 @@
       <c r="BB20" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BC20" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="n">
@@ -14260,6 +14429,9 @@
       <c r="BB21" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC21" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="n">
@@ -14452,6 +14624,9 @@
       <c r="BB22" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="BC22" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="n"/>
@@ -14621,6 +14796,9 @@
       </c>
       <c r="BB24" s="24" t="n">
         <v>11</v>
+      </c>
+      <c r="BC24" s="24" t="n">
+        <v>47</v>
       </c>
     </row>
     <row r="25">
@@ -18541,7 +18719,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB1000"/>
+  <dimension ref="A1:BC1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -18828,6 +19006,11 @@
           <t>Claude Sonnet 5 (high)</t>
         </is>
       </c>
+      <c r="BC2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Fable 5 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
@@ -19008,6 +19191,9 @@
       <c r="BB3" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC3" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="n">
@@ -19188,6 +19374,9 @@
       <c r="BB4" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC4" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="n">
@@ -19370,6 +19559,9 @@
       <c r="BB5" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BC5" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="n">
@@ -19552,6 +19744,9 @@
       <c r="BB6" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BC6" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="n">
@@ -19732,6 +19927,9 @@
         <v>2</v>
       </c>
       <c r="BB7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC7" s="24" t="n">
         <v>2</v>
       </c>
     </row>
@@ -19918,6 +20116,9 @@
       <c r="BB8" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC8" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="n">
@@ -20102,6 +20303,9 @@
       <c r="BB9" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BC9" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="n">
@@ -20288,6 +20492,9 @@
       <c r="BB10" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="n">
@@ -20478,6 +20685,9 @@
       <c r="BB11" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="BC11" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="n">
@@ -20666,6 +20876,9 @@
       <c r="BB12" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BC12" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
@@ -20858,6 +21071,9 @@
       <c r="BB13" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BC13" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="n">
@@ -21048,6 +21264,9 @@
       <c r="BB14" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BC14" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="n">
@@ -21238,6 +21457,9 @@
       <c r="BB15" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="BC15" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="n">
@@ -21428,6 +21650,9 @@
       <c r="BB16" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC16" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="n">
@@ -21618,6 +21843,9 @@
       <c r="BB17" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BC17" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n">
@@ -21812,6 +22040,9 @@
       <c r="BB18" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BC18" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="n">
@@ -22004,6 +22235,9 @@
       <c r="BB19" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC19" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="n">
@@ -22198,6 +22432,9 @@
       <c r="BB20" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BC20" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="n">
@@ -22394,6 +22631,9 @@
       <c r="BB21" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC21" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="n">
@@ -22588,6 +22828,9 @@
       <c r="BB22" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BC22" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="n"/>
@@ -22757,6 +23000,9 @@
       </c>
       <c r="BB24" s="24" t="n">
         <v>45</v>
+      </c>
+      <c r="BC24" s="24" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="25">
@@ -26677,7 +26923,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB1000"/>
+  <dimension ref="A1:BC1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -26964,6 +27210,11 @@
           <t>Claude Sonnet 5</t>
         </is>
       </c>
+      <c r="BC2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Fable 5 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
@@ -27142,6 +27393,11 @@
       <c r="BB3" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC3" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="n">
@@ -27320,6 +27576,11 @@
       <c r="BB4" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC4" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="n">
@@ -27498,6 +27759,11 @@
       <c r="BB5" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="BC5" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="n">
@@ -27676,6 +27942,11 @@
       <c r="BB6" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BC6" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="n">
@@ -27855,6 +28126,11 @@
       </c>
       <c r="BB7" s="25" t="n">
         <v>2</v>
+      </c>
+      <c r="BC7" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -28036,6 +28312,11 @@
       <c r="BB8" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="BC8" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="n">
@@ -28214,6 +28495,11 @@
       <c r="BB9" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BC9" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="n">
@@ -28394,6 +28680,11 @@
       <c r="BB10" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC10" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="n">
@@ -28576,6 +28867,11 @@
       <c r="BB11" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="BC11" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="n">
@@ -28756,6 +29052,11 @@
       <c r="BB12" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BC12" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
@@ -28938,6 +29239,11 @@
       <c r="BB13" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="BC13" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="n">
@@ -29118,6 +29424,11 @@
       <c r="BB14" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="BC14" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="n">
@@ -29300,6 +29611,11 @@
       <c r="BB15" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="BC15" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="n">
@@ -29484,6 +29800,11 @@
       <c r="BB16" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC16" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="n">
@@ -29668,6 +29989,11 @@
       <c r="BB17" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC17" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n">
@@ -29852,6 +30178,11 @@
       <c r="BB18" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="BC18" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="n">
@@ -30036,6 +30367,11 @@
       <c r="BB19" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="BC19" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="n">
@@ -30220,6 +30556,11 @@
       <c r="BB20" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="BC20" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="n">
@@ -30406,6 +30747,11 @@
       <c r="BB21" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="BC21" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="n">
@@ -30590,6 +30936,11 @@
       <c r="BB22" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="BC22" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="n"/>
@@ -30759,6 +31110,9 @@
       </c>
       <c r="BB24" s="24" t="n">
         <v>20</v>
+      </c>
+      <c r="BC24" s="24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -34679,7 +35033,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB1000"/>
+  <dimension ref="A1:BC1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -34966,6 +35320,11 @@
           <t>Claude Sonnet 5</t>
         </is>
       </c>
+      <c r="BC2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Fable 5 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
@@ -35136,6 +35495,11 @@
       <c r="BB3" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="BC3" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="n">
@@ -35308,6 +35672,11 @@
       <c r="BB4" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BC4" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="n">
@@ -35480,6 +35849,11 @@
       <c r="BB5" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="BC5" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="n">
@@ -35652,6 +36026,11 @@
       <c r="BB6" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="BC6" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="n">
@@ -35823,6 +36202,11 @@
       </c>
       <c r="BB7" s="25" t="n">
         <v>3</v>
+      </c>
+      <c r="BC7" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -35998,6 +36382,11 @@
       <c r="BB8" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="BC8" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="n">
@@ -36172,6 +36561,11 @@
       <c r="BB9" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="BC9" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="n">
@@ -36346,6 +36740,11 @@
       <c r="BB10" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="BC10" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="n">
@@ -36522,6 +36921,11 @@
       <c r="BB11" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC11" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="n">
@@ -36702,6 +37106,11 @@
       <c r="BB12" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="BC12" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
@@ -36878,6 +37287,11 @@
       <c r="BB13" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC13" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="n">
@@ -37054,6 +37468,11 @@
       <c r="BB14" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BC14" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="n">
@@ -37232,6 +37651,11 @@
       <c r="BB15" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="BC15" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="n">
@@ -37410,6 +37834,11 @@
       <c r="BB16" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC16" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="n">
@@ -37592,6 +38021,11 @@
       <c r="BB17" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="BC17" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n">
@@ -37770,6 +38204,11 @@
       <c r="BB18" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC18" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="n">
@@ -37948,6 +38387,11 @@
       <c r="BB19" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="BC19" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="n">
@@ -38126,6 +38570,11 @@
       <c r="BB20" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BC20" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="n">
@@ -38304,6 +38753,11 @@
       <c r="BB21" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BC21" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="n">
@@ -38486,6 +38940,11 @@
       <c r="BB22" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="BC22" s="29" t="inlineStr">
+        <is>
+          <t>(검열)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="n"/>
@@ -38655,6 +39114,9 @@
       </c>
       <c r="BB24" s="24" t="n">
         <v>21</v>
+      </c>
+      <c r="BC24" s="24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -42575,7 +43037,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB1000"/>
+  <dimension ref="A1:BC1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -42864,6 +43326,11 @@
           <t>Claude Sonnet 5</t>
         </is>
       </c>
+      <c r="BC2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Fable 5 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -43028,6 +43495,9 @@
       <c r="BB3" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BC3" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -43192,6 +43662,9 @@
       <c r="BB4" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC4" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -43358,6 +43831,9 @@
       <c r="BB5" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BC5" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -43524,6 +44000,9 @@
       <c r="BB6" s="25" t="n">
         <v>3</v>
       </c>
+      <c r="BC6" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -43690,6 +44169,9 @@
       <c r="BB7" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="BC7" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -43856,6 +44338,9 @@
       <c r="BB8" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="BC8" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -44022,6 +44507,9 @@
       <c r="BB9" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC9" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -44188,6 +44676,9 @@
       <c r="BB10" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC10" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -44354,6 +44845,9 @@
       <c r="BB11" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BC11" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -44520,6 +45014,9 @@
       <c r="BB12" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BC12" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -44688,6 +45185,9 @@
       <c r="BB13" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="BC13" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
@@ -44857,6 +45357,9 @@
       </c>
       <c r="BB15" s="24" t="n">
         <v>14</v>
+      </c>
+      <c r="BC15" s="24" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="16">
@@ -48813,7 +49316,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB1000"/>
+  <dimension ref="A1:BC1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -49104,6 +49607,11 @@
           <t>Claude Sonnet 5</t>
         </is>
       </c>
+      <c r="BC2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Fable 5 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -49272,6 +49780,9 @@
       <c r="BB3" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="BC3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -49442,6 +49953,9 @@
       <c r="BB4" s="25" t="n">
         <v>5</v>
       </c>
+      <c r="BC4" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -49614,6 +50128,9 @@
       <c r="BB5" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="BC5" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -49784,6 +50301,9 @@
       <c r="BB6" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC6" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -49954,6 +50474,9 @@
       <c r="BB7" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="BC7" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -50124,6 +50647,9 @@
       <c r="BB8" s="25" t="n">
         <v>1</v>
       </c>
+      <c r="BC8" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -50296,6 +50822,9 @@
       <c r="BB9" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC9" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -50466,6 +50995,9 @@
       <c r="BB10" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -50636,6 +51168,9 @@
       <c r="BB11" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BC11" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -50806,6 +51341,9 @@
       <c r="BB12" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC12" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -50976,6 +51514,9 @@
       <c r="BB13" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BC13" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
@@ -51145,6 +51686,9 @@
       </c>
       <c r="BB15" s="24" t="n">
         <v>13</v>
+      </c>
+      <c r="BC15" s="24" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="16">
@@ -55101,7 +55645,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB37"/>
+  <dimension ref="A1:BC37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -55388,6 +55932,11 @@
           <t>Claude Sonnet 5 (high)</t>
         </is>
       </c>
+      <c r="BC2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Fable 5 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -55556,6 +56105,9 @@
       <c r="BB3" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BC3" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -55724,6 +56276,9 @@
       <c r="BB4" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC4" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -55892,6 +56447,9 @@
       <c r="BB5" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC5" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -56060,6 +56618,9 @@
       <c r="BB6" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BC6" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -56226,6 +56787,9 @@
         <v>3</v>
       </c>
       <c r="BB7" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC7" s="24" t="n">
         <v>3</v>
       </c>
     </row>
@@ -56396,6 +56960,9 @@
       <c r="BB8" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BC8" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -56564,6 +57131,9 @@
       <c r="BB9" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC9" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -56734,6 +57304,9 @@
       <c r="BB10" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BC10" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -56904,6 +57477,9 @@
       <c r="BB11" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC11" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -57080,6 +57656,9 @@
       <c r="BB12" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BC12" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -57254,6 +57833,9 @@
       <c r="BB13" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BC13" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -57428,6 +58010,9 @@
       <c r="BB14" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BC14" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -57602,6 +58187,9 @@
       <c r="BB15" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC15" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -57780,6 +58368,9 @@
       <c r="BB16" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC16" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -57960,6 +58551,9 @@
       <c r="BB17" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC17" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -58134,6 +58728,9 @@
       <c r="BB18" s="24" t="n">
         <v>9</v>
       </c>
+      <c r="BC18" s="24" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -58308,6 +58905,9 @@
       <c r="BB19" s="24" t="n">
         <v>16</v>
       </c>
+      <c r="BC19" s="24" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -58486,6 +59086,9 @@
       <c r="BB20" s="24" t="n">
         <v>12</v>
       </c>
+      <c r="BC20" s="24" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -58664,6 +59267,9 @@
       <c r="BB21" s="24" t="n">
         <v>15</v>
       </c>
+      <c r="BC21" s="24" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -58852,6 +59458,9 @@
       <c r="BB22" s="24" t="n">
         <v>130</v>
       </c>
+      <c r="BC22" s="24" t="n">
+        <v>130</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -59046,6 +59655,9 @@
       <c r="BB23" s="24" t="n">
         <v>65</v>
       </c>
+      <c r="BC23" s="24" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -59240,6 +59852,9 @@
       <c r="BB24" s="24" t="n">
         <v>457</v>
       </c>
+      <c r="BC24" s="24" t="n">
+        <v>457</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n"/>
@@ -59408,6 +60023,9 @@
         <v>50</v>
       </c>
       <c r="BB26" s="24" t="n">
+        <v>74</v>
+      </c>
+      <c r="BC26" s="24" t="n">
         <v>74</v>
       </c>
     </row>
@@ -59469,7 +60087,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB37"/>
+  <dimension ref="A1:BC37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -59756,6 +60374,11 @@
           <t>Claude Sonnet 5 (high)</t>
         </is>
       </c>
+      <c r="BC2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Fable 5 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -59920,6 +60543,9 @@
       <c r="BB3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BC3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -60084,6 +60710,9 @@
       <c r="BB4" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BC4" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -60250,6 +60879,9 @@
       <c r="BB5" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BC5" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -60414,6 +61046,9 @@
       <c r="BB6" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC6" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -60580,6 +61215,9 @@
       <c r="BB7" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC7" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -60754,6 +61392,9 @@
       <c r="BB8" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BC8" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -60926,6 +61567,9 @@
       <c r="BB9" s="24" t="n">
         <v>977</v>
       </c>
+      <c r="BC9" s="24" t="n">
+        <v>977</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -61102,6 +61746,9 @@
       <c r="BB10" s="24" t="n">
         <v>262</v>
       </c>
+      <c r="BC10" s="24" t="n">
+        <v>262</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -61270,6 +61917,9 @@
         <v>18</v>
       </c>
       <c r="BB12" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="BC12" s="24" t="n">
         <v>26</v>
       </c>
     </row>
@@ -61383,7 +62033,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB1000"/>
+  <dimension ref="A1:BC1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -61672,6 +62322,11 @@
           <t>Claude Sonnet 5 (high)</t>
         </is>
       </c>
+      <c r="BC2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Fable 5 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -61840,6 +62495,9 @@
       <c r="BB3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BC3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -62008,6 +62666,9 @@
       <c r="BB4" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC4" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -62176,6 +62837,9 @@
       <c r="BB5" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BC5" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -62344,6 +63008,9 @@
       <c r="BB6" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BC6" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -62512,6 +63179,9 @@
       <c r="BB7" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BC7" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -62680,6 +63350,9 @@
       <c r="BB8" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC8" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -62856,6 +63529,9 @@
       <c r="BB9" s="24" t="n">
         <v>97</v>
       </c>
+      <c r="BC9" s="24" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -63042,6 +63718,9 @@
       <c r="BB10" s="24" t="n">
         <v>11</v>
       </c>
+      <c r="BC10" s="24" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -63210,6 +63889,9 @@
         <v>18</v>
       </c>
       <c r="BB12" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="BC12" s="24" t="n">
         <v>26</v>
       </c>
     </row>
@@ -67179,7 +67861,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB37"/>
+  <dimension ref="A1:BC37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -67466,6 +68148,11 @@
           <t>Claude Sonnet 5 (high)</t>
         </is>
       </c>
+      <c r="BC2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Fable 5 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -67632,6 +68319,9 @@
       <c r="BB3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BC3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -67798,6 +68488,9 @@
       <c r="BB4" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BC4" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -67968,6 +68661,9 @@
       <c r="BB5" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC5" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -68136,6 +68832,9 @@
       <c r="BB6" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BC6" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -68304,6 +69003,9 @@
       <c r="BB7" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC7" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -68470,6 +69172,9 @@
       <c r="BB8" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC8" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -68642,6 +69347,9 @@
       <c r="BB9" s="24" t="n">
         <v>360</v>
       </c>
+      <c r="BC9" s="24" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -68814,6 +69522,9 @@
       <c r="BB10" s="24" t="n">
         <v>221</v>
       </c>
+      <c r="BC10" s="24" t="n">
+        <v>221</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -68982,6 +69693,9 @@
         <v>14</v>
       </c>
       <c r="BB12" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="BC12" s="24" t="n">
         <v>26</v>
       </c>
     </row>
@@ -69095,7 +69809,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB1000"/>
+  <dimension ref="A1:BC1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -69385,6 +70099,11 @@
           <t>Claude Sonnet 5 (high)</t>
         </is>
       </c>
+      <c r="BC2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Fable 5 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -69549,6 +70268,9 @@
       <c r="BB3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BC3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -69713,6 +70435,9 @@
       <c r="BB4" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BC4" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -69877,6 +70602,9 @@
       <c r="BB5" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BC5" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -70047,6 +70775,9 @@
       <c r="BB6" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC6" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -70209,6 +70940,9 @@
         <v>1</v>
       </c>
       <c r="BB7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC7" s="24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -70375,6 +71109,9 @@
       <c r="BB8" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC8" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -70539,6 +71276,9 @@
       <c r="BB9" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BC9" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -70703,6 +71443,9 @@
       <c r="BB10" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -70867,6 +71610,9 @@
       <c r="BB11" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC11" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -71031,6 +71777,9 @@
       <c r="BB12" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC12" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -71195,6 +71944,9 @@
       <c r="BB13" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BC13" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -71359,6 +72111,9 @@
       <c r="BB14" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BC14" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -71523,6 +72278,9 @@
       <c r="BB15" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BC15" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -71687,6 +72445,9 @@
       <c r="BB16" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BC16" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -71851,6 +72612,9 @@
       <c r="BB17" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BC17" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -72015,6 +72779,9 @@
       <c r="BB18" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BC18" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -72179,6 +72946,9 @@
       <c r="BB19" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC19" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -72343,6 +73113,9 @@
       <c r="BB20" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BC20" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -72507,6 +73280,9 @@
       <c r="BB21" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BC21" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -72671,6 +73447,9 @@
       <c r="BB22" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BC22" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -72835,6 +73614,9 @@
       <c r="BB23" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BC23" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -72999,6 +73781,9 @@
       <c r="BB24" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BC24" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -73163,6 +73948,9 @@
       <c r="BB25" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BC25" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -73327,6 +74115,9 @@
       <c r="BB26" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BC26" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -73495,6 +74286,9 @@
       <c r="BB27" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC27" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -73659,6 +74453,9 @@
       <c r="BB28" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BC28" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -73823,6 +74620,9 @@
       <c r="BB29" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC29" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -73987,6 +74787,9 @@
       <c r="BB30" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC30" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -74151,6 +74954,9 @@
       <c r="BB31" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BC31" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -74315,6 +75121,9 @@
       <c r="BB32" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC32" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -74481,6 +75290,9 @@
       <c r="BB33" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BC33" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -74647,6 +75459,9 @@
       <c r="BB34" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC34" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -74813,6 +75628,9 @@
       <c r="BB35" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC35" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -74979,6 +75797,9 @@
       <c r="BB36" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BC36" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -75145,6 +75966,9 @@
       <c r="BB37" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC37" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -75311,6 +76135,9 @@
       <c r="BB38" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC38" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -75477,6 +76304,9 @@
       <c r="BB39" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="BC39" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -75643,6 +76473,9 @@
       <c r="BB40" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC40" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -75809,6 +76642,9 @@
       <c r="BB41" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="BC41" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -75977,6 +76813,9 @@
       <c r="BB42" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BC42" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -76143,6 +76982,9 @@
       <c r="BB43" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BC43" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -76309,6 +77151,9 @@
       <c r="BB44" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC44" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -76475,6 +77320,9 @@
       <c r="BB45" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC45" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -76641,6 +77489,9 @@
       <c r="BB46" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BC46" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -76807,6 +77658,9 @@
       <c r="BB47" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC47" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n"/>
@@ -76976,6 +77830,9 @@
       </c>
       <c r="BB49" s="24" t="n">
         <v>94</v>
+      </c>
+      <c r="BC49" s="24" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="50">
@@ -80796,7 +81653,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB1000"/>
+  <dimension ref="A1:BC1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -81087,6 +81944,11 @@
           <t>Claude Sonnet 5</t>
         </is>
       </c>
+      <c r="BC2" s="23" t="inlineStr">
+        <is>
+          <t>Claude Fable 5 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -81251,6 +82113,9 @@
       <c r="BB3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BC3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -81417,6 +82282,9 @@
       <c r="BB4" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BC4" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -81581,6 +82449,9 @@
       <c r="BB5" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BC5" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -81745,6 +82616,9 @@
       <c r="BB6" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC6" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -81907,6 +82781,9 @@
         <v>2</v>
       </c>
       <c r="BB7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC7" s="24" t="n">
         <v>2</v>
       </c>
     </row>
@@ -82073,6 +82950,9 @@
       <c r="BB8" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC8" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -82237,6 +83117,9 @@
       <c r="BB9" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC9" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -82401,6 +83284,9 @@
       <c r="BB10" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -82565,6 +83451,9 @@
       <c r="BB11" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="BC11" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -82729,6 +83618,9 @@
       <c r="BB12" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BC12" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -82893,6 +83785,9 @@
       <c r="BB13" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BC13" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -83057,6 +83952,9 @@
       <c r="BB14" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BC14" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -83221,6 +84119,9 @@
       <c r="BB15" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC15" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -83385,6 +84286,9 @@
       <c r="BB16" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC16" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -83549,6 +84453,9 @@
       <c r="BB17" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BC17" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -83713,6 +84620,9 @@
       <c r="BB18" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BC18" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -83877,6 +84787,9 @@
       <c r="BB19" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BC19" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -84041,6 +84954,9 @@
       <c r="BB20" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BC20" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -84205,6 +85121,9 @@
       <c r="BB21" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BC21" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -84371,6 +85290,9 @@
       <c r="BB22" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BC22" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n"/>
@@ -84540,6 +85462,9 @@
       </c>
       <c r="BB24" s="24" t="n">
         <v>47</v>
+      </c>
+      <c r="BC24" s="24" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="25">

--- a/2026 수능 LLM 풀이 hard.xlsx
+++ b/2026 수능 LLM 풀이 hard.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC1000"/>
+  <dimension ref="A1:BD1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -775,6 +775,11 @@
           <t>Claude Fable 5 (high)</t>
         </is>
       </c>
+      <c r="BD2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.5 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -942,6 +947,9 @@
       <c r="BC3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -1109,6 +1117,9 @@
       <c r="BC4" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD4" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -1276,6 +1287,9 @@
       <c r="BC5" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD5" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1445,6 +1459,9 @@
       <c r="BC6" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BD6" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -1612,6 +1629,9 @@
         <v>4</v>
       </c>
       <c r="BC7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD7" s="24" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1783,6 +1803,9 @@
       <c r="BC8" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD8" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -1952,6 +1975,9 @@
       <c r="BC9" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD9" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -2121,6 +2147,9 @@
       <c r="BC10" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD10" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -2290,6 +2319,9 @@
       <c r="BC11" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD11" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -2457,6 +2489,9 @@
       <c r="BC12" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD12" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -2626,6 +2661,9 @@
       <c r="BC13" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD13" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -2793,6 +2831,9 @@
       <c r="BC14" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BD14" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -2960,6 +3001,9 @@
       <c r="BC15" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BD15" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -3129,6 +3173,9 @@
       <c r="BC16" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD16" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -3298,6 +3345,9 @@
       <c r="BC17" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BD17" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -3467,6 +3517,9 @@
       <c r="BC18" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD18" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -3636,6 +3689,9 @@
       <c r="BC19" s="25" t="n">
         <v>2</v>
       </c>
+      <c r="BD19" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -3805,6 +3861,9 @@
       <c r="BC20" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD20" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -3974,6 +4033,9 @@
       <c r="BC21" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD21" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -4143,6 +4205,9 @@
       <c r="BC22" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD22" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -4312,6 +4377,9 @@
       <c r="BC23" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD23" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -4481,6 +4549,9 @@
       <c r="BC24" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD24" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -4650,6 +4721,9 @@
       <c r="BC25" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BD25" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -4819,6 +4893,9 @@
       <c r="BC26" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD26" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -4988,6 +5065,9 @@
       <c r="BC27" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD27" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -5157,6 +5237,9 @@
       <c r="BC28" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD28" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -5328,6 +5411,9 @@
       <c r="BC29" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD29" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -5499,6 +5585,9 @@
       <c r="BC30" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD30" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -5670,6 +5759,9 @@
       <c r="BC31" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BD31" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -5841,6 +5933,9 @@
       <c r="BC32" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD32" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -6012,6 +6107,9 @@
       <c r="BC33" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD33" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -6183,6 +6281,9 @@
       <c r="BC34" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD34" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -6354,6 +6455,9 @@
       <c r="BC35" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BD35" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -6525,6 +6629,9 @@
       <c r="BC36" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD36" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n"/>
@@ -6697,6 +6804,9 @@
       </c>
       <c r="BC38" s="24" t="n">
         <v>73</v>
+      </c>
+      <c r="BD38" s="24" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="39">
@@ -10561,7 +10671,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC1000"/>
+  <dimension ref="A1:BD1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -10853,6 +10963,11 @@
           <t>Claude Fable 5 (high)</t>
         </is>
       </c>
+      <c r="BD2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.5 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
@@ -11032,6 +11147,11 @@
       <c r="BC3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD3" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="n">
@@ -11211,6 +11331,11 @@
       <c r="BC4" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD4" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="n">
@@ -11386,6 +11511,11 @@
       <c r="BC5" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD5" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="n">
@@ -11567,6 +11697,11 @@
       <c r="BC6" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD6" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="n">
@@ -11751,6 +11886,11 @@
       </c>
       <c r="BC7" s="24" t="n">
         <v>1</v>
+      </c>
+      <c r="BD7" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -11941,6 +12081,11 @@
       <c r="BC8" s="25" t="n">
         <v>4</v>
       </c>
+      <c r="BD8" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="n">
@@ -12130,6 +12275,11 @@
       <c r="BC9" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="n">
@@ -12317,6 +12467,11 @@
       <c r="BC10" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="n">
@@ -12502,6 +12657,11 @@
       <c r="BC11" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD11" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="n">
@@ -12687,6 +12847,11 @@
       <c r="BC12" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD12" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
@@ -12876,6 +13041,11 @@
       <c r="BC13" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD13" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="n">
@@ -13067,6 +13237,11 @@
       <c r="BC14" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BD14" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="n">
@@ -13264,6 +13439,11 @@
       <c r="BC15" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD15" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="n">
@@ -13459,6 +13639,11 @@
       <c r="BC16" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD16" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="n">
@@ -13654,6 +13839,11 @@
       <c r="BC17" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BD17" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n">
@@ -13847,6 +14037,11 @@
       <c r="BC18" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD18" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="n">
@@ -14042,6 +14237,11 @@
       <c r="BC19" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD19" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="n">
@@ -14237,6 +14437,11 @@
       <c r="BC20" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD20" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="n">
@@ -14432,6 +14637,11 @@
       <c r="BC21" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD21" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="n">
@@ -14627,6 +14837,11 @@
       <c r="BC22" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BD22" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="n"/>
@@ -14799,6 +15014,9 @@
       </c>
       <c r="BC24" s="24" t="n">
         <v>47</v>
+      </c>
+      <c r="BD24" s="24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -18719,7 +18937,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC1000"/>
+  <dimension ref="A1:BD1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -19011,6 +19229,11 @@
           <t>Claude Fable 5 (high)</t>
         </is>
       </c>
+      <c r="BD2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.5 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
@@ -19194,6 +19417,11 @@
       <c r="BC3" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD3" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="n">
@@ -19377,6 +19605,11 @@
       <c r="BC4" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD4" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="n">
@@ -19562,6 +19795,11 @@
       <c r="BC5" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD5" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="n">
@@ -19747,6 +19985,11 @@
       <c r="BC6" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BD6" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="n">
@@ -19931,6 +20174,11 @@
       </c>
       <c r="BC7" s="24" t="n">
         <v>2</v>
+      </c>
+      <c r="BD7" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -20119,6 +20367,11 @@
       <c r="BC8" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD8" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="n">
@@ -20306,6 +20559,11 @@
       <c r="BC9" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="n">
@@ -20495,6 +20753,11 @@
       <c r="BC10" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="n">
@@ -20688,6 +20951,11 @@
       <c r="BC11" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD11" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="n">
@@ -20879,6 +21147,11 @@
       <c r="BC12" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BD12" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
@@ -21074,6 +21347,11 @@
       <c r="BC13" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD13" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="n">
@@ -21267,6 +21545,11 @@
       <c r="BC14" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD14" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="n">
@@ -21460,6 +21743,11 @@
       <c r="BC15" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD15" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="n">
@@ -21653,6 +21941,11 @@
       <c r="BC16" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD16" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="n">
@@ -21846,6 +22139,11 @@
       <c r="BC17" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BD17" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n">
@@ -22043,6 +22341,11 @@
       <c r="BC18" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD18" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="n">
@@ -22238,6 +22541,11 @@
       <c r="BC19" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD19" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="n">
@@ -22435,6 +22743,11 @@
       <c r="BC20" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD20" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="n">
@@ -22634,6 +22947,11 @@
       <c r="BC21" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD21" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="n">
@@ -22831,6 +23149,11 @@
       <c r="BC22" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BD22" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="n"/>
@@ -23003,6 +23326,9 @@
       </c>
       <c r="BC24" s="24" t="n">
         <v>50</v>
+      </c>
+      <c r="BD24" s="24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -26923,7 +27249,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC1000"/>
+  <dimension ref="A1:BD1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -27215,6 +27541,11 @@
           <t>Claude Fable 5 (high)</t>
         </is>
       </c>
+      <c r="BD2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.5 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
@@ -27398,6 +27729,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD3" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="n">
@@ -27581,6 +27915,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD4" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="n">
@@ -27764,6 +28101,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD5" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="n">
@@ -27947,6 +28287,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD6" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="n">
@@ -28131,6 +28474,9 @@
         <is>
           <t>(검열)</t>
         </is>
+      </c>
+      <c r="BD7" s="24" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -28317,6 +28663,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD8" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="n">
@@ -28500,6 +28849,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD9" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="n">
@@ -28685,6 +29037,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="n">
@@ -28872,6 +29227,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD11" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="n">
@@ -29057,6 +29415,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD12" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
@@ -29244,6 +29605,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD13" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="n">
@@ -29429,6 +29793,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD14" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="n">
@@ -29616,6 +29983,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD15" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="n">
@@ -29805,6 +30175,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD16" s="25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="n">
@@ -29994,6 +30367,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD17" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n">
@@ -30183,6 +30559,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD18" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="n">
@@ -30372,6 +30751,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD19" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="n">
@@ -30561,6 +30943,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD20" s="25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="n">
@@ -30752,6 +31137,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD21" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="n">
@@ -30941,6 +31329,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD22" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="n"/>
@@ -31113,6 +31504,9 @@
       </c>
       <c r="BC24" s="24" t="n">
         <v>0</v>
+      </c>
+      <c r="BD24" s="24" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="25">
@@ -35033,7 +35427,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC1000"/>
+  <dimension ref="A1:BD1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -35325,6 +35719,11 @@
           <t>Claude Fable 5 (high)</t>
         </is>
       </c>
+      <c r="BD2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.5 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
@@ -35500,6 +35899,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD3" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="n">
@@ -35677,6 +36079,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD4" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="n">
@@ -35854,6 +36259,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD5" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="n">
@@ -36031,6 +36439,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD6" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="n">
@@ -36207,6 +36618,9 @@
         <is>
           <t>(검열)</t>
         </is>
+      </c>
+      <c r="BD7" s="24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -36387,6 +36801,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD8" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="n">
@@ -36566,6 +36983,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD9" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="n">
@@ -36745,6 +37165,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="n">
@@ -36926,6 +37349,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD11" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="n">
@@ -37111,6 +37537,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD12" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
@@ -37292,6 +37721,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD13" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="n">
@@ -37473,6 +37905,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD14" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="n">
@@ -37656,6 +38091,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD15" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="n">
@@ -37839,6 +38277,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD16" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="20" t="n">
@@ -38026,6 +38467,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD17" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n">
@@ -38209,6 +38653,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD18" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="n">
@@ -38392,6 +38839,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD19" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="n">
@@ -38575,6 +39025,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD20" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="n">
@@ -38758,6 +39211,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD21" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="n">
@@ -38945,6 +39401,9 @@
           <t>(검열)</t>
         </is>
       </c>
+      <c r="BD22" s="25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="n"/>
@@ -39117,6 +39576,9 @@
       </c>
       <c r="BC24" s="24" t="n">
         <v>0</v>
+      </c>
+      <c r="BD24" s="24" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="25">
@@ -43037,7 +43499,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC1000"/>
+  <dimension ref="A1:BD1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -43331,6 +43793,11 @@
           <t>Claude Fable 5 (high)</t>
         </is>
       </c>
+      <c r="BD2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.5 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -43498,6 +43965,9 @@
       <c r="BC3" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD3" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -43665,6 +44135,9 @@
       <c r="BC4" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD4" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -43834,6 +44307,9 @@
       <c r="BC5" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD5" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -44003,6 +44479,9 @@
       <c r="BC6" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BD6" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -44172,6 +44651,9 @@
       <c r="BC7" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD7" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -44341,6 +44823,9 @@
       <c r="BC8" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD8" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -44510,6 +44995,9 @@
       <c r="BC9" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD9" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -44679,6 +45167,9 @@
       <c r="BC10" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD10" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -44848,6 +45339,9 @@
       <c r="BC11" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD11" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -45017,6 +45511,9 @@
       <c r="BC12" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD12" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -45188,6 +45685,9 @@
       <c r="BC13" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD13" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
@@ -45359,6 +45859,9 @@
         <v>14</v>
       </c>
       <c r="BC15" s="24" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD15" s="24" t="n">
         <v>24</v>
       </c>
     </row>
@@ -49316,7 +49819,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC1000"/>
+  <dimension ref="A1:BD1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -49612,6 +50115,11 @@
           <t>Claude Fable 5 (high)</t>
         </is>
       </c>
+      <c r="BD2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.5 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -49783,6 +50291,11 @@
       <c r="BC3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD3" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -49956,6 +50469,11 @@
       <c r="BC4" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD4" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -50131,6 +50649,11 @@
       <c r="BC5" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD5" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -50304,6 +50827,11 @@
       <c r="BC6" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD6" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -50477,6 +51005,11 @@
       <c r="BC7" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BD7" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -50650,6 +51183,11 @@
       <c r="BC8" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD8" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -50825,6 +51363,11 @@
       <c r="BC9" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -50998,6 +51541,11 @@
       <c r="BC10" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -51171,6 +51719,11 @@
       <c r="BC11" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD11" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -51344,6 +51897,11 @@
       <c r="BC12" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD12" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -51517,6 +52075,11 @@
       <c r="BC13" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD13" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
@@ -51689,6 +52252,9 @@
       </c>
       <c r="BC15" s="24" t="n">
         <v>24</v>
+      </c>
+      <c r="BD15" s="24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -55645,7 +56211,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC37"/>
+  <dimension ref="A1:BD37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -55937,6 +56503,11 @@
           <t>Claude Fable 5 (high)</t>
         </is>
       </c>
+      <c r="BD2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.5 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -56108,6 +56679,9 @@
       <c r="BC3" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BD3" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -56279,6 +56853,9 @@
       <c r="BC4" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD4" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -56450,6 +57027,9 @@
       <c r="BC5" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD5" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -56621,6 +57201,9 @@
       <c r="BC6" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD6" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -56790,6 +57373,9 @@
         <v>3</v>
       </c>
       <c r="BC7" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD7" s="24" t="n">
         <v>3</v>
       </c>
     </row>
@@ -56963,6 +57549,9 @@
       <c r="BC8" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD8" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -57134,6 +57723,9 @@
       <c r="BC9" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD9" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -57307,6 +57899,9 @@
       <c r="BC10" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BD10" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -57480,6 +58075,9 @@
       <c r="BC11" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD11" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -57659,6 +58257,9 @@
       <c r="BC12" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD12" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -57836,6 +58437,9 @@
       <c r="BC13" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD13" s="25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -58013,6 +58617,9 @@
       <c r="BC14" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD14" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -58190,6 +58797,9 @@
       <c r="BC15" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD15" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -58371,6 +58981,9 @@
       <c r="BC16" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD16" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -58554,6 +59167,9 @@
       <c r="BC17" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD17" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -58731,6 +59347,9 @@
       <c r="BC18" s="24" t="n">
         <v>9</v>
       </c>
+      <c r="BD18" s="24" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -58908,6 +59527,9 @@
       <c r="BC19" s="24" t="n">
         <v>16</v>
       </c>
+      <c r="BD19" s="24" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -59089,6 +59711,9 @@
       <c r="BC20" s="24" t="n">
         <v>12</v>
       </c>
+      <c r="BD20" s="24" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -59270,6 +59895,9 @@
       <c r="BC21" s="24" t="n">
         <v>15</v>
       </c>
+      <c r="BD21" s="24" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -59461,6 +60089,9 @@
       <c r="BC22" s="24" t="n">
         <v>130</v>
       </c>
+      <c r="BD22" s="24" t="n">
+        <v>130</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -59658,6 +60289,9 @@
       <c r="BC23" s="24" t="n">
         <v>65</v>
       </c>
+      <c r="BD23" s="25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -59855,6 +60489,9 @@
       <c r="BC24" s="24" t="n">
         <v>457</v>
       </c>
+      <c r="BD24" s="24" t="n">
+        <v>457</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n"/>
@@ -60027,6 +60664,9 @@
       </c>
       <c r="BC26" s="24" t="n">
         <v>74</v>
+      </c>
+      <c r="BD26" s="24" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="27">
@@ -60087,7 +60727,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC37"/>
+  <dimension ref="A1:BD37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -60379,6 +61019,11 @@
           <t>Claude Fable 5 (high)</t>
         </is>
       </c>
+      <c r="BD2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.5 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -60546,6 +61191,9 @@
       <c r="BC3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -60713,6 +61361,9 @@
       <c r="BC4" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BD4" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -60882,6 +61533,9 @@
       <c r="BC5" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD5" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -61049,6 +61703,9 @@
       <c r="BC6" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD6" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -61218,6 +61875,9 @@
       <c r="BC7" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD7" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -61395,6 +62055,9 @@
       <c r="BC8" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD8" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -61570,6 +62233,9 @@
       <c r="BC9" s="24" t="n">
         <v>977</v>
       </c>
+      <c r="BD9" s="24" t="n">
+        <v>977</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -61749,6 +62415,9 @@
       <c r="BC10" s="24" t="n">
         <v>262</v>
       </c>
+      <c r="BD10" s="24" t="n">
+        <v>262</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -61920,6 +62589,9 @@
         <v>26</v>
       </c>
       <c r="BC12" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD12" s="24" t="n">
         <v>26</v>
       </c>
     </row>
@@ -62033,7 +62705,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC1000"/>
+  <dimension ref="A1:BD1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -62327,6 +62999,11 @@
           <t>Claude Fable 5 (high)</t>
         </is>
       </c>
+      <c r="BD2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.5 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -62498,6 +63175,9 @@
       <c r="BC3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -62669,6 +63349,9 @@
       <c r="BC4" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD4" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -62840,6 +63523,9 @@
       <c r="BC5" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD5" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -63011,6 +63697,9 @@
       <c r="BC6" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BD6" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -63182,6 +63871,9 @@
       <c r="BC7" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD7" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -63353,6 +64045,9 @@
       <c r="BC8" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD8" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -63532,6 +64227,9 @@
       <c r="BC9" s="24" t="n">
         <v>97</v>
       </c>
+      <c r="BD9" s="24" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -63721,6 +64419,9 @@
       <c r="BC10" s="24" t="n">
         <v>11</v>
       </c>
+      <c r="BD10" s="24" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -63892,6 +64593,9 @@
         <v>26</v>
       </c>
       <c r="BC12" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD12" s="24" t="n">
         <v>26</v>
       </c>
     </row>
@@ -67861,7 +68565,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC37"/>
+  <dimension ref="A1:BD37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -68153,6 +68857,11 @@
           <t>Claude Fable 5 (high)</t>
         </is>
       </c>
+      <c r="BD2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.5 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -68322,6 +69031,9 @@
       <c r="BC3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -68491,6 +69203,9 @@
       <c r="BC4" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BD4" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -68664,6 +69379,9 @@
       <c r="BC5" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD5" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -68835,6 +69553,9 @@
       <c r="BC6" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD6" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -69006,6 +69727,9 @@
       <c r="BC7" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD7" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -69175,6 +69899,9 @@
       <c r="BC8" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD8" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -69350,6 +70077,9 @@
       <c r="BC9" s="24" t="n">
         <v>360</v>
       </c>
+      <c r="BD9" s="24" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -69525,6 +70255,9 @@
       <c r="BC10" s="24" t="n">
         <v>221</v>
       </c>
+      <c r="BD10" s="24" t="n">
+        <v>221</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -69696,6 +70429,9 @@
         <v>26</v>
       </c>
       <c r="BC12" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD12" s="24" t="n">
         <v>26</v>
       </c>
     </row>
@@ -69809,7 +70545,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC1000"/>
+  <dimension ref="A1:BD1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -70104,6 +70840,11 @@
           <t>Claude Fable 5 (high)</t>
         </is>
       </c>
+      <c r="BD2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.5 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -70271,6 +71012,9 @@
       <c r="BC3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -70438,6 +71182,9 @@
       <c r="BC4" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD4" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -70605,6 +71352,9 @@
       <c r="BC5" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BD5" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -70778,6 +71528,9 @@
       <c r="BC6" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD6" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -70943,6 +71696,9 @@
         <v>1</v>
       </c>
       <c r="BC7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD7" s="24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -71112,6 +71868,9 @@
       <c r="BC8" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD8" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -71279,6 +72038,9 @@
       <c r="BC9" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BD9" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -71446,6 +72208,9 @@
       <c r="BC10" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -71613,6 +72378,9 @@
       <c r="BC11" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD11" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -71780,6 +72548,9 @@
       <c r="BC12" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD12" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -71947,6 +72718,9 @@
       <c r="BC13" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BD13" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -72114,6 +72888,9 @@
       <c r="BC14" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD14" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -72281,6 +73058,9 @@
       <c r="BC15" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD15" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -72448,6 +73228,9 @@
       <c r="BC16" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD16" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -72615,6 +73398,9 @@
       <c r="BC17" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD17" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -72782,6 +73568,9 @@
       <c r="BC18" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BD18" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -72949,6 +73738,9 @@
       <c r="BC19" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD19" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -73116,6 +73908,9 @@
       <c r="BC20" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD20" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -73283,6 +74078,9 @@
       <c r="BC21" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BD21" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -73450,6 +74248,9 @@
       <c r="BC22" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD22" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -73617,6 +74418,9 @@
       <c r="BC23" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD23" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -73784,6 +74588,9 @@
       <c r="BC24" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BD24" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -73951,6 +74758,9 @@
       <c r="BC25" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD25" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -74118,6 +74928,9 @@
       <c r="BC26" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD26" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -74289,6 +75102,9 @@
       <c r="BC27" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD27" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -74456,6 +75272,9 @@
       <c r="BC28" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD28" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -74623,6 +75442,9 @@
       <c r="BC29" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD29" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -74790,6 +75612,9 @@
       <c r="BC30" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD30" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -74957,6 +75782,9 @@
       <c r="BC31" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD31" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -75124,6 +75952,9 @@
       <c r="BC32" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD32" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -75293,6 +76124,9 @@
       <c r="BC33" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BD33" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -75462,6 +76296,9 @@
       <c r="BC34" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD34" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -75631,6 +76468,9 @@
       <c r="BC35" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD35" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -75800,6 +76640,9 @@
       <c r="BC36" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD36" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -75969,6 +76812,9 @@
       <c r="BC37" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD37" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -76138,6 +76984,9 @@
       <c r="BC38" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD38" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -76307,6 +77156,9 @@
       <c r="BC39" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD39" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -76476,6 +77328,9 @@
       <c r="BC40" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD40" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -76645,6 +77500,9 @@
       <c r="BC41" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD41" s="25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -76816,6 +77674,9 @@
       <c r="BC42" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD42" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -76985,6 +77846,9 @@
       <c r="BC43" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD43" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -77154,6 +78018,9 @@
       <c r="BC44" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD44" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -77323,6 +78190,9 @@
       <c r="BC45" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD45" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -77492,6 +78362,9 @@
       <c r="BC46" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD46" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -77661,6 +78534,9 @@
       <c r="BC47" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD47" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n"/>
@@ -77833,6 +78709,9 @@
       </c>
       <c r="BC49" s="24" t="n">
         <v>100</v>
+      </c>
+      <c r="BD49" s="24" t="n">
+        <v>97</v>
       </c>
     </row>
     <row r="50">
@@ -81653,7 +82532,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC1000"/>
+  <dimension ref="A1:BD1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.5" customWidth="1" style="22" min="1" max="1"/>
@@ -81949,6 +82828,11 @@
           <t>Claude Fable 5 (high)</t>
         </is>
       </c>
+      <c r="BD2" s="23" t="inlineStr">
+        <is>
+          <t>Grok 4.5 (high)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -82116,6 +83000,9 @@
       <c r="BC3" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD3" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -82285,6 +83172,9 @@
       <c r="BC4" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD4" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -82452,6 +83342,9 @@
       <c r="BC5" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BD5" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -82619,6 +83512,9 @@
       <c r="BC6" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD6" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -82784,6 +83680,9 @@
         <v>2</v>
       </c>
       <c r="BC7" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD7" s="24" t="n">
         <v>2</v>
       </c>
     </row>
@@ -82953,6 +83852,9 @@
       <c r="BC8" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD8" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -83120,6 +84022,9 @@
       <c r="BC9" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD9" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -83287,6 +84192,9 @@
       <c r="BC10" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD10" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -83454,6 +84362,9 @@
       <c r="BC11" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD11" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -83621,6 +84532,9 @@
       <c r="BC12" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BD12" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -83788,6 +84702,9 @@
       <c r="BC13" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD13" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -83955,6 +84872,9 @@
       <c r="BC14" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD14" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -84122,6 +85042,9 @@
       <c r="BC15" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD15" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -84289,6 +85212,9 @@
       <c r="BC16" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD16" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -84456,6 +85382,9 @@
       <c r="BC17" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="BD17" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -84623,6 +85552,9 @@
       <c r="BC18" s="24" t="n">
         <v>5</v>
       </c>
+      <c r="BD18" s="24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -84790,6 +85722,9 @@
       <c r="BC19" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD19" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -84957,6 +85892,9 @@
       <c r="BC20" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="BD20" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -85124,6 +86062,9 @@
       <c r="BC21" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="BD21" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -85293,6 +86234,9 @@
       <c r="BC22" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="BD22" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n"/>
@@ -85464,6 +86408,9 @@
         <v>47</v>
       </c>
       <c r="BC24" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="BD24" s="24" t="n">
         <v>50</v>
       </c>
     </row>

--- a/2026 수능 LLM 풀이 hard.xlsx
+++ b/2026 수능 LLM 풀이 hard.xlsx
@@ -947,7 +947,7 @@
       <c r="BC3" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="BD3" s="24" t="n">
+      <c r="BD3" s="26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       <c r="BC4" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="BD4" s="24" t="n">
+      <c r="BD4" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       <c r="BC5" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="BD5" s="24" t="n">
+      <c r="BD5" s="26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       <c r="BC6" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="BD6" s="24" t="n">
+      <c r="BD6" s="26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
       <c r="BC7" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="BD7" s="24" t="n">
+      <c r="BD7" s="26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       <c r="BC8" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="BD8" s="24" t="n">
+      <c r="BD8" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1975,7 +1975,7 @@
       <c r="BC9" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="BD9" s="24" t="n">
+      <c r="BD9" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
       <c r="BC10" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="BD10" s="24" t="n">
+      <c r="BD10" s="26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       <c r="BC11" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="BD11" s="24" t="n">
+      <c r="BD11" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
       <c r="BC12" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="BD12" s="24" t="n">
+      <c r="BD12" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2661,7 +2661,7 @@
       <c r="BC13" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="BD13" s="24" t="n">
+      <c r="BD13" s="26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       <c r="BC14" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="BD14" s="24" t="n">
+      <c r="BD14" s="26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       <c r="BC15" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="BD15" s="24" t="n">
+      <c r="BD15" s="26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       <c r="BC16" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="BD16" s="24" t="n">
+      <c r="BD16" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       <c r="BC17" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="BD17" s="24" t="n">
+      <c r="BD17" s="26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       <c r="BC18" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="BD18" s="24" t="n">
+      <c r="BD18" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3689,7 +3689,7 @@
       <c r="BC19" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="BD19" s="24" t="n">
+      <c r="BD19" s="26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
       <c r="BC20" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="BD20" s="24" t="n">
+      <c r="BD20" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4033,7 +4033,7 @@
       <c r="BC21" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="BD21" s="24" t="n">
+      <c r="BD21" s="26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4205,7 +4205,7 @@
       <c r="BC22" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="BD22" s="24" t="n">
+      <c r="BD22" s="26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       <c r="BC23" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="BD23" s="24" t="n">
+      <c r="BD23" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4549,7 +4549,7 @@
       <c r="BC24" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="BD24" s="24" t="n">
+      <c r="BD24" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4721,7 +4721,7 @@
       <c r="BC25" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="BD25" s="24" t="n">
+      <c r="BD25" s="26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4893,7 +4893,7 @@
       <c r="BC26" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="BD26" s="24" t="n">
+      <c r="BD26" s="26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5065,7 +5065,7 @@
       <c r="BC27" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="BD27" s="24" t="n">
+      <c r="BD27" s="26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5237,7 +5237,7 @@
       <c r="BC28" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="BD28" s="24" t="n">
+      <c r="BD28" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       <c r="BC29" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="BD29" s="24" t="n">
+      <c r="BD29" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5585,7 +5585,7 @@
       <c r="BC30" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="BD30" s="24" t="n">
+      <c r="BD30" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5759,7 +5759,7 @@
       <c r="BC31" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="BD31" s="24" t="n">
+      <c r="BD31" s="26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5933,7 +5933,7 @@
       <c r="BC32" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="BD32" s="24" t="n">
+      <c r="BD32" s="26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6107,7 +6107,7 @@
       <c r="BC33" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="BD33" s="24" t="n">
+      <c r="BD33" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6281,7 +6281,7 @@
       <c r="BC34" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="BD34" s="24" t="n">
+      <c r="BD34" s="26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
       <c r="BC35" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="BD35" s="24" t="n">
+      <c r="BD35" s="26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6629,7 +6629,7 @@
       <c r="BC36" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="BD36" s="24" t="n">
+      <c r="BD36" s="26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -11147,10 +11147,8 @@
       <c r="BC3" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="BD3" s="25" t="inlineStr">
-        <is>
-          <t>(포기)</t>
-        </is>
+      <c r="BD3" s="26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -15016,7 +15014,7 @@
         <v>47</v>
       </c>
       <c r="BD24" s="24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -27729,8 +27727,10 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD3" s="24" t="n">
-        <v>5</v>
+      <c r="BD3" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -27915,8 +27915,10 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD4" s="24" t="n">
-        <v>4</v>
+      <c r="BD4" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -28101,8 +28103,10 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD5" s="24" t="n">
-        <v>1</v>
+      <c r="BD5" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -28287,8 +28291,10 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD6" s="24" t="n">
-        <v>3</v>
+      <c r="BD6" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -28475,8 +28481,10 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD7" s="24" t="n">
-        <v>4</v>
+      <c r="BD7" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -28663,8 +28671,10 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD8" s="24" t="n">
-        <v>3</v>
+      <c r="BD8" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -28849,8 +28859,10 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD9" s="24" t="n">
-        <v>3</v>
+      <c r="BD9" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -29037,8 +29049,10 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD10" s="24" t="n">
-        <v>5</v>
+      <c r="BD10" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -29227,8 +29241,10 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD11" s="24" t="n">
-        <v>5</v>
+      <c r="BD11" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -29415,8 +29431,10 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD12" s="24" t="n">
-        <v>1</v>
+      <c r="BD12" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -29605,8 +29623,10 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD13" s="24" t="n">
-        <v>1</v>
+      <c r="BD13" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -29793,8 +29813,10 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD14" s="24" t="n">
-        <v>2</v>
+      <c r="BD14" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -29983,8 +30005,10 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD15" s="24" t="n">
-        <v>2</v>
+      <c r="BD15" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -30175,8 +30199,10 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD16" s="25" t="n">
-        <v>3</v>
+      <c r="BD16" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -30367,8 +30393,10 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD17" s="25" t="n">
-        <v>2</v>
+      <c r="BD17" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -30559,8 +30587,10 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD18" s="24" t="n">
-        <v>1</v>
+      <c r="BD18" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -30751,8 +30781,10 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD19" s="25" t="n">
-        <v>4</v>
+      <c r="BD19" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -30943,8 +30975,10 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD20" s="25" t="n">
-        <v>2</v>
+      <c r="BD20" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -31137,8 +31171,10 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD21" s="24" t="n">
-        <v>5</v>
+      <c r="BD21" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -31329,8 +31365,10 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD22" s="24" t="n">
-        <v>2</v>
+      <c r="BD22" s="25" t="inlineStr">
+        <is>
+          <t>(포기)</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -31506,7 +31544,7 @@
         <v>0</v>
       </c>
       <c r="BD24" s="24" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -35899,7 +35937,7 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD3" s="24" t="n">
+      <c r="BD3" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -36079,7 +36117,7 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD4" s="24" t="n">
+      <c r="BD4" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -36259,7 +36297,7 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD5" s="24" t="n">
+      <c r="BD5" s="26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -36439,7 +36477,7 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD6" s="24" t="n">
+      <c r="BD6" s="26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -36619,7 +36657,7 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD7" s="24" t="n">
+      <c r="BD7" s="26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -36801,7 +36839,7 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD8" s="24" t="n">
+      <c r="BD8" s="26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -36983,7 +37021,7 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD9" s="24" t="n">
+      <c r="BD9" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -37165,7 +37203,7 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD10" s="24" t="n">
+      <c r="BD10" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -37349,7 +37387,7 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD11" s="24" t="n">
+      <c r="BD11" s="26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -37537,7 +37575,7 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD12" s="24" t="n">
+      <c r="BD12" s="26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -37721,7 +37759,7 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD13" s="24" t="n">
+      <c r="BD13" s="26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -37905,7 +37943,7 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD14" s="24" t="n">
+      <c r="BD14" s="26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -38091,7 +38129,7 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD15" s="24" t="n">
+      <c r="BD15" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -38277,7 +38315,7 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD16" s="24" t="n">
+      <c r="BD16" s="26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -38467,7 +38505,7 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD17" s="24" t="n">
+      <c r="BD17" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -38653,7 +38691,7 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD18" s="24" t="n">
+      <c r="BD18" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -38839,7 +38877,7 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD19" s="24" t="n">
+      <c r="BD19" s="26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -39025,7 +39063,7 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD20" s="24" t="n">
+      <c r="BD20" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -39211,7 +39249,7 @@
           <t>(검열)</t>
         </is>
       </c>
-      <c r="BD21" s="24" t="n">
+      <c r="BD21" s="26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -43965,7 +44003,7 @@
       <c r="BC3" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="BD3" s="24" t="n">
+      <c r="BD3" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -44135,7 +44173,7 @@
       <c r="BC4" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="BD4" s="24" t="n">
+      <c r="BD4" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -44307,7 +44345,7 @@
       <c r="BC5" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="BD5" s="24" t="n">
+      <c r="BD5" s="26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -44479,7 +44517,7 @@
       <c r="BC6" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="BD6" s="24" t="n">
+      <c r="BD6" s="26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -44651,7 +44689,7 @@
       <c r="BC7" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="BD7" s="24" t="n">
+      <c r="BD7" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -44823,7 +44861,7 @@
       <c r="BC8" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="BD8" s="24" t="n">
+      <c r="BD8" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -44995,7 +45033,7 @@
       <c r="BC9" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="BD9" s="24" t="n">
+      <c r="BD9" s="26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -45167,7 +45205,7 @@
       <c r="BC10" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="BD10" s="24" t="n">
+      <c r="BD10" s="26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -45339,7 +45377,7 @@
       <c r="BC11" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="BD11" s="24" t="n">
+      <c r="BD11" s="26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -45511,7 +45549,7 @@
       <c r="BC12" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="BD12" s="24" t="n">
+      <c r="BD12" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -45685,7 +45723,7 @@
       <c r="BC13" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="BD13" s="24" t="n">
+      <c r="BD13" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -56679,7 +56717,7 @@
       <c r="BC3" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="BD3" s="24" t="n">
+      <c r="BD3" s="26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -56853,7 +56891,7 @@
       <c r="BC4" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="BD4" s="24" t="n">
+      <c r="BD4" s="26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -57027,7 +57065,7 @@
       <c r="BC5" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="BD5" s="24" t="n">
+      <c r="BD5" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -57201,7 +57239,7 @@
       <c r="BC6" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="BD6" s="24" t="n">
+      <c r="BD6" s="26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -57375,7 +57413,7 @@
       <c r="BC7" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="BD7" s="24" t="n">
+      <c r="BD7" s="26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -57549,7 +57587,7 @@
       <c r="BC8" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="BD8" s="24" t="n">
+      <c r="BD8" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -57723,7 +57761,7 @@
       <c r="BC9" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="BD9" s="24" t="n">
+      <c r="BD9" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -57899,7 +57937,7 @@
       <c r="BC10" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="BD10" s="24" t="n">
+      <c r="BD10" s="26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -58075,7 +58113,7 @@
       <c r="BC11" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="BD11" s="24" t="n">
+      <c r="BD11" s="26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -58257,7 +58295,7 @@
       <c r="BC12" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="BD12" s="24" t="n">
+      <c r="BD12" s="26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -58617,7 +58655,7 @@
       <c r="BC14" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="BD14" s="24" t="n">
+      <c r="BD14" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -58797,7 +58835,7 @@
       <c r="BC15" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="BD15" s="24" t="n">
+      <c r="BD15" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -58981,7 +59019,7 @@
       <c r="BC16" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="BD16" s="24" t="n">
+      <c r="BD16" s="26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -59167,7 +59205,7 @@
       <c r="BC17" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="BD17" s="24" t="n">
+      <c r="BD17" s="26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -59347,7 +59385,7 @@
       <c r="BC18" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="BD18" s="24" t="n">
+      <c r="BD18" s="26" t="n">
         <v>9</v>
       </c>
     </row>
@@ -59527,7 +59565,7 @@
       <c r="BC19" s="24" t="n">
         <v>16</v>
       </c>
-      <c r="BD19" s="24" t="n">
+      <c r="BD19" s="26" t="n">
         <v>16</v>
       </c>
     </row>
@@ -59711,7 +59749,7 @@
       <c r="BC20" s="24" t="n">
         <v>12</v>
       </c>
-      <c r="BD20" s="24" t="n">
+      <c r="BD20" s="26" t="n">
         <v>12</v>
       </c>
     </row>
@@ -59895,7 +59933,7 @@
       <c r="BC21" s="24" t="n">
         <v>15</v>
       </c>
-      <c r="BD21" s="24" t="n">
+      <c r="BD21" s="26" t="n">
         <v>15</v>
       </c>
     </row>
@@ -60089,7 +60127,7 @@
       <c r="BC22" s="24" t="n">
         <v>130</v>
       </c>
-      <c r="BD22" s="24" t="n">
+      <c r="BD22" s="26" t="n">
         <v>130</v>
       </c>
     </row>
@@ -60489,7 +60527,7 @@
       <c r="BC24" s="24" t="n">
         <v>457</v>
       </c>
-      <c r="BD24" s="24" t="n">
+      <c r="BD24" s="26" t="n">
         <v>457</v>
       </c>
     </row>
@@ -61191,7 +61229,7 @@
       <c r="BC3" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="BD3" s="24" t="n">
+      <c r="BD3" s="26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -61361,7 +61399,7 @@
       <c r="BC4" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="BD4" s="24" t="n">
+      <c r="BD4" s="26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -61533,7 +61571,7 @@
       <c r="BC5" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="BD5" s="24" t="n">
+      <c r="BD5" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -61703,7 +61741,7 @@
       <c r="BC6" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="BD6" s="24" t="n">
+      <c r="BD6" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -61875,7 +61913,7 @@
       <c r="BC7" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="BD7" s="24" t="n">
+      <c r="BD7" s="26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -62055,7 +62093,7 @@
       <c r="BC8" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="BD8" s="24" t="n">
+      <c r="BD8" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -62233,7 +62271,7 @@
       <c r="BC9" s="24" t="n">
         <v>977</v>
       </c>
-      <c r="BD9" s="24" t="n">
+      <c r="BD9" s="26" t="n">
         <v>977</v>
       </c>
     </row>
@@ -62415,7 +62453,7 @@
       <c r="BC10" s="24" t="n">
         <v>262</v>
       </c>
-      <c r="BD10" s="24" t="n">
+      <c r="BD10" s="26" t="n">
         <v>262</v>
       </c>
     </row>
@@ -63175,7 +63213,7 @@
       <c r="BC3" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="BD3" s="24" t="n">
+      <c r="BD3" s="26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -63349,7 +63387,7 @@
       <c r="BC4" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="BD4" s="24" t="n">
+      <c r="BD4" s="26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -63523,7 +63561,7 @@
       <c r="BC5" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="BD5" s="24" t="n">
+      <c r="BD5" s="26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -63697,7 +63735,7 @@
       <c r="BC6" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="BD6" s="24" t="n">
+      <c r="BD6" s="26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -63871,7 +63909,7 @@
       <c r="BC7" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="BD7" s="24" t="n">
+      <c r="BD7" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -64045,7 +64083,7 @@
       <c r="BC8" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="BD8" s="24" t="n">
+      <c r="BD8" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -64227,7 +64265,7 @@
       <c r="BC9" s="24" t="n">
         <v>97</v>
       </c>
-      <c r="BD9" s="24" t="n">
+      <c r="BD9" s="26" t="n">
         <v>97</v>
       </c>
     </row>
@@ -64419,7 +64457,7 @@
       <c r="BC10" s="24" t="n">
         <v>11</v>
       </c>
-      <c r="BD10" s="24" t="n">
+      <c r="BD10" s="26" t="n">
         <v>11</v>
       </c>
     </row>
@@ -69031,7 +69069,7 @@
       <c r="BC3" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="BD3" s="24" t="n">
+      <c r="BD3" s="26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -69203,7 +69241,7 @@
       <c r="BC4" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="BD4" s="24" t="n">
+      <c r="BD4" s="26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -69379,7 +69417,7 @@
       <c r="BC5" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="BD5" s="24" t="n">
+      <c r="BD5" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -69553,7 +69591,7 @@
       <c r="BC6" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="BD6" s="24" t="n">
+      <c r="BD6" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -69727,7 +69765,7 @@
       <c r="BC7" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="BD7" s="24" t="n">
+      <c r="BD7" s="26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -69899,7 +69937,7 @@
       <c r="BC8" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="BD8" s="24" t="n">
+      <c r="BD8" s="26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -70077,7 +70115,7 @@
       <c r="BC9" s="24" t="n">
         <v>360</v>
       </c>
-      <c r="BD9" s="24" t="n">
+      <c r="BD9" s="26" t="n">
         <v>360</v>
       </c>
     </row>
@@ -70255,7 +70293,7 @@
       <c r="BC10" s="24" t="n">
         <v>221</v>
       </c>
-      <c r="BD10" s="24" t="n">
+      <c r="BD10" s="26" t="n">
         <v>221</v>
       </c>
     </row>
@@ -71012,7 +71050,7 @@
       <c r="BC3" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="BD3" s="24" t="n">
+      <c r="BD3" s="26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -71182,7 +71220,7 @@
       <c r="BC4" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="BD4" s="24" t="n">
+      <c r="BD4" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -71352,7 +71390,7 @@
       <c r="BC5" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="BD5" s="24" t="n">
+      <c r="BD5" s="26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -71528,7 +71566,7 @@
       <c r="BC6" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="BD6" s="24" t="n">
+      <c r="BD6" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -71698,7 +71736,7 @@
       <c r="BC7" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="BD7" s="24" t="n">
+      <c r="BD7" s="26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -71868,7 +71906,7 @@
       <c r="BC8" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="BD8" s="24" t="n">
+      <c r="BD8" s="26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -72038,7 +72076,7 @@
       <c r="BC9" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="BD9" s="24" t="n">
+      <c r="BD9" s="26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -72208,7 +72246,7 @@
       <c r="BC10" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="BD10" s="24" t="n">
+      <c r="BD10" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -72378,7 +72416,7 @@
       <c r="BC11" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="BD11" s="24" t="n">
+      <c r="BD11" s="26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -72548,7 +72586,7 @@
       <c r="BC12" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="BD12" s="24" t="n">
+      <c r="BD12" s="26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -72718,7 +72756,7 @@
       <c r="BC13" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="BD13" s="24" t="n">
+      <c r="BD13" s="26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -72888,7 +72926,7 @@
       <c r="BC14" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="BD14" s="24" t="n">
+      <c r="BD14" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -73058,7 +73096,7 @@
       <c r="BC15" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="BD15" s="24" t="n">
+      <c r="BD15" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -73228,7 +73266,7 @@
       <c r="BC16" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="BD16" s="24" t="n">
+      <c r="BD16" s="26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -73398,7 +73436,7 @@
       <c r="BC17" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="BD17" s="24" t="n">
+      <c r="BD17" s="26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -73568,7 +73606,7 @@
       <c r="BC18" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="BD18" s="24" t="n">
+      <c r="BD18" s="26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -73738,7 +73776,7 @@
       <c r="BC19" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="BD19" s="24" t="n">
+      <c r="BD19" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -73908,7 +73946,7 @@
       <c r="BC20" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="BD20" s="24" t="n">
+      <c r="BD20" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -74078,7 +74116,7 @@
       <c r="BC21" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="BD21" s="24" t="n">
+      <c r="BD21" s="26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -74248,7 +74286,7 @@
       <c r="BC22" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="BD22" s="24" t="n">
+      <c r="BD22" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -74418,7 +74456,7 @@
       <c r="BC23" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="BD23" s="24" t="n">
+      <c r="BD23" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -74588,7 +74626,7 @@
       <c r="BC24" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="BD24" s="24" t="n">
+      <c r="BD24" s="26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -74758,7 +74796,7 @@
       <c r="BC25" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="BD25" s="24" t="n">
+      <c r="BD25" s="26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -74928,7 +74966,7 @@
       <c r="BC26" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="BD26" s="24" t="n">
+      <c r="BD26" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -75102,7 +75140,7 @@
       <c r="BC27" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="BD27" s="24" t="n">
+      <c r="BD27" s="26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -75272,7 +75310,7 @@
       <c r="BC28" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="BD28" s="24" t="n">
+      <c r="BD28" s="26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -75442,7 +75480,7 @@
       <c r="BC29" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="BD29" s="24" t="n">
+      <c r="BD29" s="26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -75612,7 +75650,7 @@
       <c r="BC30" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="BD30" s="24" t="n">
+      <c r="BD30" s="26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -75782,7 +75820,7 @@
       <c r="BC31" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="BD31" s="24" t="n">
+      <c r="BD31" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -75952,7 +75990,7 @@
       <c r="BC32" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="BD32" s="24" t="n">
+      <c r="BD32" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -76124,7 +76162,7 @@
       <c r="BC33" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="BD33" s="24" t="n">
+      <c r="BD33" s="26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -76296,7 +76334,7 @@
       <c r="BC34" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="BD34" s="24" t="n">
+      <c r="BD34" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -76468,7 +76506,7 @@
       <c r="BC35" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="BD35" s="24" t="n">
+      <c r="BD35" s="26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -76640,7 +76678,7 @@
       <c r="BC36" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="BD36" s="24" t="n">
+      <c r="BD36" s="26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -76812,7 +76850,7 @@
       <c r="BC37" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="BD37" s="24" t="n">
+      <c r="BD37" s="26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -76984,7 +77022,7 @@
       <c r="BC38" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="BD38" s="24" t="n">
+      <c r="BD38" s="26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -77156,7 +77194,7 @@
       <c r="BC39" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="BD39" s="24" t="n">
+      <c r="BD39" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -77328,7 +77366,7 @@
       <c r="BC40" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="BD40" s="24" t="n">
+      <c r="BD40" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -77674,7 +77712,7 @@
       <c r="BC42" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="BD42" s="24" t="n">
+      <c r="BD42" s="26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -77846,7 +77884,7 @@
       <c r="BC43" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="BD43" s="24" t="n">
+      <c r="BD43" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -78018,7 +78056,7 @@
       <c r="BC44" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="BD44" s="24" t="n">
+      <c r="BD44" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -78190,7 +78228,7 @@
       <c r="BC45" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="BD45" s="24" t="n">
+      <c r="BD45" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -78362,7 +78400,7 @@
       <c r="BC46" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="BD46" s="24" t="n">
+      <c r="BD46" s="26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -78534,7 +78572,7 @@
       <c r="BC47" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="BD47" s="24" t="n">
+      <c r="BD47" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -83000,7 +83038,7 @@
       <c r="BC3" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="BD3" s="24" t="n">
+      <c r="BD3" s="26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -83172,7 +83210,7 @@
       <c r="BC4" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="BD4" s="24" t="n">
+      <c r="BD4" s="26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -83342,7 +83380,7 @@
       <c r="BC5" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="BD5" s="24" t="n">
+      <c r="BD5" s="26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -83512,7 +83550,7 @@
       <c r="BC6" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="BD6" s="24" t="n">
+      <c r="BD6" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -83682,7 +83720,7 @@
       <c r="BC7" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="BD7" s="24" t="n">
+      <c r="BD7" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -83852,7 +83890,7 @@
       <c r="BC8" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="BD8" s="24" t="n">
+      <c r="BD8" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -84022,7 +84060,7 @@
       <c r="BC9" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="BD9" s="24" t="n">
+      <c r="BD9" s="26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -84192,7 +84230,7 @@
       <c r="BC10" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="BD10" s="24" t="n">
+      <c r="BD10" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -84362,7 +84400,7 @@
       <c r="BC11" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="BD11" s="24" t="n">
+      <c r="BD11" s="26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -84532,7 +84570,7 @@
       <c r="BC12" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="BD12" s="24" t="n">
+      <c r="BD12" s="26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -84702,7 +84740,7 @@
       <c r="BC13" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="BD13" s="24" t="n">
+      <c r="BD13" s="26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -84872,7 +84910,7 @@
       <c r="BC14" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="BD14" s="24" t="n">
+      <c r="BD14" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -85042,7 +85080,7 @@
       <c r="BC15" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="BD15" s="24" t="n">
+      <c r="BD15" s="26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -85212,7 +85250,7 @@
       <c r="BC16" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="BD16" s="24" t="n">
+      <c r="BD16" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -85382,7 +85420,7 @@
       <c r="BC17" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="BD17" s="24" t="n">
+      <c r="BD17" s="26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -85552,7 +85590,7 @@
       <c r="BC18" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="BD18" s="24" t="n">
+      <c r="BD18" s="26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -85722,7 +85760,7 @@
       <c r="BC19" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="BD19" s="24" t="n">
+      <c r="BD19" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -85892,7 +85930,7 @@
       <c r="BC20" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="BD20" s="24" t="n">
+      <c r="BD20" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -86062,7 +86100,7 @@
       <c r="BC21" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="BD21" s="24" t="n">
+      <c r="BD21" s="26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -86234,7 +86272,7 @@
       <c r="BC22" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="BD22" s="24" t="n">
+      <c r="BD22" s="26" t="n">
         <v>4</v>
       </c>
     </row>
